--- a/code_and_data/ai_output/validation_sample.xlsx
+++ b/code_and_data/ai_output/validation_sample.xlsx
@@ -559,14 +559,6 @@
       <c r="J2" t="b">
         <v>0</v>
       </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -617,14 +609,6 @@
       <c r="J3" t="b">
         <v>0</v>
       </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -675,14 +659,6 @@
       <c r="J4" t="b">
         <v>0</v>
       </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -733,14 +709,6 @@
       <c r="J5" t="b">
         <v>0</v>
       </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -791,14 +759,6 @@
       <c r="J6" t="b">
         <v>0</v>
       </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -849,14 +809,6 @@
       <c r="J7" t="b">
         <v>0</v>
       </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -907,14 +859,6 @@
       <c r="J8" t="b">
         <v>0</v>
       </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -965,14 +909,6 @@
       <c r="J9" t="b">
         <v>0</v>
       </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1023,14 +959,6 @@
       <c r="J10" t="b">
         <v>0</v>
       </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1081,14 +1009,6 @@
       <c r="J11" t="b">
         <v>0</v>
       </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1139,14 +1059,6 @@
       <c r="J12" t="b">
         <v>0</v>
       </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1202,13 +1114,6 @@
           <t>Staff member Raj named positively; contradictory signals between positive staff experience and poor follow-up communication</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1259,14 +1164,6 @@
       <c r="J14" t="b">
         <v>0</v>
       </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1317,14 +1214,6 @@
       <c r="J15" t="b">
         <v>0</v>
       </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1375,14 +1264,6 @@
       <c r="J16" t="b">
         <v>0</v>
       </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
-      <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr"/>
-      <c r="R16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1433,14 +1314,6 @@
       <c r="J17" t="b">
         <v>0</v>
       </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1491,14 +1364,6 @@
       <c r="J18" t="b">
         <v>0</v>
       </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr"/>
-      <c r="R18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1549,14 +1414,6 @@
       <c r="J19" t="b">
         <v>0</v>
       </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
-      <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr"/>
-      <c r="R19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1607,14 +1464,6 @@
       <c r="J20" t="b">
         <v>0</v>
       </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr"/>
-      <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="inlineStr"/>
-      <c r="R20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1665,14 +1514,6 @@
       <c r="J21" t="b">
         <v>0</v>
       </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr"/>
-      <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="inlineStr"/>
-      <c r="R21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1723,14 +1564,6 @@
       <c r="J22" t="b">
         <v>0</v>
       </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr"/>
-      <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="inlineStr"/>
-      <c r="R22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1781,14 +1614,6 @@
       <c r="J23" t="b">
         <v>0</v>
       </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr"/>
-      <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="inlineStr"/>
-      <c r="R23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1839,14 +1664,6 @@
       <c r="J24" t="b">
         <v>0</v>
       </c>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="inlineStr"/>
-      <c r="P24" t="inlineStr"/>
-      <c r="Q24" t="inlineStr"/>
-      <c r="R24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1897,14 +1714,6 @@
       <c r="J25" t="b">
         <v>0</v>
       </c>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="inlineStr"/>
-      <c r="P25" t="inlineStr"/>
-      <c r="Q25" t="inlineStr"/>
-      <c r="R25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1955,14 +1764,6 @@
       <c r="J26" t="b">
         <v>0</v>
       </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr"/>
-      <c r="P26" t="inlineStr"/>
-      <c r="Q26" t="inlineStr"/>
-      <c r="R26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2013,14 +1814,6 @@
       <c r="J27" t="b">
         <v>0</v>
       </c>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
-      <c r="O27" t="inlineStr"/>
-      <c r="P27" t="inlineStr"/>
-      <c r="Q27" t="inlineStr"/>
-      <c r="R27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2071,14 +1864,6 @@
       <c r="J28" t="b">
         <v>0</v>
       </c>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
-      <c r="O28" t="inlineStr"/>
-      <c r="P28" t="inlineStr"/>
-      <c r="Q28" t="inlineStr"/>
-      <c r="R28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2129,14 +1914,6 @@
       <c r="J29" t="b">
         <v>0</v>
       </c>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
-      <c r="O29" t="inlineStr"/>
-      <c r="P29" t="inlineStr"/>
-      <c r="Q29" t="inlineStr"/>
-      <c r="R29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2187,14 +1964,6 @@
       <c r="J30" t="b">
         <v>0</v>
       </c>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
-      <c r="O30" t="inlineStr"/>
-      <c r="P30" t="inlineStr"/>
-      <c r="Q30" t="inlineStr"/>
-      <c r="R30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2245,14 +2014,6 @@
       <c r="J31" t="b">
         <v>0</v>
       </c>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
-      <c r="O31" t="inlineStr"/>
-      <c r="P31" t="inlineStr"/>
-      <c r="Q31" t="inlineStr"/>
-      <c r="R31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2303,14 +2064,6 @@
       <c r="J32" t="b">
         <v>0</v>
       </c>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
-      <c r="O32" t="inlineStr"/>
-      <c r="P32" t="inlineStr"/>
-      <c r="Q32" t="inlineStr"/>
-      <c r="R32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2361,14 +2114,6 @@
       <c r="J33" t="b">
         <v>0</v>
       </c>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
-      <c r="O33" t="inlineStr"/>
-      <c r="P33" t="inlineStr"/>
-      <c r="Q33" t="inlineStr"/>
-      <c r="R33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2419,14 +2164,6 @@
       <c r="J34" t="b">
         <v>0</v>
       </c>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
-      <c r="O34" t="inlineStr"/>
-      <c r="P34" t="inlineStr"/>
-      <c r="Q34" t="inlineStr"/>
-      <c r="R34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2477,14 +2214,6 @@
       <c r="J35" t="b">
         <v>0</v>
       </c>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
-      <c r="O35" t="inlineStr"/>
-      <c r="P35" t="inlineStr"/>
-      <c r="Q35" t="inlineStr"/>
-      <c r="R35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2535,14 +2264,6 @@
       <c r="J36" t="b">
         <v>0</v>
       </c>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
-      <c r="O36" t="inlineStr"/>
-      <c r="P36" t="inlineStr"/>
-      <c r="Q36" t="inlineStr"/>
-      <c r="R36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2593,14 +2314,6 @@
       <c r="J37" t="b">
         <v>0</v>
       </c>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
-      <c r="O37" t="inlineStr"/>
-      <c r="P37" t="inlineStr"/>
-      <c r="Q37" t="inlineStr"/>
-      <c r="R37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2651,14 +2364,6 @@
       <c r="J38" t="b">
         <v>0</v>
       </c>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
-      <c r="O38" t="inlineStr"/>
-      <c r="P38" t="inlineStr"/>
-      <c r="Q38" t="inlineStr"/>
-      <c r="R38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2709,14 +2414,6 @@
       <c r="J39" t="b">
         <v>0</v>
       </c>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
-      <c r="O39" t="inlineStr"/>
-      <c r="P39" t="inlineStr"/>
-      <c r="Q39" t="inlineStr"/>
-      <c r="R39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2767,14 +2464,6 @@
       <c r="J40" t="b">
         <v>0</v>
       </c>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
-      <c r="O40" t="inlineStr"/>
-      <c r="P40" t="inlineStr"/>
-      <c r="Q40" t="inlineStr"/>
-      <c r="R40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2825,14 +2514,6 @@
       <c r="J41" t="b">
         <v>0</v>
       </c>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
-      <c r="O41" t="inlineStr"/>
-      <c r="P41" t="inlineStr"/>
-      <c r="Q41" t="inlineStr"/>
-      <c r="R41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2883,14 +2564,6 @@
       <c r="J42" t="b">
         <v>0</v>
       </c>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
-      <c r="O42" t="inlineStr"/>
-      <c r="P42" t="inlineStr"/>
-      <c r="Q42" t="inlineStr"/>
-      <c r="R42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2941,14 +2614,6 @@
       <c r="J43" t="b">
         <v>0</v>
       </c>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
-      <c r="O43" t="inlineStr"/>
-      <c r="P43" t="inlineStr"/>
-      <c r="Q43" t="inlineStr"/>
-      <c r="R43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2999,14 +2664,6 @@
       <c r="J44" t="b">
         <v>0</v>
       </c>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
-      <c r="O44" t="inlineStr"/>
-      <c r="P44" t="inlineStr"/>
-      <c r="Q44" t="inlineStr"/>
-      <c r="R44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -3057,14 +2714,6 @@
       <c r="J45" t="b">
         <v>0</v>
       </c>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
-      <c r="O45" t="inlineStr"/>
-      <c r="P45" t="inlineStr"/>
-      <c r="Q45" t="inlineStr"/>
-      <c r="R45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -3115,14 +2764,6 @@
       <c r="J46" t="b">
         <v>0</v>
       </c>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
-      <c r="O46" t="inlineStr"/>
-      <c r="P46" t="inlineStr"/>
-      <c r="Q46" t="inlineStr"/>
-      <c r="R46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -3173,14 +2814,6 @@
       <c r="J47" t="b">
         <v>0</v>
       </c>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
-      <c r="O47" t="inlineStr"/>
-      <c r="P47" t="inlineStr"/>
-      <c r="Q47" t="inlineStr"/>
-      <c r="R47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -3231,14 +2864,6 @@
       <c r="J48" t="b">
         <v>0</v>
       </c>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
-      <c r="O48" t="inlineStr"/>
-      <c r="P48" t="inlineStr"/>
-      <c r="Q48" t="inlineStr"/>
-      <c r="R48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -3289,14 +2914,6 @@
       <c r="J49" t="b">
         <v>0</v>
       </c>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
-      <c r="O49" t="inlineStr"/>
-      <c r="P49" t="inlineStr"/>
-      <c r="Q49" t="inlineStr"/>
-      <c r="R49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -3347,14 +2964,6 @@
       <c r="J50" t="b">
         <v>0</v>
       </c>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
-      <c r="O50" t="inlineStr"/>
-      <c r="P50" t="inlineStr"/>
-      <c r="Q50" t="inlineStr"/>
-      <c r="R50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -3405,14 +3014,6 @@
       <c r="J51" t="b">
         <v>0</v>
       </c>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
-      <c r="O51" t="inlineStr"/>
-      <c r="P51" t="inlineStr"/>
-      <c r="Q51" t="inlineStr"/>
-      <c r="R51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -3463,14 +3064,6 @@
       <c r="J52" t="b">
         <v>0</v>
       </c>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
-      <c r="O52" t="inlineStr"/>
-      <c r="P52" t="inlineStr"/>
-      <c r="Q52" t="inlineStr"/>
-      <c r="R52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -3521,14 +3114,6 @@
       <c r="J53" t="b">
         <v>0</v>
       </c>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
-      <c r="O53" t="inlineStr"/>
-      <c r="P53" t="inlineStr"/>
-      <c r="Q53" t="inlineStr"/>
-      <c r="R53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -3579,14 +3164,6 @@
       <c r="J54" t="b">
         <v>0</v>
       </c>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
-      <c r="O54" t="inlineStr"/>
-      <c r="P54" t="inlineStr"/>
-      <c r="Q54" t="inlineStr"/>
-      <c r="R54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -3637,14 +3214,6 @@
       <c r="J55" t="b">
         <v>0</v>
       </c>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
-      <c r="O55" t="inlineStr"/>
-      <c r="P55" t="inlineStr"/>
-      <c r="Q55" t="inlineStr"/>
-      <c r="R55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -3695,14 +3264,6 @@
       <c r="J56" t="b">
         <v>0</v>
       </c>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
-      <c r="O56" t="inlineStr"/>
-      <c r="P56" t="inlineStr"/>
-      <c r="Q56" t="inlineStr"/>
-      <c r="R56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -3753,14 +3314,6 @@
       <c r="J57" t="b">
         <v>0</v>
       </c>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
-      <c r="O57" t="inlineStr"/>
-      <c r="P57" t="inlineStr"/>
-      <c r="Q57" t="inlineStr"/>
-      <c r="R57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -3811,14 +3364,6 @@
       <c r="J58" t="b">
         <v>0</v>
       </c>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
-      <c r="O58" t="inlineStr"/>
-      <c r="P58" t="inlineStr"/>
-      <c r="Q58" t="inlineStr"/>
-      <c r="R58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -3869,14 +3414,6 @@
       <c r="J59" t="b">
         <v>0</v>
       </c>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
-      <c r="O59" t="inlineStr"/>
-      <c r="P59" t="inlineStr"/>
-      <c r="Q59" t="inlineStr"/>
-      <c r="R59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -3927,14 +3464,6 @@
       <c r="J60" t="b">
         <v>0</v>
       </c>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
-      <c r="O60" t="inlineStr"/>
-      <c r="P60" t="inlineStr"/>
-      <c r="Q60" t="inlineStr"/>
-      <c r="R60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -3985,14 +3514,6 @@
       <c r="J61" t="b">
         <v>0</v>
       </c>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
-      <c r="O61" t="inlineStr"/>
-      <c r="P61" t="inlineStr"/>
-      <c r="Q61" t="inlineStr"/>
-      <c r="R61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -4043,14 +3564,6 @@
       <c r="J62" t="b">
         <v>0</v>
       </c>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
-      <c r="O62" t="inlineStr"/>
-      <c r="P62" t="inlineStr"/>
-      <c r="Q62" t="inlineStr"/>
-      <c r="R62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -4101,14 +3614,6 @@
       <c r="J63" t="b">
         <v>0</v>
       </c>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
-      <c r="O63" t="inlineStr"/>
-      <c r="P63" t="inlineStr"/>
-      <c r="Q63" t="inlineStr"/>
-      <c r="R63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -4159,14 +3664,6 @@
       <c r="J64" t="b">
         <v>0</v>
       </c>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
-      <c r="O64" t="inlineStr"/>
-      <c r="P64" t="inlineStr"/>
-      <c r="Q64" t="inlineStr"/>
-      <c r="R64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -4217,14 +3714,6 @@
       <c r="J65" t="b">
         <v>0</v>
       </c>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
-      <c r="O65" t="inlineStr"/>
-      <c r="P65" t="inlineStr"/>
-      <c r="Q65" t="inlineStr"/>
-      <c r="R65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -4249,7 +3738,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Vikram Iyer - Customer stated the pricing was very reasonable and good value for what was done.</t>
+          <t>[REDACTED_NAME] - Customer stated the pricing was very reasonable and good value for what was done.</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -4275,14 +3764,6 @@
       <c r="J66" t="b">
         <v>0</v>
       </c>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
-      <c r="O66" t="inlineStr"/>
-      <c r="P66" t="inlineStr"/>
-      <c r="Q66" t="inlineStr"/>
-      <c r="R66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -4333,14 +3814,6 @@
       <c r="J67" t="b">
         <v>0</v>
       </c>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
-      <c r="O67" t="inlineStr"/>
-      <c r="P67" t="inlineStr"/>
-      <c r="Q67" t="inlineStr"/>
-      <c r="R67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -4391,14 +3864,6 @@
       <c r="J68" t="b">
         <v>0</v>
       </c>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
-      <c r="O68" t="inlineStr"/>
-      <c r="P68" t="inlineStr"/>
-      <c r="Q68" t="inlineStr"/>
-      <c r="R68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -4449,14 +3914,6 @@
       <c r="J69" t="b">
         <v>0</v>
       </c>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
-      <c r="O69" t="inlineStr"/>
-      <c r="P69" t="inlineStr"/>
-      <c r="Q69" t="inlineStr"/>
-      <c r="R69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -4507,14 +3964,6 @@
       <c r="J70" t="b">
         <v>0</v>
       </c>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
-      <c r="O70" t="inlineStr"/>
-      <c r="P70" t="inlineStr"/>
-      <c r="Q70" t="inlineStr"/>
-      <c r="R70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -4539,7 +3988,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Alicia Wallace - Sarcastic but positive - said he almost fell off his chair when the service desk actually called him first.</t>
+          <t>[REDACTED_NAME] - Sarcastic but positive - said he almost fell off his chair when the service desk actually called him first.</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -4565,14 +4014,6 @@
       <c r="J71" t="b">
         <v>0</v>
       </c>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
-      <c r="O71" t="inlineStr"/>
-      <c r="P71" t="inlineStr"/>
-      <c r="Q71" t="inlineStr"/>
-      <c r="R71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -4623,14 +4064,6 @@
       <c r="J72" t="b">
         <v>0</v>
       </c>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
-      <c r="O72" t="inlineStr"/>
-      <c r="P72" t="inlineStr"/>
-      <c r="Q72" t="inlineStr"/>
-      <c r="R72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -4681,14 +4114,6 @@
       <c r="J73" t="b">
         <v>0</v>
       </c>
-      <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
-      <c r="M73" t="inlineStr"/>
-      <c r="N73" t="inlineStr"/>
-      <c r="O73" t="inlineStr"/>
-      <c r="P73" t="inlineStr"/>
-      <c r="Q73" t="inlineStr"/>
-      <c r="R73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -4739,14 +4164,6 @@
       <c r="J74" t="b">
         <v>0</v>
       </c>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
-      <c r="O74" t="inlineStr"/>
-      <c r="P74" t="inlineStr"/>
-      <c r="Q74" t="inlineStr"/>
-      <c r="R74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -4797,14 +4214,6 @@
       <c r="J75" t="b">
         <v>0</v>
       </c>
-      <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr"/>
-      <c r="N75" t="inlineStr"/>
-      <c r="O75" t="inlineStr"/>
-      <c r="P75" t="inlineStr"/>
-      <c r="Q75" t="inlineStr"/>
-      <c r="R75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -4855,14 +4264,6 @@
       <c r="J76" t="b">
         <v>0</v>
       </c>
-      <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr"/>
-      <c r="M76" t="inlineStr"/>
-      <c r="N76" t="inlineStr"/>
-      <c r="O76" t="inlineStr"/>
-      <c r="P76" t="inlineStr"/>
-      <c r="Q76" t="inlineStr"/>
-      <c r="R76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -4913,14 +4314,6 @@
       <c r="J77" t="b">
         <v>0</v>
       </c>
-      <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr"/>
-      <c r="M77" t="inlineStr"/>
-      <c r="N77" t="inlineStr"/>
-      <c r="O77" t="inlineStr"/>
-      <c r="P77" t="inlineStr"/>
-      <c r="Q77" t="inlineStr"/>
-      <c r="R77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -4971,14 +4364,6 @@
       <c r="J78" t="b">
         <v>0</v>
       </c>
-      <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr"/>
-      <c r="M78" t="inlineStr"/>
-      <c r="N78" t="inlineStr"/>
-      <c r="O78" t="inlineStr"/>
-      <c r="P78" t="inlineStr"/>
-      <c r="Q78" t="inlineStr"/>
-      <c r="R78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -5029,14 +4414,6 @@
       <c r="J79" t="b">
         <v>0</v>
       </c>
-      <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr"/>
-      <c r="M79" t="inlineStr"/>
-      <c r="N79" t="inlineStr"/>
-      <c r="O79" t="inlineStr"/>
-      <c r="P79" t="inlineStr"/>
-      <c r="Q79" t="inlineStr"/>
-      <c r="R79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -5087,14 +4464,6 @@
       <c r="J80" t="b">
         <v>0</v>
       </c>
-      <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
-      <c r="M80" t="inlineStr"/>
-      <c r="N80" t="inlineStr"/>
-      <c r="O80" t="inlineStr"/>
-      <c r="P80" t="inlineStr"/>
-      <c r="Q80" t="inlineStr"/>
-      <c r="R80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -5145,14 +4514,6 @@
       <c r="J81" t="b">
         <v>0</v>
       </c>
-      <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr"/>
-      <c r="N81" t="inlineStr"/>
-      <c r="O81" t="inlineStr"/>
-      <c r="P81" t="inlineStr"/>
-      <c r="Q81" t="inlineStr"/>
-      <c r="R81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -5203,14 +4564,6 @@
       <c r="J82" t="b">
         <v>0</v>
       </c>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr"/>
-      <c r="N82" t="inlineStr"/>
-      <c r="O82" t="inlineStr"/>
-      <c r="P82" t="inlineStr"/>
-      <c r="Q82" t="inlineStr"/>
-      <c r="R82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -5261,14 +4614,6 @@
       <c r="J83" t="b">
         <v>0</v>
       </c>
-      <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
-      <c r="M83" t="inlineStr"/>
-      <c r="N83" t="inlineStr"/>
-      <c r="O83" t="inlineStr"/>
-      <c r="P83" t="inlineStr"/>
-      <c r="Q83" t="inlineStr"/>
-      <c r="R83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -5319,14 +4664,6 @@
       <c r="J84" t="b">
         <v>0</v>
       </c>
-      <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr"/>
-      <c r="M84" t="inlineStr"/>
-      <c r="N84" t="inlineStr"/>
-      <c r="O84" t="inlineStr"/>
-      <c r="P84" t="inlineStr"/>
-      <c r="Q84" t="inlineStr"/>
-      <c r="R84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -5377,14 +4714,6 @@
       <c r="J85" t="b">
         <v>0</v>
       </c>
-      <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr"/>
-      <c r="M85" t="inlineStr"/>
-      <c r="N85" t="inlineStr"/>
-      <c r="O85" t="inlineStr"/>
-      <c r="P85" t="inlineStr"/>
-      <c r="Q85" t="inlineStr"/>
-      <c r="R85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -5435,14 +4764,6 @@
       <c r="J86" t="b">
         <v>0</v>
       </c>
-      <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr"/>
-      <c r="M86" t="inlineStr"/>
-      <c r="N86" t="inlineStr"/>
-      <c r="O86" t="inlineStr"/>
-      <c r="P86" t="inlineStr"/>
-      <c r="Q86" t="inlineStr"/>
-      <c r="R86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -5493,14 +4814,6 @@
       <c r="J87" t="b">
         <v>0</v>
       </c>
-      <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
-      <c r="M87" t="inlineStr"/>
-      <c r="N87" t="inlineStr"/>
-      <c r="O87" t="inlineStr"/>
-      <c r="P87" t="inlineStr"/>
-      <c r="Q87" t="inlineStr"/>
-      <c r="R87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -5551,14 +4864,6 @@
       <c r="J88" t="b">
         <v>0</v>
       </c>
-      <c r="K88" t="inlineStr"/>
-      <c r="L88" t="inlineStr"/>
-      <c r="M88" t="inlineStr"/>
-      <c r="N88" t="inlineStr"/>
-      <c r="O88" t="inlineStr"/>
-      <c r="P88" t="inlineStr"/>
-      <c r="Q88" t="inlineStr"/>
-      <c r="R88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -5609,14 +4914,6 @@
       <c r="J89" t="b">
         <v>0</v>
       </c>
-      <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr"/>
-      <c r="M89" t="inlineStr"/>
-      <c r="N89" t="inlineStr"/>
-      <c r="O89" t="inlineStr"/>
-      <c r="P89" t="inlineStr"/>
-      <c r="Q89" t="inlineStr"/>
-      <c r="R89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -5667,14 +4964,6 @@
       <c r="J90" t="b">
         <v>0</v>
       </c>
-      <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr"/>
-      <c r="M90" t="inlineStr"/>
-      <c r="N90" t="inlineStr"/>
-      <c r="O90" t="inlineStr"/>
-      <c r="P90" t="inlineStr"/>
-      <c r="Q90" t="inlineStr"/>
-      <c r="R90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -5725,14 +5014,6 @@
       <c r="J91" t="b">
         <v>0</v>
       </c>
-      <c r="K91" t="inlineStr"/>
-      <c r="L91" t="inlineStr"/>
-      <c r="M91" t="inlineStr"/>
-      <c r="N91" t="inlineStr"/>
-      <c r="O91" t="inlineStr"/>
-      <c r="P91" t="inlineStr"/>
-      <c r="Q91" t="inlineStr"/>
-      <c r="R91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -5783,14 +5064,6 @@
       <c r="J92" t="b">
         <v>0</v>
       </c>
-      <c r="K92" t="inlineStr"/>
-      <c r="L92" t="inlineStr"/>
-      <c r="M92" t="inlineStr"/>
-      <c r="N92" t="inlineStr"/>
-      <c r="O92" t="inlineStr"/>
-      <c r="P92" t="inlineStr"/>
-      <c r="Q92" t="inlineStr"/>
-      <c r="R92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -5841,14 +5114,6 @@
       <c r="J93" t="b">
         <v>0</v>
       </c>
-      <c r="K93" t="inlineStr"/>
-      <c r="L93" t="inlineStr"/>
-      <c r="M93" t="inlineStr"/>
-      <c r="N93" t="inlineStr"/>
-      <c r="O93" t="inlineStr"/>
-      <c r="P93" t="inlineStr"/>
-      <c r="Q93" t="inlineStr"/>
-      <c r="R93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -5899,14 +5164,6 @@
       <c r="J94" t="b">
         <v>0</v>
       </c>
-      <c r="K94" t="inlineStr"/>
-      <c r="L94" t="inlineStr"/>
-      <c r="M94" t="inlineStr"/>
-      <c r="N94" t="inlineStr"/>
-      <c r="O94" t="inlineStr"/>
-      <c r="P94" t="inlineStr"/>
-      <c r="Q94" t="inlineStr"/>
-      <c r="R94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -5957,14 +5214,6 @@
       <c r="J95" t="b">
         <v>0</v>
       </c>
-      <c r="K95" t="inlineStr"/>
-      <c r="L95" t="inlineStr"/>
-      <c r="M95" t="inlineStr"/>
-      <c r="N95" t="inlineStr"/>
-      <c r="O95" t="inlineStr"/>
-      <c r="P95" t="inlineStr"/>
-      <c r="Q95" t="inlineStr"/>
-      <c r="R95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -6015,14 +5264,6 @@
       <c r="J96" t="b">
         <v>0</v>
       </c>
-      <c r="K96" t="inlineStr"/>
-      <c r="L96" t="inlineStr"/>
-      <c r="M96" t="inlineStr"/>
-      <c r="N96" t="inlineStr"/>
-      <c r="O96" t="inlineStr"/>
-      <c r="P96" t="inlineStr"/>
-      <c r="Q96" t="inlineStr"/>
-      <c r="R96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -6073,14 +5314,6 @@
       <c r="J97" t="b">
         <v>0</v>
       </c>
-      <c r="K97" t="inlineStr"/>
-      <c r="L97" t="inlineStr"/>
-      <c r="M97" t="inlineStr"/>
-      <c r="N97" t="inlineStr"/>
-      <c r="O97" t="inlineStr"/>
-      <c r="P97" t="inlineStr"/>
-      <c r="Q97" t="inlineStr"/>
-      <c r="R97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -6131,14 +5364,6 @@
       <c r="J98" t="b">
         <v>0</v>
       </c>
-      <c r="K98" t="inlineStr"/>
-      <c r="L98" t="inlineStr"/>
-      <c r="M98" t="inlineStr"/>
-      <c r="N98" t="inlineStr"/>
-      <c r="O98" t="inlineStr"/>
-      <c r="P98" t="inlineStr"/>
-      <c r="Q98" t="inlineStr"/>
-      <c r="R98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -6189,14 +5414,6 @@
       <c r="J99" t="b">
         <v>0</v>
       </c>
-      <c r="K99" t="inlineStr"/>
-      <c r="L99" t="inlineStr"/>
-      <c r="M99" t="inlineStr"/>
-      <c r="N99" t="inlineStr"/>
-      <c r="O99" t="inlineStr"/>
-      <c r="P99" t="inlineStr"/>
-      <c r="Q99" t="inlineStr"/>
-      <c r="R99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -6247,14 +5464,6 @@
       <c r="J100" t="b">
         <v>0</v>
       </c>
-      <c r="K100" t="inlineStr"/>
-      <c r="L100" t="inlineStr"/>
-      <c r="M100" t="inlineStr"/>
-      <c r="N100" t="inlineStr"/>
-      <c r="O100" t="inlineStr"/>
-      <c r="P100" t="inlineStr"/>
-      <c r="Q100" t="inlineStr"/>
-      <c r="R100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -6305,14 +5514,6 @@
       <c r="J101" t="b">
         <v>0</v>
       </c>
-      <c r="K101" t="inlineStr"/>
-      <c r="L101" t="inlineStr"/>
-      <c r="M101" t="inlineStr"/>
-      <c r="N101" t="inlineStr"/>
-      <c r="O101" t="inlineStr"/>
-      <c r="P101" t="inlineStr"/>
-      <c r="Q101" t="inlineStr"/>
-      <c r="R101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -6363,14 +5564,6 @@
       <c r="J102" t="b">
         <v>0</v>
       </c>
-      <c r="K102" t="inlineStr"/>
-      <c r="L102" t="inlineStr"/>
-      <c r="M102" t="inlineStr"/>
-      <c r="N102" t="inlineStr"/>
-      <c r="O102" t="inlineStr"/>
-      <c r="P102" t="inlineStr"/>
-      <c r="Q102" t="inlineStr"/>
-      <c r="R102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -6421,14 +5614,6 @@
       <c r="J103" t="b">
         <v>0</v>
       </c>
-      <c r="K103" t="inlineStr"/>
-      <c r="L103" t="inlineStr"/>
-      <c r="M103" t="inlineStr"/>
-      <c r="N103" t="inlineStr"/>
-      <c r="O103" t="inlineStr"/>
-      <c r="P103" t="inlineStr"/>
-      <c r="Q103" t="inlineStr"/>
-      <c r="R103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -6479,14 +5664,6 @@
       <c r="J104" t="b">
         <v>0</v>
       </c>
-      <c r="K104" t="inlineStr"/>
-      <c r="L104" t="inlineStr"/>
-      <c r="M104" t="inlineStr"/>
-      <c r="N104" t="inlineStr"/>
-      <c r="O104" t="inlineStr"/>
-      <c r="P104" t="inlineStr"/>
-      <c r="Q104" t="inlineStr"/>
-      <c r="R104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -6537,14 +5714,6 @@
       <c r="J105" t="b">
         <v>0</v>
       </c>
-      <c r="K105" t="inlineStr"/>
-      <c r="L105" t="inlineStr"/>
-      <c r="M105" t="inlineStr"/>
-      <c r="N105" t="inlineStr"/>
-      <c r="O105" t="inlineStr"/>
-      <c r="P105" t="inlineStr"/>
-      <c r="Q105" t="inlineStr"/>
-      <c r="R105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -6595,14 +5764,6 @@
       <c r="J106" t="b">
         <v>0</v>
       </c>
-      <c r="K106" t="inlineStr"/>
-      <c r="L106" t="inlineStr"/>
-      <c r="M106" t="inlineStr"/>
-      <c r="N106" t="inlineStr"/>
-      <c r="O106" t="inlineStr"/>
-      <c r="P106" t="inlineStr"/>
-      <c r="Q106" t="inlineStr"/>
-      <c r="R106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -6653,14 +5814,6 @@
       <c r="J107" t="b">
         <v>0</v>
       </c>
-      <c r="K107" t="inlineStr"/>
-      <c r="L107" t="inlineStr"/>
-      <c r="M107" t="inlineStr"/>
-      <c r="N107" t="inlineStr"/>
-      <c r="O107" t="inlineStr"/>
-      <c r="P107" t="inlineStr"/>
-      <c r="Q107" t="inlineStr"/>
-      <c r="R107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -6711,14 +5864,6 @@
       <c r="J108" t="b">
         <v>0</v>
       </c>
-      <c r="K108" t="inlineStr"/>
-      <c r="L108" t="inlineStr"/>
-      <c r="M108" t="inlineStr"/>
-      <c r="N108" t="inlineStr"/>
-      <c r="O108" t="inlineStr"/>
-      <c r="P108" t="inlineStr"/>
-      <c r="Q108" t="inlineStr"/>
-      <c r="R108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -6769,14 +5914,6 @@
       <c r="J109" t="b">
         <v>0</v>
       </c>
-      <c r="K109" t="inlineStr"/>
-      <c r="L109" t="inlineStr"/>
-      <c r="M109" t="inlineStr"/>
-      <c r="N109" t="inlineStr"/>
-      <c r="O109" t="inlineStr"/>
-      <c r="P109" t="inlineStr"/>
-      <c r="Q109" t="inlineStr"/>
-      <c r="R109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -6827,14 +5964,6 @@
       <c r="J110" t="b">
         <v>0</v>
       </c>
-      <c r="K110" t="inlineStr"/>
-      <c r="L110" t="inlineStr"/>
-      <c r="M110" t="inlineStr"/>
-      <c r="N110" t="inlineStr"/>
-      <c r="O110" t="inlineStr"/>
-      <c r="P110" t="inlineStr"/>
-      <c r="Q110" t="inlineStr"/>
-      <c r="R110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -6885,14 +6014,6 @@
       <c r="J111" t="b">
         <v>0</v>
       </c>
-      <c r="K111" t="inlineStr"/>
-      <c r="L111" t="inlineStr"/>
-      <c r="M111" t="inlineStr"/>
-      <c r="N111" t="inlineStr"/>
-      <c r="O111" t="inlineStr"/>
-      <c r="P111" t="inlineStr"/>
-      <c r="Q111" t="inlineStr"/>
-      <c r="R111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -6943,14 +6064,6 @@
       <c r="J112" t="b">
         <v>0</v>
       </c>
-      <c r="K112" t="inlineStr"/>
-      <c r="L112" t="inlineStr"/>
-      <c r="M112" t="inlineStr"/>
-      <c r="N112" t="inlineStr"/>
-      <c r="O112" t="inlineStr"/>
-      <c r="P112" t="inlineStr"/>
-      <c r="Q112" t="inlineStr"/>
-      <c r="R112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -6975,7 +6088,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Matt Johnson - Cust said Gaz was patient and cheerful even with a toddler screaming in the background. Appreciated the kindness.</t>
+          <t>[REDACTED_NAME] - Cust said Gaz was patient and cheerful even with a toddler screaming in the background. Appreciated the kindness.</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -7001,14 +6114,6 @@
       <c r="J113" t="b">
         <v>0</v>
       </c>
-      <c r="K113" t="inlineStr"/>
-      <c r="L113" t="inlineStr"/>
-      <c r="M113" t="inlineStr"/>
-      <c r="N113" t="inlineStr"/>
-      <c r="O113" t="inlineStr"/>
-      <c r="P113" t="inlineStr"/>
-      <c r="Q113" t="inlineStr"/>
-      <c r="R113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -7059,14 +6164,6 @@
       <c r="J114" t="b">
         <v>0</v>
       </c>
-      <c r="K114" t="inlineStr"/>
-      <c r="L114" t="inlineStr"/>
-      <c r="M114" t="inlineStr"/>
-      <c r="N114" t="inlineStr"/>
-      <c r="O114" t="inlineStr"/>
-      <c r="P114" t="inlineStr"/>
-      <c r="Q114" t="inlineStr"/>
-      <c r="R114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -7117,14 +6214,6 @@
       <c r="J115" t="b">
         <v>0</v>
       </c>
-      <c r="K115" t="inlineStr"/>
-      <c r="L115" t="inlineStr"/>
-      <c r="M115" t="inlineStr"/>
-      <c r="N115" t="inlineStr"/>
-      <c r="O115" t="inlineStr"/>
-      <c r="P115" t="inlineStr"/>
-      <c r="Q115" t="inlineStr"/>
-      <c r="R115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -7175,14 +6264,6 @@
       <c r="J116" t="b">
         <v>0</v>
       </c>
-      <c r="K116" t="inlineStr"/>
-      <c r="L116" t="inlineStr"/>
-      <c r="M116" t="inlineStr"/>
-      <c r="N116" t="inlineStr"/>
-      <c r="O116" t="inlineStr"/>
-      <c r="P116" t="inlineStr"/>
-      <c r="Q116" t="inlineStr"/>
-      <c r="R116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -7207,7 +6288,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Wendy Sykes - Said not a long wait at all, which with three kids in the waiting room was a blessing.</t>
+          <t>[REDACTED_NAME] - Said not a long wait at all, which with three kids in the waiting room was a blessing.</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -7227,20 +6308,12 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>Wendy Sykes noted quick service turnaround with three children in waiting area.</t>
+          <t>[REDACTED_NAME] noted quick service turnaround with three children in waiting area.</t>
         </is>
       </c>
       <c r="J117" t="b">
         <v>0</v>
       </c>
-      <c r="K117" t="inlineStr"/>
-      <c r="L117" t="inlineStr"/>
-      <c r="M117" t="inlineStr"/>
-      <c r="N117" t="inlineStr"/>
-      <c r="O117" t="inlineStr"/>
-      <c r="P117" t="inlineStr"/>
-      <c r="Q117" t="inlineStr"/>
-      <c r="R117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -7291,14 +6364,6 @@
       <c r="J118" t="b">
         <v>0</v>
       </c>
-      <c r="K118" t="inlineStr"/>
-      <c r="L118" t="inlineStr"/>
-      <c r="M118" t="inlineStr"/>
-      <c r="N118" t="inlineStr"/>
-      <c r="O118" t="inlineStr"/>
-      <c r="P118" t="inlineStr"/>
-      <c r="Q118" t="inlineStr"/>
-      <c r="R118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -7349,14 +6414,6 @@
       <c r="J119" t="b">
         <v>0</v>
       </c>
-      <c r="K119" t="inlineStr"/>
-      <c r="L119" t="inlineStr"/>
-      <c r="M119" t="inlineStr"/>
-      <c r="N119" t="inlineStr"/>
-      <c r="O119" t="inlineStr"/>
-      <c r="P119" t="inlineStr"/>
-      <c r="Q119" t="inlineStr"/>
-      <c r="R119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -7407,14 +6464,6 @@
       <c r="J120" t="b">
         <v>0</v>
       </c>
-      <c r="K120" t="inlineStr"/>
-      <c r="L120" t="inlineStr"/>
-      <c r="M120" t="inlineStr"/>
-      <c r="N120" t="inlineStr"/>
-      <c r="O120" t="inlineStr"/>
-      <c r="P120" t="inlineStr"/>
-      <c r="Q120" t="inlineStr"/>
-      <c r="R120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -7465,14 +6514,6 @@
       <c r="J121" t="b">
         <v>0</v>
       </c>
-      <c r="K121" t="inlineStr"/>
-      <c r="L121" t="inlineStr"/>
-      <c r="M121" t="inlineStr"/>
-      <c r="N121" t="inlineStr"/>
-      <c r="O121" t="inlineStr"/>
-      <c r="P121" t="inlineStr"/>
-      <c r="Q121" t="inlineStr"/>
-      <c r="R121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -7523,14 +6564,6 @@
       <c r="J122" t="b">
         <v>0</v>
       </c>
-      <c r="K122" t="inlineStr"/>
-      <c r="L122" t="inlineStr"/>
-      <c r="M122" t="inlineStr"/>
-      <c r="N122" t="inlineStr"/>
-      <c r="O122" t="inlineStr"/>
-      <c r="P122" t="inlineStr"/>
-      <c r="Q122" t="inlineStr"/>
-      <c r="R122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -7581,14 +6614,6 @@
       <c r="J123" t="b">
         <v>0</v>
       </c>
-      <c r="K123" t="inlineStr"/>
-      <c r="L123" t="inlineStr"/>
-      <c r="M123" t="inlineStr"/>
-      <c r="N123" t="inlineStr"/>
-      <c r="O123" t="inlineStr"/>
-      <c r="P123" t="inlineStr"/>
-      <c r="Q123" t="inlineStr"/>
-      <c r="R123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -7639,14 +6664,6 @@
       <c r="J124" t="b">
         <v>0</v>
       </c>
-      <c r="K124" t="inlineStr"/>
-      <c r="L124" t="inlineStr"/>
-      <c r="M124" t="inlineStr"/>
-      <c r="N124" t="inlineStr"/>
-      <c r="O124" t="inlineStr"/>
-      <c r="P124" t="inlineStr"/>
-      <c r="Q124" t="inlineStr"/>
-      <c r="R124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -7697,14 +6714,6 @@
       <c r="J125" t="b">
         <v>0</v>
       </c>
-      <c r="K125" t="inlineStr"/>
-      <c r="L125" t="inlineStr"/>
-      <c r="M125" t="inlineStr"/>
-      <c r="N125" t="inlineStr"/>
-      <c r="O125" t="inlineStr"/>
-      <c r="P125" t="inlineStr"/>
-      <c r="Q125" t="inlineStr"/>
-      <c r="R125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -7755,14 +6764,6 @@
       <c r="J126" t="b">
         <v>0</v>
       </c>
-      <c r="K126" t="inlineStr"/>
-      <c r="L126" t="inlineStr"/>
-      <c r="M126" t="inlineStr"/>
-      <c r="N126" t="inlineStr"/>
-      <c r="O126" t="inlineStr"/>
-      <c r="P126" t="inlineStr"/>
-      <c r="Q126" t="inlineStr"/>
-      <c r="R126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -7813,14 +6814,6 @@
       <c r="J127" t="b">
         <v>0</v>
       </c>
-      <c r="K127" t="inlineStr"/>
-      <c r="L127" t="inlineStr"/>
-      <c r="M127" t="inlineStr"/>
-      <c r="N127" t="inlineStr"/>
-      <c r="O127" t="inlineStr"/>
-      <c r="P127" t="inlineStr"/>
-      <c r="Q127" t="inlineStr"/>
-      <c r="R127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -7871,14 +6864,6 @@
       <c r="J128" t="b">
         <v>0</v>
       </c>
-      <c r="K128" t="inlineStr"/>
-      <c r="L128" t="inlineStr"/>
-      <c r="M128" t="inlineStr"/>
-      <c r="N128" t="inlineStr"/>
-      <c r="O128" t="inlineStr"/>
-      <c r="P128" t="inlineStr"/>
-      <c r="Q128" t="inlineStr"/>
-      <c r="R128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -7929,14 +6914,6 @@
       <c r="J129" t="b">
         <v>0</v>
       </c>
-      <c r="K129" t="inlineStr"/>
-      <c r="L129" t="inlineStr"/>
-      <c r="M129" t="inlineStr"/>
-      <c r="N129" t="inlineStr"/>
-      <c r="O129" t="inlineStr"/>
-      <c r="P129" t="inlineStr"/>
-      <c r="Q129" t="inlineStr"/>
-      <c r="R129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -7987,14 +6964,6 @@
       <c r="J130" t="b">
         <v>0</v>
       </c>
-      <c r="K130" t="inlineStr"/>
-      <c r="L130" t="inlineStr"/>
-      <c r="M130" t="inlineStr"/>
-      <c r="N130" t="inlineStr"/>
-      <c r="O130" t="inlineStr"/>
-      <c r="P130" t="inlineStr"/>
-      <c r="Q130" t="inlineStr"/>
-      <c r="R130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -8045,14 +7014,6 @@
       <c r="J131" t="b">
         <v>0</v>
       </c>
-      <c r="K131" t="inlineStr"/>
-      <c r="L131" t="inlineStr"/>
-      <c r="M131" t="inlineStr"/>
-      <c r="N131" t="inlineStr"/>
-      <c r="O131" t="inlineStr"/>
-      <c r="P131" t="inlineStr"/>
-      <c r="Q131" t="inlineStr"/>
-      <c r="R131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -8103,14 +7064,6 @@
       <c r="J132" t="b">
         <v>0</v>
       </c>
-      <c r="K132" t="inlineStr"/>
-      <c r="L132" t="inlineStr"/>
-      <c r="M132" t="inlineStr"/>
-      <c r="N132" t="inlineStr"/>
-      <c r="O132" t="inlineStr"/>
-      <c r="P132" t="inlineStr"/>
-      <c r="Q132" t="inlineStr"/>
-      <c r="R132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -8161,14 +7114,6 @@
       <c r="J133" t="b">
         <v>0</v>
       </c>
-      <c r="K133" t="inlineStr"/>
-      <c r="L133" t="inlineStr"/>
-      <c r="M133" t="inlineStr"/>
-      <c r="N133" t="inlineStr"/>
-      <c r="O133" t="inlineStr"/>
-      <c r="P133" t="inlineStr"/>
-      <c r="Q133" t="inlineStr"/>
-      <c r="R133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -8219,14 +7164,6 @@
       <c r="J134" t="b">
         <v>0</v>
       </c>
-      <c r="K134" t="inlineStr"/>
-      <c r="L134" t="inlineStr"/>
-      <c r="M134" t="inlineStr"/>
-      <c r="N134" t="inlineStr"/>
-      <c r="O134" t="inlineStr"/>
-      <c r="P134" t="inlineStr"/>
-      <c r="Q134" t="inlineStr"/>
-      <c r="R134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -8277,14 +7214,6 @@
       <c r="J135" t="b">
         <v>0</v>
       </c>
-      <c r="K135" t="inlineStr"/>
-      <c r="L135" t="inlineStr"/>
-      <c r="M135" t="inlineStr"/>
-      <c r="N135" t="inlineStr"/>
-      <c r="O135" t="inlineStr"/>
-      <c r="P135" t="inlineStr"/>
-      <c r="Q135" t="inlineStr"/>
-      <c r="R135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -8335,14 +7264,6 @@
       <c r="J136" t="b">
         <v>0</v>
       </c>
-      <c r="K136" t="inlineStr"/>
-      <c r="L136" t="inlineStr"/>
-      <c r="M136" t="inlineStr"/>
-      <c r="N136" t="inlineStr"/>
-      <c r="O136" t="inlineStr"/>
-      <c r="P136" t="inlineStr"/>
-      <c r="Q136" t="inlineStr"/>
-      <c r="R136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -8393,14 +7314,6 @@
       <c r="J137" t="b">
         <v>0</v>
       </c>
-      <c r="K137" t="inlineStr"/>
-      <c r="L137" t="inlineStr"/>
-      <c r="M137" t="inlineStr"/>
-      <c r="N137" t="inlineStr"/>
-      <c r="O137" t="inlineStr"/>
-      <c r="P137" t="inlineStr"/>
-      <c r="Q137" t="inlineStr"/>
-      <c r="R137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -8451,14 +7364,6 @@
       <c r="J138" t="b">
         <v>0</v>
       </c>
-      <c r="K138" t="inlineStr"/>
-      <c r="L138" t="inlineStr"/>
-      <c r="M138" t="inlineStr"/>
-      <c r="N138" t="inlineStr"/>
-      <c r="O138" t="inlineStr"/>
-      <c r="P138" t="inlineStr"/>
-      <c r="Q138" t="inlineStr"/>
-      <c r="R138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -8509,14 +7414,6 @@
       <c r="J139" t="b">
         <v>0</v>
       </c>
-      <c r="K139" t="inlineStr"/>
-      <c r="L139" t="inlineStr"/>
-      <c r="M139" t="inlineStr"/>
-      <c r="N139" t="inlineStr"/>
-      <c r="O139" t="inlineStr"/>
-      <c r="P139" t="inlineStr"/>
-      <c r="Q139" t="inlineStr"/>
-      <c r="R139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -8567,14 +7464,6 @@
       <c r="J140" t="b">
         <v>0</v>
       </c>
-      <c r="K140" t="inlineStr"/>
-      <c r="L140" t="inlineStr"/>
-      <c r="M140" t="inlineStr"/>
-      <c r="N140" t="inlineStr"/>
-      <c r="O140" t="inlineStr"/>
-      <c r="P140" t="inlineStr"/>
-      <c r="Q140" t="inlineStr"/>
-      <c r="R140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -8625,14 +7514,6 @@
       <c r="J141" t="b">
         <v>0</v>
       </c>
-      <c r="K141" t="inlineStr"/>
-      <c r="L141" t="inlineStr"/>
-      <c r="M141" t="inlineStr"/>
-      <c r="N141" t="inlineStr"/>
-      <c r="O141" t="inlineStr"/>
-      <c r="P141" t="inlineStr"/>
-      <c r="Q141" t="inlineStr"/>
-      <c r="R141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -8683,14 +7564,6 @@
       <c r="J142" t="b">
         <v>0</v>
       </c>
-      <c r="K142" t="inlineStr"/>
-      <c r="L142" t="inlineStr"/>
-      <c r="M142" t="inlineStr"/>
-      <c r="N142" t="inlineStr"/>
-      <c r="O142" t="inlineStr"/>
-      <c r="P142" t="inlineStr"/>
-      <c r="Q142" t="inlineStr"/>
-      <c r="R142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -8741,14 +7614,6 @@
       <c r="J143" t="b">
         <v>0</v>
       </c>
-      <c r="K143" t="inlineStr"/>
-      <c r="L143" t="inlineStr"/>
-      <c r="M143" t="inlineStr"/>
-      <c r="N143" t="inlineStr"/>
-      <c r="O143" t="inlineStr"/>
-      <c r="P143" t="inlineStr"/>
-      <c r="Q143" t="inlineStr"/>
-      <c r="R143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -8799,14 +7664,6 @@
       <c r="J144" t="b">
         <v>0</v>
       </c>
-      <c r="K144" t="inlineStr"/>
-      <c r="L144" t="inlineStr"/>
-      <c r="M144" t="inlineStr"/>
-      <c r="N144" t="inlineStr"/>
-      <c r="O144" t="inlineStr"/>
-      <c r="P144" t="inlineStr"/>
-      <c r="Q144" t="inlineStr"/>
-      <c r="R144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -8857,14 +7714,6 @@
       <c r="J145" t="b">
         <v>0</v>
       </c>
-      <c r="K145" t="inlineStr"/>
-      <c r="L145" t="inlineStr"/>
-      <c r="M145" t="inlineStr"/>
-      <c r="N145" t="inlineStr"/>
-      <c r="O145" t="inlineStr"/>
-      <c r="P145" t="inlineStr"/>
-      <c r="Q145" t="inlineStr"/>
-      <c r="R145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -8915,14 +7764,6 @@
       <c r="J146" t="b">
         <v>0</v>
       </c>
-      <c r="K146" t="inlineStr"/>
-      <c r="L146" t="inlineStr"/>
-      <c r="M146" t="inlineStr"/>
-      <c r="N146" t="inlineStr"/>
-      <c r="O146" t="inlineStr"/>
-      <c r="P146" t="inlineStr"/>
-      <c r="Q146" t="inlineStr"/>
-      <c r="R146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -8973,14 +7814,6 @@
       <c r="J147" t="b">
         <v>0</v>
       </c>
-      <c r="K147" t="inlineStr"/>
-      <c r="L147" t="inlineStr"/>
-      <c r="M147" t="inlineStr"/>
-      <c r="N147" t="inlineStr"/>
-      <c r="O147" t="inlineStr"/>
-      <c r="P147" t="inlineStr"/>
-      <c r="Q147" t="inlineStr"/>
-      <c r="R147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -9031,14 +7864,6 @@
       <c r="J148" t="b">
         <v>0</v>
       </c>
-      <c r="K148" t="inlineStr"/>
-      <c r="L148" t="inlineStr"/>
-      <c r="M148" t="inlineStr"/>
-      <c r="N148" t="inlineStr"/>
-      <c r="O148" t="inlineStr"/>
-      <c r="P148" t="inlineStr"/>
-      <c r="Q148" t="inlineStr"/>
-      <c r="R148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -9089,14 +7914,6 @@
       <c r="J149" t="b">
         <v>0</v>
       </c>
-      <c r="K149" t="inlineStr"/>
-      <c r="L149" t="inlineStr"/>
-      <c r="M149" t="inlineStr"/>
-      <c r="N149" t="inlineStr"/>
-      <c r="O149" t="inlineStr"/>
-      <c r="P149" t="inlineStr"/>
-      <c r="Q149" t="inlineStr"/>
-      <c r="R149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -9147,14 +7964,6 @@
       <c r="J150" t="b">
         <v>0</v>
       </c>
-      <c r="K150" t="inlineStr"/>
-      <c r="L150" t="inlineStr"/>
-      <c r="M150" t="inlineStr"/>
-      <c r="N150" t="inlineStr"/>
-      <c r="O150" t="inlineStr"/>
-      <c r="P150" t="inlineStr"/>
-      <c r="Q150" t="inlineStr"/>
-      <c r="R150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -9205,14 +8014,6 @@
       <c r="J151" t="b">
         <v>0</v>
       </c>
-      <c r="K151" t="inlineStr"/>
-      <c r="L151" t="inlineStr"/>
-      <c r="M151" t="inlineStr"/>
-      <c r="N151" t="inlineStr"/>
-      <c r="O151" t="inlineStr"/>
-      <c r="P151" t="inlineStr"/>
-      <c r="Q151" t="inlineStr"/>
-      <c r="R151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -9263,14 +8064,6 @@
       <c r="J152" t="b">
         <v>0</v>
       </c>
-      <c r="K152" t="inlineStr"/>
-      <c r="L152" t="inlineStr"/>
-      <c r="M152" t="inlineStr"/>
-      <c r="N152" t="inlineStr"/>
-      <c r="O152" t="inlineStr"/>
-      <c r="P152" t="inlineStr"/>
-      <c r="Q152" t="inlineStr"/>
-      <c r="R152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -9295,7 +8088,7 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Amy Dalton - Rang twice with updates, no need to call in himself. Said that's how it should be.</t>
+          <t>[REDACTED_NAME] - Rang twice with updates, no need to call in himself. Said that's how it should be.</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
@@ -9315,20 +8108,12 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>Staff member Amy Dalton provided proactive calls with updates so customer didn't need to follow up.</t>
+          <t>Staff member [REDACTED_NAME] provided proactive calls with updates so customer didn't need to follow up.</t>
         </is>
       </c>
       <c r="J153" t="b">
         <v>0</v>
       </c>
-      <c r="K153" t="inlineStr"/>
-      <c r="L153" t="inlineStr"/>
-      <c r="M153" t="inlineStr"/>
-      <c r="N153" t="inlineStr"/>
-      <c r="O153" t="inlineStr"/>
-      <c r="P153" t="inlineStr"/>
-      <c r="Q153" t="inlineStr"/>
-      <c r="R153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -9379,14 +8164,6 @@
       <c r="J154" t="b">
         <v>0</v>
       </c>
-      <c r="K154" t="inlineStr"/>
-      <c r="L154" t="inlineStr"/>
-      <c r="M154" t="inlineStr"/>
-      <c r="N154" t="inlineStr"/>
-      <c r="O154" t="inlineStr"/>
-      <c r="P154" t="inlineStr"/>
-      <c r="Q154" t="inlineStr"/>
-      <c r="R154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -9437,14 +8214,6 @@
       <c r="J155" t="b">
         <v>0</v>
       </c>
-      <c r="K155" t="inlineStr"/>
-      <c r="L155" t="inlineStr"/>
-      <c r="M155" t="inlineStr"/>
-      <c r="N155" t="inlineStr"/>
-      <c r="O155" t="inlineStr"/>
-      <c r="P155" t="inlineStr"/>
-      <c r="Q155" t="inlineStr"/>
-      <c r="R155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -9495,14 +8264,6 @@
       <c r="J156" t="b">
         <v>0</v>
       </c>
-      <c r="K156" t="inlineStr"/>
-      <c r="L156" t="inlineStr"/>
-      <c r="M156" t="inlineStr"/>
-      <c r="N156" t="inlineStr"/>
-      <c r="O156" t="inlineStr"/>
-      <c r="P156" t="inlineStr"/>
-      <c r="Q156" t="inlineStr"/>
-      <c r="R156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -9553,14 +8314,6 @@
       <c r="J157" t="b">
         <v>0</v>
       </c>
-      <c r="K157" t="inlineStr"/>
-      <c r="L157" t="inlineStr"/>
-      <c r="M157" t="inlineStr"/>
-      <c r="N157" t="inlineStr"/>
-      <c r="O157" t="inlineStr"/>
-      <c r="P157" t="inlineStr"/>
-      <c r="Q157" t="inlineStr"/>
-      <c r="R157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -9611,14 +8364,6 @@
       <c r="J158" t="b">
         <v>0</v>
       </c>
-      <c r="K158" t="inlineStr"/>
-      <c r="L158" t="inlineStr"/>
-      <c r="M158" t="inlineStr"/>
-      <c r="N158" t="inlineStr"/>
-      <c r="O158" t="inlineStr"/>
-      <c r="P158" t="inlineStr"/>
-      <c r="Q158" t="inlineStr"/>
-      <c r="R158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -9669,14 +8414,6 @@
       <c r="J159" t="b">
         <v>0</v>
       </c>
-      <c r="K159" t="inlineStr"/>
-      <c r="L159" t="inlineStr"/>
-      <c r="M159" t="inlineStr"/>
-      <c r="N159" t="inlineStr"/>
-      <c r="O159" t="inlineStr"/>
-      <c r="P159" t="inlineStr"/>
-      <c r="Q159" t="inlineStr"/>
-      <c r="R159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -9727,14 +8464,6 @@
       <c r="J160" t="b">
         <v>0</v>
       </c>
-      <c r="K160" t="inlineStr"/>
-      <c r="L160" t="inlineStr"/>
-      <c r="M160" t="inlineStr"/>
-      <c r="N160" t="inlineStr"/>
-      <c r="O160" t="inlineStr"/>
-      <c r="P160" t="inlineStr"/>
-      <c r="Q160" t="inlineStr"/>
-      <c r="R160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -9785,14 +8514,6 @@
       <c r="J161" t="b">
         <v>0</v>
       </c>
-      <c r="K161" t="inlineStr"/>
-      <c r="L161" t="inlineStr"/>
-      <c r="M161" t="inlineStr"/>
-      <c r="N161" t="inlineStr"/>
-      <c r="O161" t="inlineStr"/>
-      <c r="P161" t="inlineStr"/>
-      <c r="Q161" t="inlineStr"/>
-      <c r="R161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -9843,14 +8564,6 @@
       <c r="J162" t="b">
         <v>0</v>
       </c>
-      <c r="K162" t="inlineStr"/>
-      <c r="L162" t="inlineStr"/>
-      <c r="M162" t="inlineStr"/>
-      <c r="N162" t="inlineStr"/>
-      <c r="O162" t="inlineStr"/>
-      <c r="P162" t="inlineStr"/>
-      <c r="Q162" t="inlineStr"/>
-      <c r="R162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -9901,14 +8614,6 @@
       <c r="J163" t="b">
         <v>0</v>
       </c>
-      <c r="K163" t="inlineStr"/>
-      <c r="L163" t="inlineStr"/>
-      <c r="M163" t="inlineStr"/>
-      <c r="N163" t="inlineStr"/>
-      <c r="O163" t="inlineStr"/>
-      <c r="P163" t="inlineStr"/>
-      <c r="Q163" t="inlineStr"/>
-      <c r="R163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -9959,14 +8664,6 @@
       <c r="J164" t="b">
         <v>0</v>
       </c>
-      <c r="K164" t="inlineStr"/>
-      <c r="L164" t="inlineStr"/>
-      <c r="M164" t="inlineStr"/>
-      <c r="N164" t="inlineStr"/>
-      <c r="O164" t="inlineStr"/>
-      <c r="P164" t="inlineStr"/>
-      <c r="Q164" t="inlineStr"/>
-      <c r="R164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -10017,14 +8714,6 @@
       <c r="J165" t="b">
         <v>0</v>
       </c>
-      <c r="K165" t="inlineStr"/>
-      <c r="L165" t="inlineStr"/>
-      <c r="M165" t="inlineStr"/>
-      <c r="N165" t="inlineStr"/>
-      <c r="O165" t="inlineStr"/>
-      <c r="P165" t="inlineStr"/>
-      <c r="Q165" t="inlineStr"/>
-      <c r="R165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -10075,14 +8764,6 @@
       <c r="J166" t="b">
         <v>0</v>
       </c>
-      <c r="K166" t="inlineStr"/>
-      <c r="L166" t="inlineStr"/>
-      <c r="M166" t="inlineStr"/>
-      <c r="N166" t="inlineStr"/>
-      <c r="O166" t="inlineStr"/>
-      <c r="P166" t="inlineStr"/>
-      <c r="Q166" t="inlineStr"/>
-      <c r="R166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -10138,13 +8819,6 @@
           <t>Invoice includes charges (cleaning fee, higher parts price) not in original quote — potential financial dispute.</t>
         </is>
       </c>
-      <c r="L167" t="inlineStr"/>
-      <c r="M167" t="inlineStr"/>
-      <c r="N167" t="inlineStr"/>
-      <c r="O167" t="inlineStr"/>
-      <c r="P167" t="inlineStr"/>
-      <c r="Q167" t="inlineStr"/>
-      <c r="R167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -10195,14 +8869,6 @@
       <c r="J168" t="b">
         <v>0</v>
       </c>
-      <c r="K168" t="inlineStr"/>
-      <c r="L168" t="inlineStr"/>
-      <c r="M168" t="inlineStr"/>
-      <c r="N168" t="inlineStr"/>
-      <c r="O168" t="inlineStr"/>
-      <c r="P168" t="inlineStr"/>
-      <c r="Q168" t="inlineStr"/>
-      <c r="R168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -10253,14 +8919,6 @@
       <c r="J169" t="b">
         <v>0</v>
       </c>
-      <c r="K169" t="inlineStr"/>
-      <c r="L169" t="inlineStr"/>
-      <c r="M169" t="inlineStr"/>
-      <c r="N169" t="inlineStr"/>
-      <c r="O169" t="inlineStr"/>
-      <c r="P169" t="inlineStr"/>
-      <c r="Q169" t="inlineStr"/>
-      <c r="R169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -10311,14 +8969,6 @@
       <c r="J170" t="b">
         <v>0</v>
       </c>
-      <c r="K170" t="inlineStr"/>
-      <c r="L170" t="inlineStr"/>
-      <c r="M170" t="inlineStr"/>
-      <c r="N170" t="inlineStr"/>
-      <c r="O170" t="inlineStr"/>
-      <c r="P170" t="inlineStr"/>
-      <c r="Q170" t="inlineStr"/>
-      <c r="R170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -10374,13 +9024,6 @@
           <t>Unresolved brake light issue is a potential safety concern requiring human review.</t>
         </is>
       </c>
-      <c r="L171" t="inlineStr"/>
-      <c r="M171" t="inlineStr"/>
-      <c r="N171" t="inlineStr"/>
-      <c r="O171" t="inlineStr"/>
-      <c r="P171" t="inlineStr"/>
-      <c r="Q171" t="inlineStr"/>
-      <c r="R171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -10431,14 +9074,6 @@
       <c r="J172" t="b">
         <v>0</v>
       </c>
-      <c r="K172" t="inlineStr"/>
-      <c r="L172" t="inlineStr"/>
-      <c r="M172" t="inlineStr"/>
-      <c r="N172" t="inlineStr"/>
-      <c r="O172" t="inlineStr"/>
-      <c r="P172" t="inlineStr"/>
-      <c r="Q172" t="inlineStr"/>
-      <c r="R172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -10494,13 +9129,6 @@
           <t>Customer has been chasing for a week with no response — emails ignored and calls going to voicemail. High risk of customer loss and possible escalation.</t>
         </is>
       </c>
-      <c r="L173" t="inlineStr"/>
-      <c r="M173" t="inlineStr"/>
-      <c r="N173" t="inlineStr"/>
-      <c r="O173" t="inlineStr"/>
-      <c r="P173" t="inlineStr"/>
-      <c r="Q173" t="inlineStr"/>
-      <c r="R173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -10556,13 +9184,6 @@
           <t>Pricing discrepancy between website quote and final charge, plus recurring fault after service — potential legal/financial dispute and safety implication.</t>
         </is>
       </c>
-      <c r="L174" t="inlineStr"/>
-      <c r="M174" t="inlineStr"/>
-      <c r="N174" t="inlineStr"/>
-      <c r="O174" t="inlineStr"/>
-      <c r="P174" t="inlineStr"/>
-      <c r="Q174" t="inlineStr"/>
-      <c r="R174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -10587,7 +9208,7 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Charlotte Cahill - Sent a text from the car park asking if it was ready. No reply. Went in and they didn't know either.</t>
+          <t>[REDACTED_NAME] - Sent a text from the car park asking if it was ready. No reply. Went in and they didn't know either.</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
@@ -10613,14 +9234,6 @@
       <c r="J175" t="b">
         <v>0</v>
       </c>
-      <c r="K175" t="inlineStr"/>
-      <c r="L175" t="inlineStr"/>
-      <c r="M175" t="inlineStr"/>
-      <c r="N175" t="inlineStr"/>
-      <c r="O175" t="inlineStr"/>
-      <c r="P175" t="inlineStr"/>
-      <c r="Q175" t="inlineStr"/>
-      <c r="R175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -10671,14 +9284,6 @@
       <c r="J176" t="b">
         <v>0</v>
       </c>
-      <c r="K176" t="inlineStr"/>
-      <c r="L176" t="inlineStr"/>
-      <c r="M176" t="inlineStr"/>
-      <c r="N176" t="inlineStr"/>
-      <c r="O176" t="inlineStr"/>
-      <c r="P176" t="inlineStr"/>
-      <c r="Q176" t="inlineStr"/>
-      <c r="R176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -10729,14 +9334,6 @@
       <c r="J177" t="b">
         <v>0</v>
       </c>
-      <c r="K177" t="inlineStr"/>
-      <c r="L177" t="inlineStr"/>
-      <c r="M177" t="inlineStr"/>
-      <c r="N177" t="inlineStr"/>
-      <c r="O177" t="inlineStr"/>
-      <c r="P177" t="inlineStr"/>
-      <c r="Q177" t="inlineStr"/>
-      <c r="R177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -10792,13 +9389,6 @@
           <t>Customer has included personal contact details requesting follow-up; unexpected charges flagged by a first-time owner warrant human review.</t>
         </is>
       </c>
-      <c r="L178" t="inlineStr"/>
-      <c r="M178" t="inlineStr"/>
-      <c r="N178" t="inlineStr"/>
-      <c r="O178" t="inlineStr"/>
-      <c r="P178" t="inlineStr"/>
-      <c r="Q178" t="inlineStr"/>
-      <c r="R178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -10849,14 +9439,6 @@
       <c r="J179" t="b">
         <v>0</v>
       </c>
-      <c r="K179" t="inlineStr"/>
-      <c r="L179" t="inlineStr"/>
-      <c r="M179" t="inlineStr"/>
-      <c r="N179" t="inlineStr"/>
-      <c r="O179" t="inlineStr"/>
-      <c r="P179" t="inlineStr"/>
-      <c r="Q179" t="inlineStr"/>
-      <c r="R179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -10907,14 +9489,6 @@
       <c r="J180" t="b">
         <v>0</v>
       </c>
-      <c r="K180" t="inlineStr"/>
-      <c r="L180" t="inlineStr"/>
-      <c r="M180" t="inlineStr"/>
-      <c r="N180" t="inlineStr"/>
-      <c r="O180" t="inlineStr"/>
-      <c r="P180" t="inlineStr"/>
-      <c r="Q180" t="inlineStr"/>
-      <c r="R180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -10970,13 +9544,6 @@
           <t>Customer explicitly states they are driving at night with a non-functioning headlight — immediate safety concern.</t>
         </is>
       </c>
-      <c r="L181" t="inlineStr"/>
-      <c r="M181" t="inlineStr"/>
-      <c r="N181" t="inlineStr"/>
-      <c r="O181" t="inlineStr"/>
-      <c r="P181" t="inlineStr"/>
-      <c r="Q181" t="inlineStr"/>
-      <c r="R181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -11027,14 +9594,6 @@
       <c r="J182" t="b">
         <v>0</v>
       </c>
-      <c r="K182" t="inlineStr"/>
-      <c r="L182" t="inlineStr"/>
-      <c r="M182" t="inlineStr"/>
-      <c r="N182" t="inlineStr"/>
-      <c r="O182" t="inlineStr"/>
-      <c r="P182" t="inlineStr"/>
-      <c r="Q182" t="inlineStr"/>
-      <c r="R182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -11085,14 +9644,6 @@
       <c r="J183" t="b">
         <v>0</v>
       </c>
-      <c r="K183" t="inlineStr"/>
-      <c r="L183" t="inlineStr"/>
-      <c r="M183" t="inlineStr"/>
-      <c r="N183" t="inlineStr"/>
-      <c r="O183" t="inlineStr"/>
-      <c r="P183" t="inlineStr"/>
-      <c r="Q183" t="inlineStr"/>
-      <c r="R183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -11148,13 +9699,6 @@
           <t>Staff member named; potential discriminatory or condescending behaviour flagged by customer.</t>
         </is>
       </c>
-      <c r="L184" t="inlineStr"/>
-      <c r="M184" t="inlineStr"/>
-      <c r="N184" t="inlineStr"/>
-      <c r="O184" t="inlineStr"/>
-      <c r="P184" t="inlineStr"/>
-      <c r="Q184" t="inlineStr"/>
-      <c r="R184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -11205,14 +9749,6 @@
       <c r="J185" t="b">
         <v>0</v>
       </c>
-      <c r="K185" t="inlineStr"/>
-      <c r="L185" t="inlineStr"/>
-      <c r="M185" t="inlineStr"/>
-      <c r="N185" t="inlineStr"/>
-      <c r="O185" t="inlineStr"/>
-      <c r="P185" t="inlineStr"/>
-      <c r="Q185" t="inlineStr"/>
-      <c r="R185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -11263,14 +9799,6 @@
       <c r="J186" t="b">
         <v>0</v>
       </c>
-      <c r="K186" t="inlineStr"/>
-      <c r="L186" t="inlineStr"/>
-      <c r="M186" t="inlineStr"/>
-      <c r="N186" t="inlineStr"/>
-      <c r="O186" t="inlineStr"/>
-      <c r="P186" t="inlineStr"/>
-      <c r="Q186" t="inlineStr"/>
-      <c r="R186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -11321,14 +9849,6 @@
       <c r="J187" t="b">
         <v>0</v>
       </c>
-      <c r="K187" t="inlineStr"/>
-      <c r="L187" t="inlineStr"/>
-      <c r="M187" t="inlineStr"/>
-      <c r="N187" t="inlineStr"/>
-      <c r="O187" t="inlineStr"/>
-      <c r="P187" t="inlineStr"/>
-      <c r="Q187" t="inlineStr"/>
-      <c r="R187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -11384,13 +9904,6 @@
           <t>Customer describes an unresolved mechanical fault (clunking noise) with no response to direct email to service manager — potential safety concern and escalation warranted. Customer has provided email for follow-up.</t>
         </is>
       </c>
-      <c r="L188" t="inlineStr"/>
-      <c r="M188" t="inlineStr"/>
-      <c r="N188" t="inlineStr"/>
-      <c r="O188" t="inlineStr"/>
-      <c r="P188" t="inlineStr"/>
-      <c r="Q188" t="inlineStr"/>
-      <c r="R188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -11441,14 +9954,6 @@
       <c r="J189" t="b">
         <v>0</v>
       </c>
-      <c r="K189" t="inlineStr"/>
-      <c r="L189" t="inlineStr"/>
-      <c r="M189" t="inlineStr"/>
-      <c r="N189" t="inlineStr"/>
-      <c r="O189" t="inlineStr"/>
-      <c r="P189" t="inlineStr"/>
-      <c r="Q189" t="inlineStr"/>
-      <c r="R189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -11499,14 +10004,6 @@
       <c r="J190" t="b">
         <v>0</v>
       </c>
-      <c r="K190" t="inlineStr"/>
-      <c r="L190" t="inlineStr"/>
-      <c r="M190" t="inlineStr"/>
-      <c r="N190" t="inlineStr"/>
-      <c r="O190" t="inlineStr"/>
-      <c r="P190" t="inlineStr"/>
-      <c r="Q190" t="inlineStr"/>
-      <c r="R190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -11557,14 +10054,6 @@
       <c r="J191" t="b">
         <v>0</v>
       </c>
-      <c r="K191" t="inlineStr"/>
-      <c r="L191" t="inlineStr"/>
-      <c r="M191" t="inlineStr"/>
-      <c r="N191" t="inlineStr"/>
-      <c r="O191" t="inlineStr"/>
-      <c r="P191" t="inlineStr"/>
-      <c r="Q191" t="inlineStr"/>
-      <c r="R191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -11620,13 +10109,6 @@
           <t>Loose wheel nut after service is a critical safety concern requiring immediate human review.</t>
         </is>
       </c>
-      <c r="L192" t="inlineStr"/>
-      <c r="M192" t="inlineStr"/>
-      <c r="N192" t="inlineStr"/>
-      <c r="O192" t="inlineStr"/>
-      <c r="P192" t="inlineStr"/>
-      <c r="Q192" t="inlineStr"/>
-      <c r="R192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -11677,14 +10159,6 @@
       <c r="J193" t="b">
         <v>0</v>
       </c>
-      <c r="K193" t="inlineStr"/>
-      <c r="L193" t="inlineStr"/>
-      <c r="M193" t="inlineStr"/>
-      <c r="N193" t="inlineStr"/>
-      <c r="O193" t="inlineStr"/>
-      <c r="P193" t="inlineStr"/>
-      <c r="Q193" t="inlineStr"/>
-      <c r="R193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -11735,14 +10209,6 @@
       <c r="J194" t="b">
         <v>0</v>
       </c>
-      <c r="K194" t="inlineStr"/>
-      <c r="L194" t="inlineStr"/>
-      <c r="M194" t="inlineStr"/>
-      <c r="N194" t="inlineStr"/>
-      <c r="O194" t="inlineStr"/>
-      <c r="P194" t="inlineStr"/>
-      <c r="Q194" t="inlineStr"/>
-      <c r="R194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -11793,14 +10259,6 @@
       <c r="J195" t="b">
         <v>0</v>
       </c>
-      <c r="K195" t="inlineStr"/>
-      <c r="L195" t="inlineStr"/>
-      <c r="M195" t="inlineStr"/>
-      <c r="N195" t="inlineStr"/>
-      <c r="O195" t="inlineStr"/>
-      <c r="P195" t="inlineStr"/>
-      <c r="Q195" t="inlineStr"/>
-      <c r="R195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -11851,14 +10309,6 @@
       <c r="J196" t="b">
         <v>0</v>
       </c>
-      <c r="K196" t="inlineStr"/>
-      <c r="L196" t="inlineStr"/>
-      <c r="M196" t="inlineStr"/>
-      <c r="N196" t="inlineStr"/>
-      <c r="O196" t="inlineStr"/>
-      <c r="P196" t="inlineStr"/>
-      <c r="Q196" t="inlineStr"/>
-      <c r="R196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -11914,13 +10364,6 @@
           <t>Potentially unauthorised additional work added to bill without prior customer approval.</t>
         </is>
       </c>
-      <c r="L197" t="inlineStr"/>
-      <c r="M197" t="inlineStr"/>
-      <c r="N197" t="inlineStr"/>
-      <c r="O197" t="inlineStr"/>
-      <c r="P197" t="inlineStr"/>
-      <c r="Q197" t="inlineStr"/>
-      <c r="R197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -11971,14 +10414,6 @@
       <c r="J198" t="b">
         <v>0</v>
       </c>
-      <c r="K198" t="inlineStr"/>
-      <c r="L198" t="inlineStr"/>
-      <c r="M198" t="inlineStr"/>
-      <c r="N198" t="inlineStr"/>
-      <c r="O198" t="inlineStr"/>
-      <c r="P198" t="inlineStr"/>
-      <c r="Q198" t="inlineStr"/>
-      <c r="R198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -12029,14 +10464,6 @@
       <c r="J199" t="b">
         <v>0</v>
       </c>
-      <c r="K199" t="inlineStr"/>
-      <c r="L199" t="inlineStr"/>
-      <c r="M199" t="inlineStr"/>
-      <c r="N199" t="inlineStr"/>
-      <c r="O199" t="inlineStr"/>
-      <c r="P199" t="inlineStr"/>
-      <c r="Q199" t="inlineStr"/>
-      <c r="R199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -12092,13 +10519,6 @@
           <t>Contradictory signals — sarcastic praise mixed with genuine complaint makes intent ambiguous.</t>
         </is>
       </c>
-      <c r="L200" t="inlineStr"/>
-      <c r="M200" t="inlineStr"/>
-      <c r="N200" t="inlineStr"/>
-      <c r="O200" t="inlineStr"/>
-      <c r="P200" t="inlineStr"/>
-      <c r="Q200" t="inlineStr"/>
-      <c r="R200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -12149,14 +10569,6 @@
       <c r="J201" t="b">
         <v>0</v>
       </c>
-      <c r="K201" t="inlineStr"/>
-      <c r="L201" t="inlineStr"/>
-      <c r="M201" t="inlineStr"/>
-      <c r="N201" t="inlineStr"/>
-      <c r="O201" t="inlineStr"/>
-      <c r="P201" t="inlineStr"/>
-      <c r="Q201" t="inlineStr"/>
-      <c r="R201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -12212,13 +10624,6 @@
           <t>Customer disputes pricing and claims unauthorised extras were added; callback requested — potential financial dispute.</t>
         </is>
       </c>
-      <c r="L202" t="inlineStr"/>
-      <c r="M202" t="inlineStr"/>
-      <c r="N202" t="inlineStr"/>
-      <c r="O202" t="inlineStr"/>
-      <c r="P202" t="inlineStr"/>
-      <c r="Q202" t="inlineStr"/>
-      <c r="R202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -12269,14 +10674,6 @@
       <c r="J203" t="b">
         <v>0</v>
       </c>
-      <c r="K203" t="inlineStr"/>
-      <c r="L203" t="inlineStr"/>
-      <c r="M203" t="inlineStr"/>
-      <c r="N203" t="inlineStr"/>
-      <c r="O203" t="inlineStr"/>
-      <c r="P203" t="inlineStr"/>
-      <c r="Q203" t="inlineStr"/>
-      <c r="R203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -12327,14 +10724,6 @@
       <c r="J204" t="b">
         <v>0</v>
       </c>
-      <c r="K204" t="inlineStr"/>
-      <c r="L204" t="inlineStr"/>
-      <c r="M204" t="inlineStr"/>
-      <c r="N204" t="inlineStr"/>
-      <c r="O204" t="inlineStr"/>
-      <c r="P204" t="inlineStr"/>
-      <c r="Q204" t="inlineStr"/>
-      <c r="R204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -12385,14 +10774,6 @@
       <c r="J205" t="b">
         <v>0</v>
       </c>
-      <c r="K205" t="inlineStr"/>
-      <c r="L205" t="inlineStr"/>
-      <c r="M205" t="inlineStr"/>
-      <c r="N205" t="inlineStr"/>
-      <c r="O205" t="inlineStr"/>
-      <c r="P205" t="inlineStr"/>
-      <c r="Q205" t="inlineStr"/>
-      <c r="R205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -12448,13 +10829,6 @@
           <t>Long-term loyal customer (4 cars, 20+ years) reporting dismissive named staff member; high churn risk.</t>
         </is>
       </c>
-      <c r="L206" t="inlineStr"/>
-      <c r="M206" t="inlineStr"/>
-      <c r="N206" t="inlineStr"/>
-      <c r="O206" t="inlineStr"/>
-      <c r="P206" t="inlineStr"/>
-      <c r="Q206" t="inlineStr"/>
-      <c r="R206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -12505,14 +10879,6 @@
       <c r="J207" t="b">
         <v>0</v>
       </c>
-      <c r="K207" t="inlineStr"/>
-      <c r="L207" t="inlineStr"/>
-      <c r="M207" t="inlineStr"/>
-      <c r="N207" t="inlineStr"/>
-      <c r="O207" t="inlineStr"/>
-      <c r="P207" t="inlineStr"/>
-      <c r="Q207" t="inlineStr"/>
-      <c r="R207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -12563,14 +10929,6 @@
       <c r="J208" t="b">
         <v>0</v>
       </c>
-      <c r="K208" t="inlineStr"/>
-      <c r="L208" t="inlineStr"/>
-      <c r="M208" t="inlineStr"/>
-      <c r="N208" t="inlineStr"/>
-      <c r="O208" t="inlineStr"/>
-      <c r="P208" t="inlineStr"/>
-      <c r="Q208" t="inlineStr"/>
-      <c r="R208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -12626,13 +10984,6 @@
           <t>Customer explicitly states an unauthorised charge was applied and is requesting a refund — potential financial/legal dispute</t>
         </is>
       </c>
-      <c r="L209" t="inlineStr"/>
-      <c r="M209" t="inlineStr"/>
-      <c r="N209" t="inlineStr"/>
-      <c r="O209" t="inlineStr"/>
-      <c r="P209" t="inlineStr"/>
-      <c r="Q209" t="inlineStr"/>
-      <c r="R209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -12683,14 +11034,6 @@
       <c r="J210" t="b">
         <v>0</v>
       </c>
-      <c r="K210" t="inlineStr"/>
-      <c r="L210" t="inlineStr"/>
-      <c r="M210" t="inlineStr"/>
-      <c r="N210" t="inlineStr"/>
-      <c r="O210" t="inlineStr"/>
-      <c r="P210" t="inlineStr"/>
-      <c r="Q210" t="inlineStr"/>
-      <c r="R210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -12746,13 +11089,6 @@
           <t>Fleet handover failure across eight vehicles — high business impact and potential contractual implications.</t>
         </is>
       </c>
-      <c r="L211" t="inlineStr"/>
-      <c r="M211" t="inlineStr"/>
-      <c r="N211" t="inlineStr"/>
-      <c r="O211" t="inlineStr"/>
-      <c r="P211" t="inlineStr"/>
-      <c r="Q211" t="inlineStr"/>
-      <c r="R211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -12808,13 +11144,6 @@
           <t>Significant delay far exceeding the advised timeframe — customer has formally registered a concern suggesting potential escalation or dispute.</t>
         </is>
       </c>
-      <c r="L212" t="inlineStr"/>
-      <c r="M212" t="inlineStr"/>
-      <c r="N212" t="inlineStr"/>
-      <c r="O212" t="inlineStr"/>
-      <c r="P212" t="inlineStr"/>
-      <c r="Q212" t="inlineStr"/>
-      <c r="R212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -12870,13 +11199,6 @@
           <t>Safety concern — impaired visibility due to non-functioning demister in winter conditions with children in the vehicle.</t>
         </is>
       </c>
-      <c r="L213" t="inlineStr"/>
-      <c r="M213" t="inlineStr"/>
-      <c r="N213" t="inlineStr"/>
-      <c r="O213" t="inlineStr"/>
-      <c r="P213" t="inlineStr"/>
-      <c r="Q213" t="inlineStr"/>
-      <c r="R213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -12932,13 +11254,6 @@
           <t>Customer has requested a callback and describes physical site conditions that may constitute a safety hazard for visitors.</t>
         </is>
       </c>
-      <c r="L214" t="inlineStr"/>
-      <c r="M214" t="inlineStr"/>
-      <c r="N214" t="inlineStr"/>
-      <c r="O214" t="inlineStr"/>
-      <c r="P214" t="inlineStr"/>
-      <c r="Q214" t="inlineStr"/>
-      <c r="R214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -12989,14 +11304,6 @@
       <c r="J215" t="b">
         <v>0</v>
       </c>
-      <c r="K215" t="inlineStr"/>
-      <c r="L215" t="inlineStr"/>
-      <c r="M215" t="inlineStr"/>
-      <c r="N215" t="inlineStr"/>
-      <c r="O215" t="inlineStr"/>
-      <c r="P215" t="inlineStr"/>
-      <c r="Q215" t="inlineStr"/>
-      <c r="R215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -13052,13 +11359,6 @@
           <t>No brake pads available for a vehicle sold by the dealership is a safety-adjacent parts issue — customer may have driven with compromised brakes while waiting.</t>
         </is>
       </c>
-      <c r="L216" t="inlineStr"/>
-      <c r="M216" t="inlineStr"/>
-      <c r="N216" t="inlineStr"/>
-      <c r="O216" t="inlineStr"/>
-      <c r="P216" t="inlineStr"/>
-      <c r="Q216" t="inlineStr"/>
-      <c r="R216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -13109,14 +11409,6 @@
       <c r="J217" t="b">
         <v>0</v>
       </c>
-      <c r="K217" t="inlineStr"/>
-      <c r="L217" t="inlineStr"/>
-      <c r="M217" t="inlineStr"/>
-      <c r="N217" t="inlineStr"/>
-      <c r="O217" t="inlineStr"/>
-      <c r="P217" t="inlineStr"/>
-      <c r="Q217" t="inlineStr"/>
-      <c r="R217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -13167,14 +11459,6 @@
       <c r="J218" t="b">
         <v>0</v>
       </c>
-      <c r="K218" t="inlineStr"/>
-      <c r="L218" t="inlineStr"/>
-      <c r="M218" t="inlineStr"/>
-      <c r="N218" t="inlineStr"/>
-      <c r="O218" t="inlineStr"/>
-      <c r="P218" t="inlineStr"/>
-      <c r="Q218" t="inlineStr"/>
-      <c r="R218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -13225,14 +11509,6 @@
       <c r="J219" t="b">
         <v>0</v>
       </c>
-      <c r="K219" t="inlineStr"/>
-      <c r="L219" t="inlineStr"/>
-      <c r="M219" t="inlineStr"/>
-      <c r="N219" t="inlineStr"/>
-      <c r="O219" t="inlineStr"/>
-      <c r="P219" t="inlineStr"/>
-      <c r="Q219" t="inlineStr"/>
-      <c r="R219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -13257,7 +11533,7 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Margaret Alexiou - Moved here a month ago and has no idea who to ask for. Said she rang the number on the booking sheet and it just rolled to a generic message, so she's not sure anyone knows her car is there.</t>
+          <t>[REDACTED_NAME] - Moved here a month ago and has no idea who to ask for. Said she rang the number on the booking sheet and it just rolled to a generic message, so she's not sure anyone knows her car is there.</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
@@ -13277,7 +11553,7 @@
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t>New customer Margaret Alexiou could not reach the dealership after dropping off her vehicle and fears staff don't know her car is there.</t>
+          <t>New customer [REDACTED_NAME] could not reach the dealership after dropping off her vehicle and fears staff don't know her car is there.</t>
         </is>
       </c>
       <c r="J220" t="b">
@@ -13288,13 +11564,6 @@
           <t>Customer is uncertain whether the dealership knows her vehicle is on site — potential lost or untracked vehicle in the system.</t>
         </is>
       </c>
-      <c r="L220" t="inlineStr"/>
-      <c r="M220" t="inlineStr"/>
-      <c r="N220" t="inlineStr"/>
-      <c r="O220" t="inlineStr"/>
-      <c r="P220" t="inlineStr"/>
-      <c r="Q220" t="inlineStr"/>
-      <c r="R220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -13345,14 +11614,6 @@
       <c r="J221" t="b">
         <v>0</v>
       </c>
-      <c r="K221" t="inlineStr"/>
-      <c r="L221" t="inlineStr"/>
-      <c r="M221" t="inlineStr"/>
-      <c r="N221" t="inlineStr"/>
-      <c r="O221" t="inlineStr"/>
-      <c r="P221" t="inlineStr"/>
-      <c r="Q221" t="inlineStr"/>
-      <c r="R221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -13403,14 +11664,6 @@
       <c r="J222" t="b">
         <v>0</v>
       </c>
-      <c r="K222" t="inlineStr"/>
-      <c r="L222" t="inlineStr"/>
-      <c r="M222" t="inlineStr"/>
-      <c r="N222" t="inlineStr"/>
-      <c r="O222" t="inlineStr"/>
-      <c r="P222" t="inlineStr"/>
-      <c r="Q222" t="inlineStr"/>
-      <c r="R222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -13461,14 +11714,6 @@
       <c r="J223" t="b">
         <v>0</v>
       </c>
-      <c r="K223" t="inlineStr"/>
-      <c r="L223" t="inlineStr"/>
-      <c r="M223" t="inlineStr"/>
-      <c r="N223" t="inlineStr"/>
-      <c r="O223" t="inlineStr"/>
-      <c r="P223" t="inlineStr"/>
-      <c r="Q223" t="inlineStr"/>
-      <c r="R223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -13519,14 +11764,6 @@
       <c r="J224" t="b">
         <v>0</v>
       </c>
-      <c r="K224" t="inlineStr"/>
-      <c r="L224" t="inlineStr"/>
-      <c r="M224" t="inlineStr"/>
-      <c r="N224" t="inlineStr"/>
-      <c r="O224" t="inlineStr"/>
-      <c r="P224" t="inlineStr"/>
-      <c r="Q224" t="inlineStr"/>
-      <c r="R224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -13577,14 +11814,6 @@
       <c r="J225" t="b">
         <v>0</v>
       </c>
-      <c r="K225" t="inlineStr"/>
-      <c r="L225" t="inlineStr"/>
-      <c r="M225" t="inlineStr"/>
-      <c r="N225" t="inlineStr"/>
-      <c r="O225" t="inlineStr"/>
-      <c r="P225" t="inlineStr"/>
-      <c r="Q225" t="inlineStr"/>
-      <c r="R225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -13635,14 +11864,6 @@
       <c r="J226" t="b">
         <v>0</v>
       </c>
-      <c r="K226" t="inlineStr"/>
-      <c r="L226" t="inlineStr"/>
-      <c r="M226" t="inlineStr"/>
-      <c r="N226" t="inlineStr"/>
-      <c r="O226" t="inlineStr"/>
-      <c r="P226" t="inlineStr"/>
-      <c r="Q226" t="inlineStr"/>
-      <c r="R226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -13698,13 +11919,6 @@
           <t>Potential charge for unnecessary diagnostic scan — customer indicates the fault cause (loose gas cap) was already known. May constitute an unfair charge under Australian Consumer Law.</t>
         </is>
       </c>
-      <c r="L227" t="inlineStr"/>
-      <c r="M227" t="inlineStr"/>
-      <c r="N227" t="inlineStr"/>
-      <c r="O227" t="inlineStr"/>
-      <c r="P227" t="inlineStr"/>
-      <c r="Q227" t="inlineStr"/>
-      <c r="R227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -13755,14 +11969,6 @@
       <c r="J228" t="b">
         <v>0</v>
       </c>
-      <c r="K228" t="inlineStr"/>
-      <c r="L228" t="inlineStr"/>
-      <c r="M228" t="inlineStr"/>
-      <c r="N228" t="inlineStr"/>
-      <c r="O228" t="inlineStr"/>
-      <c r="P228" t="inlineStr"/>
-      <c r="Q228" t="inlineStr"/>
-      <c r="R228" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -13813,14 +12019,6 @@
       <c r="J229" t="b">
         <v>0</v>
       </c>
-      <c r="K229" t="inlineStr"/>
-      <c r="L229" t="inlineStr"/>
-      <c r="M229" t="inlineStr"/>
-      <c r="N229" t="inlineStr"/>
-      <c r="O229" t="inlineStr"/>
-      <c r="P229" t="inlineStr"/>
-      <c r="Q229" t="inlineStr"/>
-      <c r="R229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -13876,13 +12074,6 @@
           <t>Potential safety hazard — strong chemical smell and fogged windows in waiting area may indicate exposure to harmful fumes</t>
         </is>
       </c>
-      <c r="L230" t="inlineStr"/>
-      <c r="M230" t="inlineStr"/>
-      <c r="N230" t="inlineStr"/>
-      <c r="O230" t="inlineStr"/>
-      <c r="P230" t="inlineStr"/>
-      <c r="Q230" t="inlineStr"/>
-      <c r="R230" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -13933,14 +12124,6 @@
       <c r="J231" t="b">
         <v>0</v>
       </c>
-      <c r="K231" t="inlineStr"/>
-      <c r="L231" t="inlineStr"/>
-      <c r="M231" t="inlineStr"/>
-      <c r="N231" t="inlineStr"/>
-      <c r="O231" t="inlineStr"/>
-      <c r="P231" t="inlineStr"/>
-      <c r="Q231" t="inlineStr"/>
-      <c r="R231" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -13991,14 +12174,6 @@
       <c r="J232" t="b">
         <v>0</v>
       </c>
-      <c r="K232" t="inlineStr"/>
-      <c r="L232" t="inlineStr"/>
-      <c r="M232" t="inlineStr"/>
-      <c r="N232" t="inlineStr"/>
-      <c r="O232" t="inlineStr"/>
-      <c r="P232" t="inlineStr"/>
-      <c r="Q232" t="inlineStr"/>
-      <c r="R232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -14049,14 +12224,6 @@
       <c r="J233" t="b">
         <v>0</v>
       </c>
-      <c r="K233" t="inlineStr"/>
-      <c r="L233" t="inlineStr"/>
-      <c r="M233" t="inlineStr"/>
-      <c r="N233" t="inlineStr"/>
-      <c r="O233" t="inlineStr"/>
-      <c r="P233" t="inlineStr"/>
-      <c r="Q233" t="inlineStr"/>
-      <c r="R233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -14107,14 +12274,6 @@
       <c r="J234" t="b">
         <v>0</v>
       </c>
-      <c r="K234" t="inlineStr"/>
-      <c r="L234" t="inlineStr"/>
-      <c r="M234" t="inlineStr"/>
-      <c r="N234" t="inlineStr"/>
-      <c r="O234" t="inlineStr"/>
-      <c r="P234" t="inlineStr"/>
-      <c r="Q234" t="inlineStr"/>
-      <c r="R234" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -14165,14 +12324,6 @@
       <c r="J235" t="b">
         <v>0</v>
       </c>
-      <c r="K235" t="inlineStr"/>
-      <c r="L235" t="inlineStr"/>
-      <c r="M235" t="inlineStr"/>
-      <c r="N235" t="inlineStr"/>
-      <c r="O235" t="inlineStr"/>
-      <c r="P235" t="inlineStr"/>
-      <c r="Q235" t="inlineStr"/>
-      <c r="R235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -14223,14 +12374,6 @@
       <c r="J236" t="b">
         <v>0</v>
       </c>
-      <c r="K236" t="inlineStr"/>
-      <c r="L236" t="inlineStr"/>
-      <c r="M236" t="inlineStr"/>
-      <c r="N236" t="inlineStr"/>
-      <c r="O236" t="inlineStr"/>
-      <c r="P236" t="inlineStr"/>
-      <c r="Q236" t="inlineStr"/>
-      <c r="R236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -14286,13 +12429,6 @@
           <t>Brake safety concern — pulsing pedal after brake service is a potential safety hazard requiring immediate human review.</t>
         </is>
       </c>
-      <c r="L237" t="inlineStr"/>
-      <c r="M237" t="inlineStr"/>
-      <c r="N237" t="inlineStr"/>
-      <c r="O237" t="inlineStr"/>
-      <c r="P237" t="inlineStr"/>
-      <c r="Q237" t="inlineStr"/>
-      <c r="R237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -14343,14 +12479,6 @@
       <c r="J238" t="b">
         <v>0</v>
       </c>
-      <c r="K238" t="inlineStr"/>
-      <c r="L238" t="inlineStr"/>
-      <c r="M238" t="inlineStr"/>
-      <c r="N238" t="inlineStr"/>
-      <c r="O238" t="inlineStr"/>
-      <c r="P238" t="inlineStr"/>
-      <c r="Q238" t="inlineStr"/>
-      <c r="R238" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -14406,13 +12534,6 @@
           <t>Customer is without their vehicle due to back-ordered overseas part and has left contact details requesting a callback.</t>
         </is>
       </c>
-      <c r="L239" t="inlineStr"/>
-      <c r="M239" t="inlineStr"/>
-      <c r="N239" t="inlineStr"/>
-      <c r="O239" t="inlineStr"/>
-      <c r="P239" t="inlineStr"/>
-      <c r="Q239" t="inlineStr"/>
-      <c r="R239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -14463,14 +12584,6 @@
       <c r="J240" t="b">
         <v>0</v>
       </c>
-      <c r="K240" t="inlineStr"/>
-      <c r="L240" t="inlineStr"/>
-      <c r="M240" t="inlineStr"/>
-      <c r="N240" t="inlineStr"/>
-      <c r="O240" t="inlineStr"/>
-      <c r="P240" t="inlineStr"/>
-      <c r="Q240" t="inlineStr"/>
-      <c r="R240" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -14521,14 +12634,6 @@
       <c r="J241" t="b">
         <v>0</v>
       </c>
-      <c r="K241" t="inlineStr"/>
-      <c r="L241" t="inlineStr"/>
-      <c r="M241" t="inlineStr"/>
-      <c r="N241" t="inlineStr"/>
-      <c r="O241" t="inlineStr"/>
-      <c r="P241" t="inlineStr"/>
-      <c r="Q241" t="inlineStr"/>
-      <c r="R241" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -14579,14 +12684,6 @@
       <c r="J242" t="b">
         <v>0</v>
       </c>
-      <c r="K242" t="inlineStr"/>
-      <c r="L242" t="inlineStr"/>
-      <c r="M242" t="inlineStr"/>
-      <c r="N242" t="inlineStr"/>
-      <c r="O242" t="inlineStr"/>
-      <c r="P242" t="inlineStr"/>
-      <c r="Q242" t="inlineStr"/>
-      <c r="R242" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -14637,14 +12734,6 @@
       <c r="J243" t="b">
         <v>0</v>
       </c>
-      <c r="K243" t="inlineStr"/>
-      <c r="L243" t="inlineStr"/>
-      <c r="M243" t="inlineStr"/>
-      <c r="N243" t="inlineStr"/>
-      <c r="O243" t="inlineStr"/>
-      <c r="P243" t="inlineStr"/>
-      <c r="Q243" t="inlineStr"/>
-      <c r="R243" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -14695,14 +12784,6 @@
       <c r="J244" t="b">
         <v>0</v>
       </c>
-      <c r="K244" t="inlineStr"/>
-      <c r="L244" t="inlineStr"/>
-      <c r="M244" t="inlineStr"/>
-      <c r="N244" t="inlineStr"/>
-      <c r="O244" t="inlineStr"/>
-      <c r="P244" t="inlineStr"/>
-      <c r="Q244" t="inlineStr"/>
-      <c r="R244" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -14753,14 +12834,6 @@
       <c r="J245" t="b">
         <v>0</v>
       </c>
-      <c r="K245" t="inlineStr"/>
-      <c r="L245" t="inlineStr"/>
-      <c r="M245" t="inlineStr"/>
-      <c r="N245" t="inlineStr"/>
-      <c r="O245" t="inlineStr"/>
-      <c r="P245" t="inlineStr"/>
-      <c r="Q245" t="inlineStr"/>
-      <c r="R245" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -14811,14 +12884,6 @@
       <c r="J246" t="b">
         <v>0</v>
       </c>
-      <c r="K246" t="inlineStr"/>
-      <c r="L246" t="inlineStr"/>
-      <c r="M246" t="inlineStr"/>
-      <c r="N246" t="inlineStr"/>
-      <c r="O246" t="inlineStr"/>
-      <c r="P246" t="inlineStr"/>
-      <c r="Q246" t="inlineStr"/>
-      <c r="R246" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -14869,14 +12934,6 @@
       <c r="J247" t="b">
         <v>0</v>
       </c>
-      <c r="K247" t="inlineStr"/>
-      <c r="L247" t="inlineStr"/>
-      <c r="M247" t="inlineStr"/>
-      <c r="N247" t="inlineStr"/>
-      <c r="O247" t="inlineStr"/>
-      <c r="P247" t="inlineStr"/>
-      <c r="Q247" t="inlineStr"/>
-      <c r="R247" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -14932,13 +12989,6 @@
           <t>Vehicle returned with physical damage — potential liability and unresolved follow-up complaint.</t>
         </is>
       </c>
-      <c r="L248" t="inlineStr"/>
-      <c r="M248" t="inlineStr"/>
-      <c r="N248" t="inlineStr"/>
-      <c r="O248" t="inlineStr"/>
-      <c r="P248" t="inlineStr"/>
-      <c r="Q248" t="inlineStr"/>
-      <c r="R248" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -14989,14 +13039,6 @@
       <c r="J249" t="b">
         <v>0</v>
       </c>
-      <c r="K249" t="inlineStr"/>
-      <c r="L249" t="inlineStr"/>
-      <c r="M249" t="inlineStr"/>
-      <c r="N249" t="inlineStr"/>
-      <c r="O249" t="inlineStr"/>
-      <c r="P249" t="inlineStr"/>
-      <c r="Q249" t="inlineStr"/>
-      <c r="R249" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -15047,14 +13089,6 @@
       <c r="J250" t="b">
         <v>0</v>
       </c>
-      <c r="K250" t="inlineStr"/>
-      <c r="L250" t="inlineStr"/>
-      <c r="M250" t="inlineStr"/>
-      <c r="N250" t="inlineStr"/>
-      <c r="O250" t="inlineStr"/>
-      <c r="P250" t="inlineStr"/>
-      <c r="Q250" t="inlineStr"/>
-      <c r="R250" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -15105,14 +13139,6 @@
       <c r="J251" t="b">
         <v>0</v>
       </c>
-      <c r="K251" t="inlineStr"/>
-      <c r="L251" t="inlineStr"/>
-      <c r="M251" t="inlineStr"/>
-      <c r="N251" t="inlineStr"/>
-      <c r="O251" t="inlineStr"/>
-      <c r="P251" t="inlineStr"/>
-      <c r="Q251" t="inlineStr"/>
-      <c r="R251" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -15274,7 +13300,6 @@
       <c r="N2" t="b">
         <v>0</v>
       </c>
-      <c r="O2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -15345,7 +13370,6 @@
       <c r="N3" t="b">
         <v>0</v>
       </c>
-      <c r="O3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -15416,7 +13440,6 @@
       <c r="N4" t="b">
         <v>0</v>
       </c>
-      <c r="O4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -15487,7 +13510,6 @@
       <c r="N5" t="b">
         <v>0</v>
       </c>
-      <c r="O5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -15558,7 +13580,6 @@
       <c r="N6" t="b">
         <v>0</v>
       </c>
-      <c r="O6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -15704,7 +13725,6 @@
       <c r="N8" t="b">
         <v>0</v>
       </c>
-      <c r="O8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -15775,7 +13795,6 @@
       <c r="N9" t="b">
         <v>0</v>
       </c>
-      <c r="O9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -15846,7 +13865,6 @@
       <c r="N10" t="b">
         <v>0</v>
       </c>
-      <c r="O10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -15992,7 +14010,6 @@
       <c r="N12" t="b">
         <v>0</v>
       </c>
-      <c r="O12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -16063,7 +14080,6 @@
       <c r="N13" t="b">
         <v>0</v>
       </c>
-      <c r="O13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -16134,7 +14150,6 @@
       <c r="N14" t="b">
         <v>0</v>
       </c>
-      <c r="O14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -16205,7 +14220,6 @@
       <c r="N15" t="b">
         <v>0</v>
       </c>
-      <c r="O15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -16276,7 +14290,6 @@
       <c r="N16" t="b">
         <v>0</v>
       </c>
-      <c r="O16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -16347,7 +14360,6 @@
       <c r="N17" t="b">
         <v>0</v>
       </c>
-      <c r="O17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -16418,7 +14430,6 @@
       <c r="N18" t="b">
         <v>0</v>
       </c>
-      <c r="O18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -16489,7 +14500,6 @@
       <c r="N19" t="b">
         <v>0</v>
       </c>
-      <c r="O19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -16560,7 +14570,6 @@
       <c r="N20" t="b">
         <v>0</v>
       </c>
-      <c r="O20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -16631,7 +14640,6 @@
       <c r="N21" t="b">
         <v>0</v>
       </c>
-      <c r="O21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -16702,7 +14710,6 @@
       <c r="N22" t="b">
         <v>0</v>
       </c>
-      <c r="O22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -16773,7 +14780,6 @@
       <c r="N23" t="b">
         <v>0</v>
       </c>
-      <c r="O23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -16919,7 +14925,6 @@
       <c r="N25" t="b">
         <v>0</v>
       </c>
-      <c r="O25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -16990,7 +14995,6 @@
       <c r="N26" t="b">
         <v>0</v>
       </c>
-      <c r="O26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -17061,7 +15065,6 @@
       <c r="N27" t="b">
         <v>0</v>
       </c>
-      <c r="O27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -17207,7 +15210,6 @@
       <c r="N29" t="b">
         <v>0</v>
       </c>
-      <c r="O29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -17278,7 +15280,6 @@
       <c r="N30" t="b">
         <v>0</v>
       </c>
-      <c r="O30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -17349,7 +15350,6 @@
       <c r="N31" t="b">
         <v>0</v>
       </c>
-      <c r="O31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -17420,7 +15420,6 @@
       <c r="N32" t="b">
         <v>0</v>
       </c>
-      <c r="O32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -17491,7 +15490,6 @@
       <c r="N33" t="b">
         <v>0</v>
       </c>
-      <c r="O33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -17562,7 +15560,6 @@
       <c r="N34" t="b">
         <v>0</v>
       </c>
-      <c r="O34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -17633,7 +15630,6 @@
       <c r="N35" t="b">
         <v>0</v>
       </c>
-      <c r="O35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -17854,7 +15850,6 @@
       <c r="N38" t="b">
         <v>0</v>
       </c>
-      <c r="O38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -17925,7 +15920,6 @@
       <c r="N39" t="b">
         <v>0</v>
       </c>
-      <c r="O39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -17996,7 +15990,6 @@
       <c r="N40" t="b">
         <v>0</v>
       </c>
-      <c r="O40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -18067,7 +16060,6 @@
       <c r="N41" t="b">
         <v>0</v>
       </c>
-      <c r="O41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -18138,7 +16130,6 @@
       <c r="N42" t="b">
         <v>0</v>
       </c>
-      <c r="O42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -18209,7 +16200,6 @@
       <c r="N43" t="b">
         <v>0</v>
       </c>
-      <c r="O43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -18280,7 +16270,6 @@
       <c r="N44" t="b">
         <v>0</v>
       </c>
-      <c r="O44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -18351,7 +16340,6 @@
       <c r="N45" t="b">
         <v>0</v>
       </c>
-      <c r="O45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -18647,7 +16635,6 @@
       <c r="N49" t="b">
         <v>0</v>
       </c>
-      <c r="O49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -18718,7 +16705,6 @@
       <c r="N50" t="b">
         <v>0</v>
       </c>
-      <c r="O50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -18789,7 +16775,6 @@
       <c r="N51" t="b">
         <v>0</v>
       </c>
-      <c r="O51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -18860,7 +16845,6 @@
       <c r="N52" t="b">
         <v>0</v>
       </c>
-      <c r="O52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -18931,7 +16915,6 @@
       <c r="N53" t="b">
         <v>0</v>
       </c>
-      <c r="O53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -19077,7 +17060,6 @@
       <c r="N55" t="b">
         <v>0</v>
       </c>
-      <c r="O55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -19148,7 +17130,6 @@
       <c r="N56" t="b">
         <v>0</v>
       </c>
-      <c r="O56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -19219,7 +17200,6 @@
       <c r="N57" t="b">
         <v>0</v>
       </c>
-      <c r="O57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -19290,7 +17270,6 @@
       <c r="N58" t="b">
         <v>0</v>
       </c>
-      <c r="O58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -19361,7 +17340,6 @@
       <c r="N59" t="b">
         <v>0</v>
       </c>
-      <c r="O59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -19432,7 +17410,6 @@
       <c r="N60" t="b">
         <v>0</v>
       </c>
-      <c r="O60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -19503,7 +17480,6 @@
       <c r="N61" t="b">
         <v>0</v>
       </c>
-      <c r="O61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -19649,7 +17625,6 @@
       <c r="N63" t="b">
         <v>0</v>
       </c>
-      <c r="O63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -19720,7 +17695,6 @@
       <c r="N64" t="b">
         <v>0</v>
       </c>
-      <c r="O64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -19791,7 +17765,6 @@
       <c r="N65" t="b">
         <v>0</v>
       </c>
-      <c r="O65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -20012,7 +17985,6 @@
       <c r="N68" t="b">
         <v>0</v>
       </c>
-      <c r="O68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -20158,7 +18130,6 @@
       <c r="N70" t="b">
         <v>0</v>
       </c>
-      <c r="O70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -20229,7 +18200,6 @@
       <c r="N71" t="b">
         <v>0</v>
       </c>
-      <c r="O71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -20450,7 +18420,6 @@
       <c r="N74" t="b">
         <v>0</v>
       </c>
-      <c r="O74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -20521,7 +18490,6 @@
       <c r="N75" t="b">
         <v>0</v>
       </c>
-      <c r="O75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -20592,7 +18560,6 @@
       <c r="N76" t="b">
         <v>0</v>
       </c>
-      <c r="O76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -20663,7 +18630,6 @@
       <c r="N77" t="b">
         <v>0</v>
       </c>
-      <c r="O77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -20734,7 +18700,6 @@
       <c r="N78" t="b">
         <v>0</v>
       </c>
-      <c r="O78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -20805,7 +18770,6 @@
       <c r="N79" t="b">
         <v>0</v>
       </c>
-      <c r="O79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -20876,7 +18840,6 @@
       <c r="N80" t="b">
         <v>0</v>
       </c>
-      <c r="O80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -20947,7 +18910,6 @@
       <c r="N81" t="b">
         <v>0</v>
       </c>
-      <c r="O81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -21018,7 +18980,6 @@
       <c r="N82" t="b">
         <v>0</v>
       </c>
-      <c r="O82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -21089,7 +19050,6 @@
       <c r="N83" t="b">
         <v>0</v>
       </c>
-      <c r="O83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -21160,7 +19120,6 @@
       <c r="N84" t="b">
         <v>0</v>
       </c>
-      <c r="O84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -21231,7 +19190,6 @@
       <c r="N85" t="b">
         <v>0</v>
       </c>
-      <c r="O85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -21302,7 +19260,6 @@
       <c r="N86" t="b">
         <v>0</v>
       </c>
-      <c r="O86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -21373,7 +19330,6 @@
       <c r="N87" t="b">
         <v>0</v>
       </c>
-      <c r="O87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -21444,7 +19400,6 @@
       <c r="N88" t="b">
         <v>0</v>
       </c>
-      <c r="O88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -21515,7 +19470,6 @@
       <c r="N89" t="b">
         <v>0</v>
       </c>
-      <c r="O89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -21586,7 +19540,6 @@
       <c r="N90" t="b">
         <v>0</v>
       </c>
-      <c r="O90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -21657,7 +19610,6 @@
       <c r="N91" t="b">
         <v>0</v>
       </c>
-      <c r="O91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -21728,7 +19680,6 @@
       <c r="N92" t="b">
         <v>0</v>
       </c>
-      <c r="O92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -21874,7 +19825,6 @@
       <c r="N94" t="b">
         <v>0</v>
       </c>
-      <c r="O94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -21945,7 +19895,6 @@
       <c r="N95" t="b">
         <v>0</v>
       </c>
-      <c r="O95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -22016,7 +19965,6 @@
       <c r="N96" t="b">
         <v>0</v>
       </c>
-      <c r="O96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -22087,7 +20035,6 @@
       <c r="N97" t="b">
         <v>0</v>
       </c>
-      <c r="O97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -22158,7 +20105,6 @@
       <c r="N98" t="b">
         <v>0</v>
       </c>
-      <c r="O98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -22229,7 +20175,6 @@
       <c r="N99" t="b">
         <v>0</v>
       </c>
-      <c r="O99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -22300,7 +20245,6 @@
       <c r="N100" t="b">
         <v>0</v>
       </c>
-      <c r="O100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -22371,7 +20315,6 @@
       <c r="N101" t="b">
         <v>0</v>
       </c>
-      <c r="O101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -22442,7 +20385,6 @@
       <c r="N102" t="b">
         <v>0</v>
       </c>
-      <c r="O102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -22513,7 +20455,6 @@
       <c r="N103" t="b">
         <v>0</v>
       </c>
-      <c r="O103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -22584,7 +20525,6 @@
       <c r="N104" t="b">
         <v>0</v>
       </c>
-      <c r="O104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -22655,7 +20595,6 @@
       <c r="N105" t="b">
         <v>0</v>
       </c>
-      <c r="O105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -22726,7 +20665,6 @@
       <c r="N106" t="b">
         <v>0</v>
       </c>
-      <c r="O106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -22797,7 +20735,6 @@
       <c r="N107" t="b">
         <v>0</v>
       </c>
-      <c r="O107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -22868,7 +20805,6 @@
       <c r="N108" t="b">
         <v>0</v>
       </c>
-      <c r="O108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -22939,7 +20875,6 @@
       <c r="N109" t="b">
         <v>0</v>
       </c>
-      <c r="O109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -23010,7 +20945,6 @@
       <c r="N110" t="b">
         <v>0</v>
       </c>
-      <c r="O110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -23081,7 +21015,6 @@
       <c r="N111" t="b">
         <v>0</v>
       </c>
-      <c r="O111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -23152,7 +21085,6 @@
       <c r="N112" t="b">
         <v>0</v>
       </c>
-      <c r="O112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -23223,7 +21155,6 @@
       <c r="N113" t="b">
         <v>0</v>
       </c>
-      <c r="O113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -23294,7 +21225,6 @@
       <c r="N114" t="b">
         <v>0</v>
       </c>
-      <c r="O114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -23365,7 +21295,6 @@
       <c r="N115" t="b">
         <v>0</v>
       </c>
-      <c r="O115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -23436,7 +21365,6 @@
       <c r="N116" t="b">
         <v>0</v>
       </c>
-      <c r="O116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -23507,7 +21435,6 @@
       <c r="N117" t="b">
         <v>0</v>
       </c>
-      <c r="O117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -23578,7 +21505,6 @@
       <c r="N118" t="b">
         <v>0</v>
       </c>
-      <c r="O118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -23649,7 +21575,6 @@
       <c r="N119" t="b">
         <v>0</v>
       </c>
-      <c r="O119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -23720,7 +21645,6 @@
       <c r="N120" t="b">
         <v>0</v>
       </c>
-      <c r="O120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -23791,7 +21715,6 @@
       <c r="N121" t="b">
         <v>0</v>
       </c>
-      <c r="O121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -23937,7 +21860,6 @@
       <c r="N123" t="b">
         <v>0</v>
       </c>
-      <c r="O123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -24008,7 +21930,6 @@
       <c r="N124" t="b">
         <v>0</v>
       </c>
-      <c r="O124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -24229,7 +22150,6 @@
       <c r="N127" t="b">
         <v>0</v>
       </c>
-      <c r="O127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -24300,7 +22220,6 @@
       <c r="N128" t="b">
         <v>0</v>
       </c>
-      <c r="O128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -24371,7 +22290,6 @@
       <c r="N129" t="b">
         <v>0</v>
       </c>
-      <c r="O129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -24442,7 +22360,6 @@
       <c r="N130" t="b">
         <v>0</v>
       </c>
-      <c r="O130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -24513,7 +22430,6 @@
       <c r="N131" t="b">
         <v>0</v>
       </c>
-      <c r="O131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -24584,7 +22500,6 @@
       <c r="N132" t="b">
         <v>0</v>
       </c>
-      <c r="O132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -24655,7 +22570,6 @@
       <c r="N133" t="b">
         <v>0</v>
       </c>
-      <c r="O133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -24726,7 +22640,6 @@
       <c r="N134" t="b">
         <v>0</v>
       </c>
-      <c r="O134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -24797,7 +22710,6 @@
       <c r="N135" t="b">
         <v>0</v>
       </c>
-      <c r="O135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -24868,7 +22780,6 @@
       <c r="N136" t="b">
         <v>0</v>
       </c>
-      <c r="O136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -24939,7 +22850,6 @@
       <c r="N137" t="b">
         <v>0</v>
       </c>
-      <c r="O137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -25010,7 +22920,6 @@
       <c r="N138" t="b">
         <v>0</v>
       </c>
-      <c r="O138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -25081,7 +22990,6 @@
       <c r="N139" t="b">
         <v>0</v>
       </c>
-      <c r="O139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -25302,7 +23210,6 @@
       <c r="N142" t="b">
         <v>0</v>
       </c>
-      <c r="O142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -25373,7 +23280,6 @@
       <c r="N143" t="b">
         <v>0</v>
       </c>
-      <c r="O143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -25444,7 +23350,6 @@
       <c r="N144" t="b">
         <v>0</v>
       </c>
-      <c r="O144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -25515,7 +23420,6 @@
       <c r="N145" t="b">
         <v>0</v>
       </c>
-      <c r="O145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -25586,7 +23490,6 @@
       <c r="N146" t="b">
         <v>0</v>
       </c>
-      <c r="O146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -25657,7 +23560,6 @@
       <c r="N147" t="b">
         <v>0</v>
       </c>
-      <c r="O147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -25728,7 +23630,6 @@
       <c r="N148" t="b">
         <v>0</v>
       </c>
-      <c r="O148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -25799,7 +23700,6 @@
       <c r="N149" t="b">
         <v>0</v>
       </c>
-      <c r="O149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -25870,7 +23770,6 @@
       <c r="N150" t="b">
         <v>0</v>
       </c>
-      <c r="O150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -25941,7 +23840,6 @@
       <c r="N151" t="b">
         <v>0</v>
       </c>
-      <c r="O151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -26012,7 +23910,6 @@
       <c r="N152" t="b">
         <v>0</v>
       </c>
-      <c r="O152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -26083,7 +23980,6 @@
       <c r="N153" t="b">
         <v>0</v>
       </c>
-      <c r="O153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -26154,7 +24050,6 @@
       <c r="N154" t="b">
         <v>0</v>
       </c>
-      <c r="O154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -26300,7 +24195,6 @@
       <c r="N156" t="b">
         <v>0</v>
       </c>
-      <c r="O156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -26371,7 +24265,6 @@
       <c r="N157" t="b">
         <v>0</v>
       </c>
-      <c r="O157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -26517,7 +24410,6 @@
       <c r="N159" t="b">
         <v>0</v>
       </c>
-      <c r="O159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -26588,7 +24480,6 @@
       <c r="N160" t="b">
         <v>0</v>
       </c>
-      <c r="O160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -26659,7 +24550,6 @@
       <c r="N161" t="b">
         <v>0</v>
       </c>
-      <c r="O161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -26730,7 +24620,6 @@
       <c r="N162" t="b">
         <v>0</v>
       </c>
-      <c r="O162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -26801,7 +24690,6 @@
       <c r="N163" t="b">
         <v>0</v>
       </c>
-      <c r="O163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -26872,7 +24760,6 @@
       <c r="N164" t="b">
         <v>0</v>
       </c>
-      <c r="O164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -27018,7 +24905,6 @@
       <c r="N166" t="b">
         <v>0</v>
       </c>
-      <c r="O166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -27089,7 +24975,6 @@
       <c r="N167" t="b">
         <v>0</v>
       </c>
-      <c r="O167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -27160,7 +25045,6 @@
       <c r="N168" t="b">
         <v>0</v>
       </c>
-      <c r="O168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -27231,7 +25115,6 @@
       <c r="N169" t="b">
         <v>0</v>
       </c>
-      <c r="O169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -27377,7 +25260,6 @@
       <c r="N171" t="b">
         <v>0</v>
       </c>
-      <c r="O171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -27523,7 +25405,6 @@
       <c r="N173" t="b">
         <v>0</v>
       </c>
-      <c r="O173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -27594,7 +25475,6 @@
       <c r="N174" t="b">
         <v>0</v>
       </c>
-      <c r="O174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -27665,7 +25545,6 @@
       <c r="N175" t="b">
         <v>0</v>
       </c>
-      <c r="O175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -27736,7 +25615,6 @@
       <c r="N176" t="b">
         <v>0</v>
       </c>
-      <c r="O176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -27807,7 +25685,6 @@
       <c r="N177" t="b">
         <v>0</v>
       </c>
-      <c r="O177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -27878,7 +25755,6 @@
       <c r="N178" t="b">
         <v>0</v>
       </c>
-      <c r="O178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -27949,7 +25825,6 @@
       <c r="N179" t="b">
         <v>0</v>
       </c>
-      <c r="O179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -28020,7 +25895,6 @@
       <c r="N180" t="b">
         <v>0</v>
       </c>
-      <c r="O180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -28091,7 +25965,6 @@
       <c r="N181" t="b">
         <v>0</v>
       </c>
-      <c r="O181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -28237,7 +26110,6 @@
       <c r="N183" t="b">
         <v>0</v>
       </c>
-      <c r="O183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -28383,7 +26255,6 @@
       <c r="N185" t="b">
         <v>0</v>
       </c>
-      <c r="O185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -28529,7 +26400,6 @@
       <c r="N187" t="b">
         <v>0</v>
       </c>
-      <c r="O187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -28600,7 +26470,6 @@
       <c r="N188" t="b">
         <v>0</v>
       </c>
-      <c r="O188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -28671,7 +26540,6 @@
       <c r="N189" t="b">
         <v>0</v>
       </c>
-      <c r="O189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -28742,7 +26610,6 @@
       <c r="N190" t="b">
         <v>0</v>
       </c>
-      <c r="O190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -28813,7 +26680,6 @@
       <c r="N191" t="b">
         <v>0</v>
       </c>
-      <c r="O191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -28884,7 +26750,6 @@
       <c r="N192" t="b">
         <v>0</v>
       </c>
-      <c r="O192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -28927,7 +26792,6 @@
           <t>Vehicle Knowledge &amp; Explanation</t>
         </is>
       </c>
-      <c r="I193" t="inlineStr"/>
       <c r="J193" t="inlineStr">
         <is>
           <t>Positive</t>
@@ -28938,7 +26802,6 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="L193" t="inlineStr"/>
       <c r="M193" t="inlineStr">
         <is>
           <t>Service</t>
@@ -28947,7 +26810,6 @@
       <c r="N193" t="b">
         <v>0</v>
       </c>
-      <c r="O193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -28990,7 +26852,6 @@
           <t>Timeliness &amp; Wait Times</t>
         </is>
       </c>
-      <c r="I194" t="inlineStr"/>
       <c r="J194" t="inlineStr">
         <is>
           <t>Positive</t>
@@ -29001,7 +26862,6 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="L194" t="inlineStr"/>
       <c r="M194" t="inlineStr">
         <is>
           <t>Service</t>
@@ -29010,7 +26870,6 @@
       <c r="N194" t="b">
         <v>0</v>
       </c>
-      <c r="O194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -29053,7 +26912,6 @@
           <t>Positive Experience (General)</t>
         </is>
       </c>
-      <c r="I195" t="inlineStr"/>
       <c r="J195" t="inlineStr">
         <is>
           <t>Positive</t>
@@ -29064,7 +26922,6 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="L195" t="inlineStr"/>
       <c r="M195" t="inlineStr">
         <is>
           <t>Sales</t>
@@ -29073,7 +26930,6 @@
       <c r="N195" t="b">
         <v>0</v>
       </c>
-      <c r="O195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -29116,7 +26972,6 @@
           <t>Vehicle Knowledge &amp; Explanation</t>
         </is>
       </c>
-      <c r="I196" t="inlineStr"/>
       <c r="J196" t="inlineStr">
         <is>
           <t>Positive</t>
@@ -29127,7 +26982,6 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="L196" t="inlineStr"/>
       <c r="M196" t="inlineStr">
         <is>
           <t>Service</t>
@@ -29136,7 +26990,6 @@
       <c r="N196" t="b">
         <v>0</v>
       </c>
-      <c r="O196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -29179,7 +27032,6 @@
           <t>Sales Process &amp; Handover</t>
         </is>
       </c>
-      <c r="I197" t="inlineStr"/>
       <c r="J197" t="inlineStr">
         <is>
           <t>Positive</t>
@@ -29190,7 +27042,6 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="L197" t="inlineStr"/>
       <c r="M197" t="inlineStr">
         <is>
           <t>Sales</t>
@@ -29199,7 +27050,6 @@
       <c r="N197" t="b">
         <v>0</v>
       </c>
-      <c r="O197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -29242,7 +27092,6 @@
           <t>Vehicle Knowledge &amp; Explanation</t>
         </is>
       </c>
-      <c r="I198" t="inlineStr"/>
       <c r="J198" t="inlineStr">
         <is>
           <t>Positive</t>
@@ -29253,7 +27102,6 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="L198" t="inlineStr"/>
       <c r="M198" t="inlineStr">
         <is>
           <t>Sales</t>
@@ -29262,7 +27110,6 @@
       <c r="N198" t="b">
         <v>0</v>
       </c>
-      <c r="O198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -29305,7 +27152,6 @@
           <t>Pricing &amp; Charges</t>
         </is>
       </c>
-      <c r="I199" t="inlineStr"/>
       <c r="J199" t="inlineStr">
         <is>
           <t>Positive</t>
@@ -29316,7 +27162,6 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="L199" t="inlineStr"/>
       <c r="M199" t="inlineStr">
         <is>
           <t>Service</t>
@@ -29325,7 +27170,6 @@
       <c r="N199" t="b">
         <v>0</v>
       </c>
-      <c r="O199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -29368,7 +27212,6 @@
           <t>Staff Attitude &amp; Behaviour</t>
         </is>
       </c>
-      <c r="I200" t="inlineStr"/>
       <c r="J200" t="inlineStr">
         <is>
           <t>Positive</t>
@@ -29379,7 +27222,6 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="L200" t="inlineStr"/>
       <c r="M200" t="inlineStr">
         <is>
           <t>Parts</t>
@@ -29388,7 +27230,6 @@
       <c r="N200" t="b">
         <v>0</v>
       </c>
-      <c r="O200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -29431,7 +27272,6 @@
           <t>Communication &amp; Updates</t>
         </is>
       </c>
-      <c r="I201" t="inlineStr"/>
       <c r="J201" t="inlineStr">
         <is>
           <t>Positive</t>
@@ -29442,7 +27282,6 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="L201" t="inlineStr"/>
       <c r="M201" t="inlineStr">
         <is>
           <t>Service</t>
@@ -29451,7 +27290,6 @@
       <c r="N201" t="b">
         <v>0</v>
       </c>
-      <c r="O201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -29494,7 +27332,6 @@
           <t>Staff Attitude &amp; Behaviour</t>
         </is>
       </c>
-      <c r="I202" t="inlineStr"/>
       <c r="J202" t="inlineStr">
         <is>
           <t>Positive</t>
@@ -29505,7 +27342,6 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="L202" t="inlineStr"/>
       <c r="M202" t="inlineStr">
         <is>
           <t>Sales</t>
@@ -29514,7 +27350,6 @@
       <c r="N202" t="b">
         <v>0</v>
       </c>
-      <c r="O202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -29557,7 +27392,6 @@
           <t>Communication &amp; Updates</t>
         </is>
       </c>
-      <c r="I203" t="inlineStr"/>
       <c r="J203" t="inlineStr">
         <is>
           <t>Positive</t>
@@ -29568,7 +27402,6 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="L203" t="inlineStr"/>
       <c r="M203" t="inlineStr">
         <is>
           <t>Service</t>
@@ -29577,7 +27410,6 @@
       <c r="N203" t="b">
         <v>0</v>
       </c>
-      <c r="O203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -29620,7 +27452,6 @@
           <t>Vehicle Knowledge &amp; Explanation</t>
         </is>
       </c>
-      <c r="I204" t="inlineStr"/>
       <c r="J204" t="inlineStr">
         <is>
           <t>Positive</t>
@@ -29631,7 +27462,6 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="L204" t="inlineStr"/>
       <c r="M204" t="inlineStr">
         <is>
           <t>Sales</t>
@@ -29640,7 +27470,6 @@
       <c r="N204" t="b">
         <v>0</v>
       </c>
-      <c r="O204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -29683,7 +27512,6 @@
           <t>Positive Experience (General)</t>
         </is>
       </c>
-      <c r="I205" t="inlineStr"/>
       <c r="J205" t="inlineStr">
         <is>
           <t>Positive</t>
@@ -29694,7 +27522,6 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="L205" t="inlineStr"/>
       <c r="M205" t="inlineStr">
         <is>
           <t>Service</t>
@@ -29703,7 +27530,6 @@
       <c r="N205" t="b">
         <v>0</v>
       </c>
-      <c r="O205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -29746,7 +27572,6 @@
           <t>Staff Attitude &amp; Behaviour</t>
         </is>
       </c>
-      <c r="I206" t="inlineStr"/>
       <c r="J206" t="inlineStr">
         <is>
           <t>Positive</t>
@@ -29757,7 +27582,6 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="L206" t="inlineStr"/>
       <c r="M206" t="inlineStr">
         <is>
           <t>Sales</t>
@@ -29766,7 +27590,6 @@
       <c r="N206" t="b">
         <v>0</v>
       </c>
-      <c r="O206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -29809,7 +27632,6 @@
           <t>Staff Attitude &amp; Behaviour</t>
         </is>
       </c>
-      <c r="I207" t="inlineStr"/>
       <c r="J207" t="inlineStr">
         <is>
           <t>Positive</t>
@@ -29820,7 +27642,6 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="L207" t="inlineStr"/>
       <c r="M207" t="inlineStr">
         <is>
           <t>Parts</t>
@@ -29829,7 +27650,6 @@
       <c r="N207" t="b">
         <v>0</v>
       </c>
-      <c r="O207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -29872,7 +27692,6 @@
           <t>Communication &amp; Updates</t>
         </is>
       </c>
-      <c r="I208" t="inlineStr"/>
       <c r="J208" t="inlineStr">
         <is>
           <t>Positive</t>
@@ -29883,7 +27702,6 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="L208" t="inlineStr"/>
       <c r="M208" t="inlineStr">
         <is>
           <t>Service</t>
@@ -29892,7 +27710,6 @@
       <c r="N208" t="b">
         <v>0</v>
       </c>
-      <c r="O208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -29935,7 +27752,6 @@
           <t>Staff Attitude &amp; Behaviour</t>
         </is>
       </c>
-      <c r="I209" t="inlineStr"/>
       <c r="J209" t="inlineStr">
         <is>
           <t>Positive</t>
@@ -29946,7 +27762,6 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="L209" t="inlineStr"/>
       <c r="M209" t="inlineStr">
         <is>
           <t>Sales</t>
@@ -29955,7 +27770,6 @@
       <c r="N209" t="b">
         <v>0</v>
       </c>
-      <c r="O209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -29998,7 +27812,6 @@
           <t>Pricing &amp; Charges</t>
         </is>
       </c>
-      <c r="I210" t="inlineStr"/>
       <c r="J210" t="inlineStr">
         <is>
           <t>Positive</t>
@@ -30009,7 +27822,6 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="L210" t="inlineStr"/>
       <c r="M210" t="inlineStr">
         <is>
           <t>Service</t>
@@ -30018,7 +27830,6 @@
       <c r="N210" t="b">
         <v>0</v>
       </c>
-      <c r="O210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -30061,7 +27872,6 @@
           <t>Staff Attitude &amp; Behaviour</t>
         </is>
       </c>
-      <c r="I211" t="inlineStr"/>
       <c r="J211" t="inlineStr">
         <is>
           <t>Positive</t>
@@ -30072,7 +27882,6 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="L211" t="inlineStr"/>
       <c r="M211" t="inlineStr">
         <is>
           <t>Sales</t>
@@ -30081,7 +27890,6 @@
       <c r="N211" t="b">
         <v>0</v>
       </c>
-      <c r="O211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -30124,7 +27932,6 @@
           <t>Vehicle Knowledge &amp; Explanation</t>
         </is>
       </c>
-      <c r="I212" t="inlineStr"/>
       <c r="J212" t="inlineStr">
         <is>
           <t>Positive</t>
@@ -30135,7 +27942,6 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="L212" t="inlineStr"/>
       <c r="M212" t="inlineStr">
         <is>
           <t>Service</t>
@@ -30144,7 +27950,6 @@
       <c r="N212" t="b">
         <v>0</v>
       </c>
-      <c r="O212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -30187,7 +27992,6 @@
           <t>Communication &amp; Updates</t>
         </is>
       </c>
-      <c r="I213" t="inlineStr"/>
       <c r="J213" t="inlineStr">
         <is>
           <t>Positive</t>
@@ -30198,7 +28002,6 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="L213" t="inlineStr"/>
       <c r="M213" t="inlineStr">
         <is>
           <t>Service</t>
@@ -30207,7 +28010,6 @@
       <c r="N213" t="b">
         <v>0</v>
       </c>
-      <c r="O213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -30250,7 +28052,6 @@
           <t>Pricing &amp; Charges</t>
         </is>
       </c>
-      <c r="I214" t="inlineStr"/>
       <c r="J214" t="inlineStr">
         <is>
           <t>Positive</t>
@@ -30261,7 +28062,6 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="L214" t="inlineStr"/>
       <c r="M214" t="inlineStr">
         <is>
           <t>Service</t>
@@ -30270,7 +28070,6 @@
       <c r="N214" t="b">
         <v>0</v>
       </c>
-      <c r="O214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -30313,7 +28112,6 @@
           <t>Communication &amp; Updates</t>
         </is>
       </c>
-      <c r="I215" t="inlineStr"/>
       <c r="J215" t="inlineStr">
         <is>
           <t>Positive</t>
@@ -30324,7 +28122,6 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="L215" t="inlineStr"/>
       <c r="M215" t="inlineStr">
         <is>
           <t>Sales</t>
@@ -30333,7 +28130,6 @@
       <c r="N215" t="b">
         <v>0</v>
       </c>
-      <c r="O215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -30376,7 +28172,6 @@
           <t>Staff Attitude &amp; Behaviour</t>
         </is>
       </c>
-      <c r="I216" t="inlineStr"/>
       <c r="J216" t="inlineStr">
         <is>
           <t>Positive</t>
@@ -30387,7 +28182,6 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="L216" t="inlineStr"/>
       <c r="M216" t="inlineStr">
         <is>
           <t>Sales</t>
@@ -30396,7 +28190,6 @@
       <c r="N216" t="b">
         <v>0</v>
       </c>
-      <c r="O216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -30439,7 +28232,6 @@
           <t>Communication &amp; Updates</t>
         </is>
       </c>
-      <c r="I217" t="inlineStr"/>
       <c r="J217" t="inlineStr">
         <is>
           <t>Positive</t>
@@ -30450,7 +28242,6 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="L217" t="inlineStr"/>
       <c r="M217" t="inlineStr">
         <is>
           <t>Service</t>
@@ -30459,7 +28250,6 @@
       <c r="N217" t="b">
         <v>0</v>
       </c>
-      <c r="O217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -30502,7 +28292,6 @@
           <t>Timeliness &amp; Wait Times</t>
         </is>
       </c>
-      <c r="I218" t="inlineStr"/>
       <c r="J218" t="inlineStr">
         <is>
           <t>Positive</t>
@@ -30513,7 +28302,6 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="L218" t="inlineStr"/>
       <c r="M218" t="inlineStr">
         <is>
           <t>Service</t>
@@ -30522,7 +28310,6 @@
       <c r="N218" t="b">
         <v>0</v>
       </c>
-      <c r="O218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -30565,7 +28352,6 @@
           <t>Pricing &amp; Charges</t>
         </is>
       </c>
-      <c r="I219" t="inlineStr"/>
       <c r="J219" t="inlineStr">
         <is>
           <t>Positive</t>
@@ -30576,7 +28362,6 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="L219" t="inlineStr"/>
       <c r="M219" t="inlineStr">
         <is>
           <t>Sales</t>
@@ -30585,7 +28370,6 @@
       <c r="N219" t="b">
         <v>0</v>
       </c>
-      <c r="O219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -30628,7 +28412,6 @@
           <t>Sales Process &amp; Handover</t>
         </is>
       </c>
-      <c r="I220" t="inlineStr"/>
       <c r="J220" t="inlineStr">
         <is>
           <t>Positive</t>
@@ -30639,7 +28422,6 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="L220" t="inlineStr"/>
       <c r="M220" t="inlineStr">
         <is>
           <t>Sales</t>
@@ -30648,7 +28430,6 @@
       <c r="N220" t="b">
         <v>0</v>
       </c>
-      <c r="O220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -30691,7 +28472,6 @@
           <t>Vehicle Knowledge &amp; Explanation</t>
         </is>
       </c>
-      <c r="I221" t="inlineStr"/>
       <c r="J221" t="inlineStr">
         <is>
           <t>Positive</t>
@@ -30702,7 +28482,6 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="L221" t="inlineStr"/>
       <c r="M221" t="inlineStr">
         <is>
           <t>Service</t>
@@ -30711,7 +28490,6 @@
       <c r="N221" t="b">
         <v>0</v>
       </c>
-      <c r="O221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -30754,7 +28532,6 @@
           <t>Communication &amp; Updates</t>
         </is>
       </c>
-      <c r="I222" t="inlineStr"/>
       <c r="J222" t="inlineStr">
         <is>
           <t>Positive</t>
@@ -30765,7 +28542,6 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="L222" t="inlineStr"/>
       <c r="M222" t="inlineStr">
         <is>
           <t>Sales</t>
@@ -30774,7 +28550,6 @@
       <c r="N222" t="b">
         <v>0</v>
       </c>
-      <c r="O222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -30817,7 +28592,6 @@
           <t>Staff Attitude &amp; Behaviour</t>
         </is>
       </c>
-      <c r="I223" t="inlineStr"/>
       <c r="J223" t="inlineStr">
         <is>
           <t>Positive</t>
@@ -30828,7 +28602,6 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="L223" t="inlineStr"/>
       <c r="M223" t="inlineStr">
         <is>
           <t>Service</t>
@@ -30837,7 +28610,6 @@
       <c r="N223" t="b">
         <v>0</v>
       </c>
-      <c r="O223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -30880,7 +28652,6 @@
           <t>Communication &amp; Updates</t>
         </is>
       </c>
-      <c r="I224" t="inlineStr"/>
       <c r="J224" t="inlineStr">
         <is>
           <t>Positive</t>
@@ -30891,7 +28662,6 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="L224" t="inlineStr"/>
       <c r="M224" t="inlineStr">
         <is>
           <t>Service</t>
@@ -30900,7 +28670,6 @@
       <c r="N224" t="b">
         <v>0</v>
       </c>
-      <c r="O224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -30943,7 +28712,6 @@
           <t>Pricing &amp; Charges</t>
         </is>
       </c>
-      <c r="I225" t="inlineStr"/>
       <c r="J225" t="inlineStr">
         <is>
           <t>Positive</t>
@@ -30954,7 +28722,6 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="L225" t="inlineStr"/>
       <c r="M225" t="inlineStr">
         <is>
           <t>Sales</t>
@@ -30963,7 +28730,6 @@
       <c r="N225" t="b">
         <v>0</v>
       </c>
-      <c r="O225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -31006,7 +28772,6 @@
           <t>Vehicle Knowledge &amp; Explanation</t>
         </is>
       </c>
-      <c r="I226" t="inlineStr"/>
       <c r="J226" t="inlineStr">
         <is>
           <t>Positive</t>
@@ -31017,7 +28782,6 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="L226" t="inlineStr"/>
       <c r="M226" t="inlineStr">
         <is>
           <t>Service</t>
@@ -31026,7 +28790,6 @@
       <c r="N226" t="b">
         <v>0</v>
       </c>
-      <c r="O226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -31069,7 +28832,6 @@
           <t>Staff Attitude &amp; Behaviour</t>
         </is>
       </c>
-      <c r="I227" t="inlineStr"/>
       <c r="J227" t="inlineStr">
         <is>
           <t>Positive</t>
@@ -31080,7 +28842,6 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="L227" t="inlineStr"/>
       <c r="M227" t="inlineStr">
         <is>
           <t>Service</t>
@@ -31089,7 +28850,6 @@
       <c r="N227" t="b">
         <v>0</v>
       </c>
-      <c r="O227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -31132,7 +28892,6 @@
           <t>Timeliness &amp; Wait Times</t>
         </is>
       </c>
-      <c r="I228" t="inlineStr"/>
       <c r="J228" t="inlineStr">
         <is>
           <t>Positive</t>
@@ -31143,7 +28902,6 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="L228" t="inlineStr"/>
       <c r="M228" t="inlineStr">
         <is>
           <t>Service</t>
@@ -31152,7 +28910,6 @@
       <c r="N228" t="b">
         <v>0</v>
       </c>
-      <c r="O228" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -31195,7 +28952,6 @@
           <t>Timeliness &amp; Wait Times</t>
         </is>
       </c>
-      <c r="I229" t="inlineStr"/>
       <c r="J229" t="inlineStr">
         <is>
           <t>Positive</t>
@@ -31206,7 +28962,6 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="L229" t="inlineStr"/>
       <c r="M229" t="inlineStr">
         <is>
           <t>Service</t>
@@ -31215,7 +28970,6 @@
       <c r="N229" t="b">
         <v>0</v>
       </c>
-      <c r="O229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -31258,7 +29012,6 @@
           <t>Vehicle Knowledge &amp; Explanation</t>
         </is>
       </c>
-      <c r="I230" t="inlineStr"/>
       <c r="J230" t="inlineStr">
         <is>
           <t>Positive</t>
@@ -31269,7 +29022,6 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="L230" t="inlineStr"/>
       <c r="M230" t="inlineStr">
         <is>
           <t>Sales</t>
@@ -31278,7 +29030,6 @@
       <c r="N230" t="b">
         <v>0</v>
       </c>
-      <c r="O230" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -31321,7 +29072,6 @@
           <t>Pricing &amp; Charges</t>
         </is>
       </c>
-      <c r="I231" t="inlineStr"/>
       <c r="J231" t="inlineStr">
         <is>
           <t>Positive</t>
@@ -31332,7 +29082,6 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="L231" t="inlineStr"/>
       <c r="M231" t="inlineStr">
         <is>
           <t>Parts</t>
@@ -31341,7 +29090,6 @@
       <c r="N231" t="b">
         <v>0</v>
       </c>
-      <c r="O231" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -31384,7 +29132,6 @@
           <t>Vehicle Knowledge &amp; Explanation</t>
         </is>
       </c>
-      <c r="I232" t="inlineStr"/>
       <c r="J232" t="inlineStr">
         <is>
           <t>Positive</t>
@@ -31395,7 +29142,6 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="L232" t="inlineStr"/>
       <c r="M232" t="inlineStr">
         <is>
           <t>Service</t>
@@ -31404,7 +29150,6 @@
       <c r="N232" t="b">
         <v>0</v>
       </c>
-      <c r="O232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -31447,7 +29192,6 @@
           <t>Vehicle Knowledge &amp; Explanation</t>
         </is>
       </c>
-      <c r="I233" t="inlineStr"/>
       <c r="J233" t="inlineStr">
         <is>
           <t>Positive</t>
@@ -31458,7 +29202,6 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="L233" t="inlineStr"/>
       <c r="M233" t="inlineStr">
         <is>
           <t>Sales</t>
@@ -31467,7 +29210,6 @@
       <c r="N233" t="b">
         <v>0</v>
       </c>
-      <c r="O233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -31510,7 +29252,6 @@
           <t>Timeliness &amp; Wait Times</t>
         </is>
       </c>
-      <c r="I234" t="inlineStr"/>
       <c r="J234" t="inlineStr">
         <is>
           <t>Positive</t>
@@ -31521,7 +29262,6 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="L234" t="inlineStr"/>
       <c r="M234" t="inlineStr">
         <is>
           <t>Service</t>
@@ -31530,7 +29270,6 @@
       <c r="N234" t="b">
         <v>0</v>
       </c>
-      <c r="O234" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -31573,7 +29312,6 @@
           <t>Vehicle Knowledge &amp; Explanation</t>
         </is>
       </c>
-      <c r="I235" t="inlineStr"/>
       <c r="J235" t="inlineStr">
         <is>
           <t>Positive</t>
@@ -31584,7 +29322,6 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="L235" t="inlineStr"/>
       <c r="M235" t="inlineStr">
         <is>
           <t>Service</t>
@@ -31593,7 +29330,6 @@
       <c r="N235" t="b">
         <v>0</v>
       </c>
-      <c r="O235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -31636,7 +29372,6 @@
           <t>Timeliness &amp; Wait Times</t>
         </is>
       </c>
-      <c r="I236" t="inlineStr"/>
       <c r="J236" t="inlineStr">
         <is>
           <t>Positive</t>
@@ -31647,7 +29382,6 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="L236" t="inlineStr"/>
       <c r="M236" t="inlineStr">
         <is>
           <t>Service</t>
@@ -31656,7 +29390,6 @@
       <c r="N236" t="b">
         <v>0</v>
       </c>
-      <c r="O236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -31699,7 +29432,6 @@
           <t>Vehicle Knowledge &amp; Explanation</t>
         </is>
       </c>
-      <c r="I237" t="inlineStr"/>
       <c r="J237" t="inlineStr">
         <is>
           <t>Positive</t>
@@ -31710,7 +29442,6 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="L237" t="inlineStr"/>
       <c r="M237" t="inlineStr">
         <is>
           <t>Service</t>
@@ -31719,7 +29450,6 @@
       <c r="N237" t="b">
         <v>0</v>
       </c>
-      <c r="O237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -31762,7 +29492,6 @@
           <t>Staff Attitude &amp; Behaviour</t>
         </is>
       </c>
-      <c r="I238" t="inlineStr"/>
       <c r="J238" t="inlineStr">
         <is>
           <t>Positive</t>
@@ -31773,7 +29502,6 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="L238" t="inlineStr"/>
       <c r="M238" t="inlineStr">
         <is>
           <t>Service</t>
@@ -31782,7 +29510,6 @@
       <c r="N238" t="b">
         <v>0</v>
       </c>
-      <c r="O238" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -31825,7 +29552,6 @@
           <t>Staff Attitude &amp; Behaviour</t>
         </is>
       </c>
-      <c r="I239" t="inlineStr"/>
       <c r="J239" t="inlineStr">
         <is>
           <t>Positive</t>
@@ -31836,7 +29562,6 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="L239" t="inlineStr"/>
       <c r="M239" t="inlineStr">
         <is>
           <t>Service</t>
@@ -31845,7 +29570,6 @@
       <c r="N239" t="b">
         <v>0</v>
       </c>
-      <c r="O239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -31888,7 +29612,6 @@
           <t>Staff Attitude &amp; Behaviour</t>
         </is>
       </c>
-      <c r="I240" t="inlineStr"/>
       <c r="J240" t="inlineStr">
         <is>
           <t>Positive</t>
@@ -31899,7 +29622,6 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="L240" t="inlineStr"/>
       <c r="M240" t="inlineStr">
         <is>
           <t>Service</t>
@@ -31908,7 +29630,6 @@
       <c r="N240" t="b">
         <v>0</v>
       </c>
-      <c r="O240" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -31951,7 +29672,6 @@
           <t>Staff Attitude &amp; Behaviour</t>
         </is>
       </c>
-      <c r="I241" t="inlineStr"/>
       <c r="J241" t="inlineStr">
         <is>
           <t>Positive</t>
@@ -31962,7 +29682,6 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="L241" t="inlineStr"/>
       <c r="M241" t="inlineStr">
         <is>
           <t>Sales</t>
@@ -31971,7 +29690,6 @@
       <c r="N241" t="b">
         <v>0</v>
       </c>
-      <c r="O241" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -32014,7 +29732,6 @@
           <t>Pricing &amp; Charges</t>
         </is>
       </c>
-      <c r="I242" t="inlineStr"/>
       <c r="J242" t="inlineStr">
         <is>
           <t>Positive</t>
@@ -32025,7 +29742,6 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="L242" t="inlineStr"/>
       <c r="M242" t="inlineStr">
         <is>
           <t>Service</t>
@@ -32034,7 +29750,6 @@
       <c r="N242" t="b">
         <v>0</v>
       </c>
-      <c r="O242" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -32077,7 +29792,6 @@
           <t>Pricing &amp; Charges</t>
         </is>
       </c>
-      <c r="I243" t="inlineStr"/>
       <c r="J243" t="inlineStr">
         <is>
           <t>Positive</t>
@@ -32088,7 +29802,6 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="L243" t="inlineStr"/>
       <c r="M243" t="inlineStr">
         <is>
           <t>Parts</t>
@@ -32097,7 +29810,6 @@
       <c r="N243" t="b">
         <v>0</v>
       </c>
-      <c r="O243" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -32140,7 +29852,6 @@
           <t>Timeliness &amp; Wait Times</t>
         </is>
       </c>
-      <c r="I244" t="inlineStr"/>
       <c r="J244" t="inlineStr">
         <is>
           <t>Positive</t>
@@ -32151,7 +29862,6 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="L244" t="inlineStr"/>
       <c r="M244" t="inlineStr">
         <is>
           <t>Parts</t>
@@ -32160,7 +29870,6 @@
       <c r="N244" t="b">
         <v>0</v>
       </c>
-      <c r="O244" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -32203,7 +29912,6 @@
           <t>Communication &amp; Updates</t>
         </is>
       </c>
-      <c r="I245" t="inlineStr"/>
       <c r="J245" t="inlineStr">
         <is>
           <t>Positive</t>
@@ -32214,7 +29922,6 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="L245" t="inlineStr"/>
       <c r="M245" t="inlineStr">
         <is>
           <t>Service</t>
@@ -32223,7 +29930,6 @@
       <c r="N245" t="b">
         <v>0</v>
       </c>
-      <c r="O245" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -32266,7 +29972,6 @@
           <t>Positive Experience (General)</t>
         </is>
       </c>
-      <c r="I246" t="inlineStr"/>
       <c r="J246" t="inlineStr">
         <is>
           <t>Positive</t>
@@ -32277,7 +29982,6 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="L246" t="inlineStr"/>
       <c r="M246" t="inlineStr">
         <is>
           <t>Service</t>
@@ -32286,7 +29990,6 @@
       <c r="N246" t="b">
         <v>0</v>
       </c>
-      <c r="O246" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -32329,7 +30032,6 @@
           <t>Staff Attitude &amp; Behaviour</t>
         </is>
       </c>
-      <c r="I247" t="inlineStr"/>
       <c r="J247" t="inlineStr">
         <is>
           <t>Positive</t>
@@ -32340,7 +30042,6 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="L247" t="inlineStr"/>
       <c r="M247" t="inlineStr">
         <is>
           <t>Service</t>
@@ -32349,7 +30050,6 @@
       <c r="N247" t="b">
         <v>0</v>
       </c>
-      <c r="O247" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -32392,7 +30092,6 @@
           <t>Vehicle Knowledge &amp; Explanation</t>
         </is>
       </c>
-      <c r="I248" t="inlineStr"/>
       <c r="J248" t="inlineStr">
         <is>
           <t>Positive</t>
@@ -32403,7 +30102,6 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="L248" t="inlineStr"/>
       <c r="M248" t="inlineStr">
         <is>
           <t>Service</t>
@@ -32412,7 +30110,6 @@
       <c r="N248" t="b">
         <v>0</v>
       </c>
-      <c r="O248" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -32455,7 +30152,6 @@
           <t>Pricing &amp; Charges</t>
         </is>
       </c>
-      <c r="I249" t="inlineStr"/>
       <c r="J249" t="inlineStr">
         <is>
           <t>Positive</t>
@@ -32466,7 +30162,6 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="L249" t="inlineStr"/>
       <c r="M249" t="inlineStr">
         <is>
           <t>Service</t>
@@ -32475,7 +30170,6 @@
       <c r="N249" t="b">
         <v>0</v>
       </c>
-      <c r="O249" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -32518,7 +30212,6 @@
           <t>Positive Experience (General)</t>
         </is>
       </c>
-      <c r="I250" t="inlineStr"/>
       <c r="J250" t="inlineStr">
         <is>
           <t>Positive</t>
@@ -32529,7 +30222,6 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="L250" t="inlineStr"/>
       <c r="M250" t="inlineStr">
         <is>
           <t>Sales</t>
@@ -32538,7 +30230,6 @@
       <c r="N250" t="b">
         <v>0</v>
       </c>
-      <c r="O250" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -32581,7 +30272,6 @@
           <t>Timeliness &amp; Wait Times</t>
         </is>
       </c>
-      <c r="I251" t="inlineStr"/>
       <c r="J251" t="inlineStr">
         <is>
           <t>Positive</t>
@@ -32592,7 +30282,6 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="L251" t="inlineStr"/>
       <c r="M251" t="inlineStr">
         <is>
           <t>Service</t>
@@ -32601,7 +30290,6 @@
       <c r="N251" t="b">
         <v>0</v>
       </c>
-      <c r="O251" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -32644,7 +30332,6 @@
           <t>Staff Attitude &amp; Behaviour</t>
         </is>
       </c>
-      <c r="I252" t="inlineStr"/>
       <c r="J252" t="inlineStr">
         <is>
           <t>Positive</t>
@@ -32655,7 +30342,6 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="L252" t="inlineStr"/>
       <c r="M252" t="inlineStr">
         <is>
           <t>Service</t>
@@ -32664,7 +30350,6 @@
       <c r="N252" t="b">
         <v>0</v>
       </c>
-      <c r="O252" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -32707,7 +30392,6 @@
           <t>Staff Attitude &amp; Behaviour</t>
         </is>
       </c>
-      <c r="I253" t="inlineStr"/>
       <c r="J253" t="inlineStr">
         <is>
           <t>Positive</t>
@@ -32718,7 +30402,6 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="L253" t="inlineStr"/>
       <c r="M253" t="inlineStr">
         <is>
           <t>Service</t>
@@ -32727,7 +30410,6 @@
       <c r="N253" t="b">
         <v>0</v>
       </c>
-      <c r="O253" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -32770,7 +30452,6 @@
           <t>Pricing &amp; Charges</t>
         </is>
       </c>
-      <c r="I254" t="inlineStr"/>
       <c r="J254" t="inlineStr">
         <is>
           <t>Positive</t>
@@ -32781,7 +30462,6 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="L254" t="inlineStr"/>
       <c r="M254" t="inlineStr">
         <is>
           <t>Service</t>
@@ -32790,7 +30470,6 @@
       <c r="N254" t="b">
         <v>0</v>
       </c>
-      <c r="O254" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -32833,7 +30512,6 @@
           <t>Timeliness &amp; Wait Times</t>
         </is>
       </c>
-      <c r="I255" t="inlineStr"/>
       <c r="J255" t="inlineStr">
         <is>
           <t>Positive</t>
@@ -32844,7 +30522,6 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="L255" t="inlineStr"/>
       <c r="M255" t="inlineStr">
         <is>
           <t>Service</t>
@@ -32853,7 +30530,6 @@
       <c r="N255" t="b">
         <v>0</v>
       </c>
-      <c r="O255" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -32896,7 +30572,6 @@
           <t>Timeliness &amp; Wait Times</t>
         </is>
       </c>
-      <c r="I256" t="inlineStr"/>
       <c r="J256" t="inlineStr">
         <is>
           <t>Positive</t>
@@ -32907,7 +30582,6 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="L256" t="inlineStr"/>
       <c r="M256" t="inlineStr">
         <is>
           <t>Service</t>
@@ -32916,7 +30590,6 @@
       <c r="N256" t="b">
         <v>0</v>
       </c>
-      <c r="O256" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -32959,7 +30632,6 @@
           <t>Parts Availability &amp; Delays</t>
         </is>
       </c>
-      <c r="I257" t="inlineStr"/>
       <c r="J257" t="inlineStr">
         <is>
           <t>Positive</t>
@@ -32970,7 +30642,6 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="L257" t="inlineStr"/>
       <c r="M257" t="inlineStr">
         <is>
           <t>Parts</t>
@@ -32979,7 +30650,6 @@
       <c r="N257" t="b">
         <v>0</v>
       </c>
-      <c r="O257" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -33022,7 +30692,6 @@
           <t>Positive Experience (General)</t>
         </is>
       </c>
-      <c r="I258" t="inlineStr"/>
       <c r="J258" t="inlineStr">
         <is>
           <t>Positive</t>
@@ -33033,7 +30702,6 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="L258" t="inlineStr"/>
       <c r="M258" t="inlineStr">
         <is>
           <t>Service</t>
@@ -33042,7 +30710,6 @@
       <c r="N258" t="b">
         <v>0</v>
       </c>
-      <c r="O258" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -33085,7 +30752,6 @@
           <t>Communication &amp; Updates</t>
         </is>
       </c>
-      <c r="I259" t="inlineStr"/>
       <c r="J259" t="inlineStr">
         <is>
           <t>Positive</t>
@@ -33096,7 +30762,6 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="L259" t="inlineStr"/>
       <c r="M259" t="inlineStr">
         <is>
           <t>Service</t>
@@ -33105,7 +30770,6 @@
       <c r="N259" t="b">
         <v>0</v>
       </c>
-      <c r="O259" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -33148,7 +30812,6 @@
           <t>Pricing &amp; Charges</t>
         </is>
       </c>
-      <c r="I260" t="inlineStr"/>
       <c r="J260" t="inlineStr">
         <is>
           <t>Positive</t>
@@ -33159,7 +30822,6 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="L260" t="inlineStr"/>
       <c r="M260" t="inlineStr">
         <is>
           <t>Service</t>
@@ -33168,7 +30830,6 @@
       <c r="N260" t="b">
         <v>0</v>
       </c>
-      <c r="O260" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -33211,7 +30872,6 @@
           <t>Vehicle Knowledge &amp; Explanation</t>
         </is>
       </c>
-      <c r="I261" t="inlineStr"/>
       <c r="J261" t="inlineStr">
         <is>
           <t>Positive</t>
@@ -33222,7 +30882,6 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="L261" t="inlineStr"/>
       <c r="M261" t="inlineStr">
         <is>
           <t>Service</t>
@@ -33231,7 +30890,6 @@
       <c r="N261" t="b">
         <v>0</v>
       </c>
-      <c r="O261" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -33274,7 +30932,6 @@
           <t>Vehicle Knowledge &amp; Explanation</t>
         </is>
       </c>
-      <c r="I262" t="inlineStr"/>
       <c r="J262" t="inlineStr">
         <is>
           <t>Positive</t>
@@ -33285,7 +30942,6 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="L262" t="inlineStr"/>
       <c r="M262" t="inlineStr">
         <is>
           <t>Service</t>
@@ -33294,7 +30950,6 @@
       <c r="N262" t="b">
         <v>0</v>
       </c>
-      <c r="O262" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -33337,7 +30992,6 @@
           <t>Timeliness &amp; Wait Times</t>
         </is>
       </c>
-      <c r="I263" t="inlineStr"/>
       <c r="J263" t="inlineStr">
         <is>
           <t>Positive</t>
@@ -33348,7 +31002,6 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="L263" t="inlineStr"/>
       <c r="M263" t="inlineStr">
         <is>
           <t>Service</t>
@@ -33357,7 +31010,6 @@
       <c r="N263" t="b">
         <v>0</v>
       </c>
-      <c r="O263" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -33400,7 +31052,6 @@
           <t>Vehicle Knowledge &amp; Explanation</t>
         </is>
       </c>
-      <c r="I264" t="inlineStr"/>
       <c r="J264" t="inlineStr">
         <is>
           <t>Positive</t>
@@ -33411,7 +31062,6 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="L264" t="inlineStr"/>
       <c r="M264" t="inlineStr">
         <is>
           <t>Service</t>
@@ -33420,7 +31070,6 @@
       <c r="N264" t="b">
         <v>0</v>
       </c>
-      <c r="O264" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -33463,7 +31112,6 @@
           <t>Parts Availability &amp; Delays</t>
         </is>
       </c>
-      <c r="I265" t="inlineStr"/>
       <c r="J265" t="inlineStr">
         <is>
           <t>Neutral</t>
@@ -33474,7 +31122,6 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="L265" t="inlineStr"/>
       <c r="M265" t="inlineStr">
         <is>
           <t>Service</t>
@@ -33483,7 +31130,6 @@
       <c r="N265" t="b">
         <v>0</v>
       </c>
-      <c r="O265" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -33526,7 +31172,6 @@
           <t>Vehicle Knowledge &amp; Explanation</t>
         </is>
       </c>
-      <c r="I266" t="inlineStr"/>
       <c r="J266" t="inlineStr">
         <is>
           <t>Positive</t>
@@ -33537,7 +31182,6 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="L266" t="inlineStr"/>
       <c r="M266" t="inlineStr">
         <is>
           <t>Service</t>
@@ -33546,7 +31190,6 @@
       <c r="N266" t="b">
         <v>0</v>
       </c>
-      <c r="O266" t="inlineStr"/>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -33589,7 +31232,6 @@
           <t>Pricing &amp; Charges</t>
         </is>
       </c>
-      <c r="I267" t="inlineStr"/>
       <c r="J267" t="inlineStr">
         <is>
           <t>Positive</t>
@@ -33600,7 +31242,6 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="L267" t="inlineStr"/>
       <c r="M267" t="inlineStr">
         <is>
           <t>Service</t>
@@ -33609,7 +31250,6 @@
       <c r="N267" t="b">
         <v>0</v>
       </c>
-      <c r="O267" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -33652,7 +31292,6 @@
           <t>Positive Experience (General)</t>
         </is>
       </c>
-      <c r="I268" t="inlineStr"/>
       <c r="J268" t="inlineStr">
         <is>
           <t>Positive</t>
@@ -33663,7 +31302,6 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="L268" t="inlineStr"/>
       <c r="M268" t="inlineStr">
         <is>
           <t>Unknown</t>
@@ -33672,7 +31310,6 @@
       <c r="N268" t="b">
         <v>0</v>
       </c>
-      <c r="O268" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -33715,7 +31352,6 @@
           <t>Sales Process &amp; Handover</t>
         </is>
       </c>
-      <c r="I269" t="inlineStr"/>
       <c r="J269" t="inlineStr">
         <is>
           <t>Positive</t>
@@ -33726,7 +31362,6 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="L269" t="inlineStr"/>
       <c r="M269" t="inlineStr">
         <is>
           <t>Sales</t>
@@ -33735,7 +31370,6 @@
       <c r="N269" t="b">
         <v>0</v>
       </c>
-      <c r="O269" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -33778,7 +31412,6 @@
           <t>Timeliness &amp; Wait Times</t>
         </is>
       </c>
-      <c r="I270" t="inlineStr"/>
       <c r="J270" t="inlineStr">
         <is>
           <t>Positive</t>
@@ -33789,7 +31422,6 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="L270" t="inlineStr"/>
       <c r="M270" t="inlineStr">
         <is>
           <t>Parts</t>
@@ -33798,7 +31430,6 @@
       <c r="N270" t="b">
         <v>0</v>
       </c>
-      <c r="O270" t="inlineStr"/>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -33841,7 +31472,6 @@
           <t>Timeliness &amp; Wait Times</t>
         </is>
       </c>
-      <c r="I271" t="inlineStr"/>
       <c r="J271" t="inlineStr">
         <is>
           <t>Positive</t>
@@ -33852,7 +31482,6 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="L271" t="inlineStr"/>
       <c r="M271" t="inlineStr">
         <is>
           <t>Service</t>
@@ -33861,7 +31490,6 @@
       <c r="N271" t="b">
         <v>0</v>
       </c>
-      <c r="O271" t="inlineStr"/>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -33904,7 +31532,6 @@
           <t>Positive Experience (General)</t>
         </is>
       </c>
-      <c r="I272" t="inlineStr"/>
       <c r="J272" t="inlineStr">
         <is>
           <t>Positive</t>
@@ -33915,7 +31542,6 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="L272" t="inlineStr"/>
       <c r="M272" t="inlineStr">
         <is>
           <t>Service</t>
@@ -33924,7 +31550,6 @@
       <c r="N272" t="b">
         <v>0</v>
       </c>
-      <c r="O272" t="inlineStr"/>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -33967,7 +31592,6 @@
           <t>Staff Attitude &amp; Behaviour</t>
         </is>
       </c>
-      <c r="I273" t="inlineStr"/>
       <c r="J273" t="inlineStr">
         <is>
           <t>Positive</t>
@@ -33978,7 +31602,6 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="L273" t="inlineStr"/>
       <c r="M273" t="inlineStr">
         <is>
           <t>Service</t>
@@ -33987,7 +31610,6 @@
       <c r="N273" t="b">
         <v>0</v>
       </c>
-      <c r="O273" t="inlineStr"/>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -34030,7 +31652,6 @@
           <t>Staff Attitude &amp; Behaviour</t>
         </is>
       </c>
-      <c r="I274" t="inlineStr"/>
       <c r="J274" t="inlineStr">
         <is>
           <t>Positive</t>
@@ -34041,7 +31662,6 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="L274" t="inlineStr"/>
       <c r="M274" t="inlineStr">
         <is>
           <t>Service</t>
@@ -34050,7 +31670,6 @@
       <c r="N274" t="b">
         <v>0</v>
       </c>
-      <c r="O274" t="inlineStr"/>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -34093,7 +31712,6 @@
           <t>Positive Experience (General)</t>
         </is>
       </c>
-      <c r="I275" t="inlineStr"/>
       <c r="J275" t="inlineStr">
         <is>
           <t>Positive</t>
@@ -34104,7 +31722,6 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="L275" t="inlineStr"/>
       <c r="M275" t="inlineStr">
         <is>
           <t>Service</t>
@@ -34113,7 +31730,6 @@
       <c r="N275" t="b">
         <v>0</v>
       </c>
-      <c r="O275" t="inlineStr"/>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -34156,7 +31772,6 @@
           <t>Pricing &amp; Charges</t>
         </is>
       </c>
-      <c r="I276" t="inlineStr"/>
       <c r="J276" t="inlineStr">
         <is>
           <t>Positive</t>
@@ -34167,7 +31782,6 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="L276" t="inlineStr"/>
       <c r="M276" t="inlineStr">
         <is>
           <t>Service</t>
@@ -34176,7 +31790,6 @@
       <c r="N276" t="b">
         <v>0</v>
       </c>
-      <c r="O276" t="inlineStr"/>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -34219,7 +31832,6 @@
           <t>Staff Attitude &amp; Behaviour</t>
         </is>
       </c>
-      <c r="I277" t="inlineStr"/>
       <c r="J277" t="inlineStr">
         <is>
           <t>Positive</t>
@@ -34230,7 +31842,6 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="L277" t="inlineStr"/>
       <c r="M277" t="inlineStr">
         <is>
           <t>Parts</t>
@@ -34239,7 +31850,6 @@
       <c r="N277" t="b">
         <v>0</v>
       </c>
-      <c r="O277" t="inlineStr"/>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -34282,7 +31892,6 @@
           <t>Staff Attitude &amp; Behaviour</t>
         </is>
       </c>
-      <c r="I278" t="inlineStr"/>
       <c r="J278" t="inlineStr">
         <is>
           <t>Positive</t>
@@ -34293,7 +31902,6 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="L278" t="inlineStr"/>
       <c r="M278" t="inlineStr">
         <is>
           <t>Service</t>
@@ -34302,7 +31910,6 @@
       <c r="N278" t="b">
         <v>0</v>
       </c>
-      <c r="O278" t="inlineStr"/>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -34345,7 +31952,6 @@
           <t>Staff Attitude &amp; Behaviour</t>
         </is>
       </c>
-      <c r="I279" t="inlineStr"/>
       <c r="J279" t="inlineStr">
         <is>
           <t>Positive</t>
@@ -34356,7 +31962,6 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="L279" t="inlineStr"/>
       <c r="M279" t="inlineStr">
         <is>
           <t>Service</t>
@@ -34365,7 +31970,6 @@
       <c r="N279" t="b">
         <v>0</v>
       </c>
-      <c r="O279" t="inlineStr"/>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -34408,7 +32012,6 @@
           <t>Vehicle Knowledge &amp; Explanation</t>
         </is>
       </c>
-      <c r="I280" t="inlineStr"/>
       <c r="J280" t="inlineStr">
         <is>
           <t>Positive</t>
@@ -34419,7 +32022,6 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="L280" t="inlineStr"/>
       <c r="M280" t="inlineStr">
         <is>
           <t>Service</t>
@@ -34428,7 +32030,6 @@
       <c r="N280" t="b">
         <v>0</v>
       </c>
-      <c r="O280" t="inlineStr"/>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -34471,7 +32072,6 @@
           <t>Vehicle Knowledge &amp; Explanation</t>
         </is>
       </c>
-      <c r="I281" t="inlineStr"/>
       <c r="J281" t="inlineStr">
         <is>
           <t>Positive</t>
@@ -34482,7 +32082,6 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="L281" t="inlineStr"/>
       <c r="M281" t="inlineStr">
         <is>
           <t>Service</t>
@@ -34491,7 +32090,6 @@
       <c r="N281" t="b">
         <v>0</v>
       </c>
-      <c r="O281" t="inlineStr"/>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -34534,7 +32132,6 @@
           <t>Communication &amp; Updates</t>
         </is>
       </c>
-      <c r="I282" t="inlineStr"/>
       <c r="J282" t="inlineStr">
         <is>
           <t>Positive</t>
@@ -34545,7 +32142,6 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="L282" t="inlineStr"/>
       <c r="M282" t="inlineStr">
         <is>
           <t>Service</t>
@@ -34554,7 +32150,6 @@
       <c r="N282" t="b">
         <v>0</v>
       </c>
-      <c r="O282" t="inlineStr"/>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -34597,7 +32192,6 @@
           <t>Communication &amp; Updates</t>
         </is>
       </c>
-      <c r="I283" t="inlineStr"/>
       <c r="J283" t="inlineStr">
         <is>
           <t>Positive</t>
@@ -34608,7 +32202,6 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="L283" t="inlineStr"/>
       <c r="M283" t="inlineStr">
         <is>
           <t>Service</t>
@@ -34617,7 +32210,6 @@
       <c r="N283" t="b">
         <v>0</v>
       </c>
-      <c r="O283" t="inlineStr"/>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -34660,7 +32252,6 @@
           <t>Pricing &amp; Charges</t>
         </is>
       </c>
-      <c r="I284" t="inlineStr"/>
       <c r="J284" t="inlineStr">
         <is>
           <t>Positive</t>
@@ -34671,7 +32262,6 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="L284" t="inlineStr"/>
       <c r="M284" t="inlineStr">
         <is>
           <t>Parts</t>
@@ -34680,7 +32270,6 @@
       <c r="N284" t="b">
         <v>0</v>
       </c>
-      <c r="O284" t="inlineStr"/>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -34723,7 +32312,6 @@
           <t>Staff Attitude &amp; Behaviour</t>
         </is>
       </c>
-      <c r="I285" t="inlineStr"/>
       <c r="J285" t="inlineStr">
         <is>
           <t>Positive</t>
@@ -34734,7 +32322,6 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="L285" t="inlineStr"/>
       <c r="M285" t="inlineStr">
         <is>
           <t>Service</t>
@@ -34743,7 +32330,6 @@
       <c r="N285" t="b">
         <v>0</v>
       </c>
-      <c r="O285" t="inlineStr"/>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -34786,7 +32372,6 @@
           <t>Timeliness &amp; Wait Times</t>
         </is>
       </c>
-      <c r="I286" t="inlineStr"/>
       <c r="J286" t="inlineStr">
         <is>
           <t>Positive</t>
@@ -34797,7 +32382,6 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="L286" t="inlineStr"/>
       <c r="M286" t="inlineStr">
         <is>
           <t>Service</t>
@@ -34806,7 +32390,6 @@
       <c r="N286" t="b">
         <v>0</v>
       </c>
-      <c r="O286" t="inlineStr"/>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -34849,7 +32432,6 @@
           <t>Timeliness &amp; Wait Times</t>
         </is>
       </c>
-      <c r="I287" t="inlineStr"/>
       <c r="J287" t="inlineStr">
         <is>
           <t>Positive</t>
@@ -34860,7 +32442,6 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="L287" t="inlineStr"/>
       <c r="M287" t="inlineStr">
         <is>
           <t>Service</t>
@@ -34869,7 +32450,6 @@
       <c r="N287" t="b">
         <v>0</v>
       </c>
-      <c r="O287" t="inlineStr"/>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -34912,7 +32492,6 @@
           <t>Sales Process &amp; Handover</t>
         </is>
       </c>
-      <c r="I288" t="inlineStr"/>
       <c r="J288" t="inlineStr">
         <is>
           <t>Positive</t>
@@ -34923,7 +32502,6 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="L288" t="inlineStr"/>
       <c r="M288" t="inlineStr">
         <is>
           <t>Sales</t>
@@ -34932,7 +32510,6 @@
       <c r="N288" t="b">
         <v>0</v>
       </c>
-      <c r="O288" t="inlineStr"/>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -34975,7 +32552,6 @@
           <t>Staff Attitude &amp; Behaviour</t>
         </is>
       </c>
-      <c r="I289" t="inlineStr"/>
       <c r="J289" t="inlineStr">
         <is>
           <t>Positive</t>
@@ -34986,7 +32562,6 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="L289" t="inlineStr"/>
       <c r="M289" t="inlineStr">
         <is>
           <t>Sales</t>
@@ -34995,7 +32570,6 @@
       <c r="N289" t="b">
         <v>0</v>
       </c>
-      <c r="O289" t="inlineStr"/>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -35038,7 +32612,6 @@
           <t>Staff Attitude &amp; Behaviour</t>
         </is>
       </c>
-      <c r="I290" t="inlineStr"/>
       <c r="J290" t="inlineStr">
         <is>
           <t>Positive</t>
@@ -35049,7 +32622,6 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="L290" t="inlineStr"/>
       <c r="M290" t="inlineStr">
         <is>
           <t>Sales</t>
@@ -35058,7 +32630,6 @@
       <c r="N290" t="b">
         <v>0</v>
       </c>
-      <c r="O290" t="inlineStr"/>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -35101,7 +32672,6 @@
           <t>Staff Attitude &amp; Behaviour</t>
         </is>
       </c>
-      <c r="I291" t="inlineStr"/>
       <c r="J291" t="inlineStr">
         <is>
           <t>Positive</t>
@@ -35112,7 +32682,6 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="L291" t="inlineStr"/>
       <c r="M291" t="inlineStr">
         <is>
           <t>Service</t>
@@ -35121,7 +32690,6 @@
       <c r="N291" t="b">
         <v>0</v>
       </c>
-      <c r="O291" t="inlineStr"/>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -35164,7 +32732,6 @@
           <t>Communication &amp; Updates</t>
         </is>
       </c>
-      <c r="I292" t="inlineStr"/>
       <c r="J292" t="inlineStr">
         <is>
           <t>Positive</t>
@@ -35175,7 +32742,6 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="L292" t="inlineStr"/>
       <c r="M292" t="inlineStr">
         <is>
           <t>Service</t>
@@ -35184,7 +32750,6 @@
       <c r="N292" t="b">
         <v>0</v>
       </c>
-      <c r="O292" t="inlineStr"/>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -35227,7 +32792,6 @@
           <t>Vehicle Knowledge &amp; Explanation</t>
         </is>
       </c>
-      <c r="I293" t="inlineStr"/>
       <c r="J293" t="inlineStr">
         <is>
           <t>Positive</t>
@@ -35238,7 +32802,6 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="L293" t="inlineStr"/>
       <c r="M293" t="inlineStr">
         <is>
           <t>Service</t>
@@ -35247,7 +32810,6 @@
       <c r="N293" t="b">
         <v>0</v>
       </c>
-      <c r="O293" t="inlineStr"/>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -35290,7 +32852,6 @@
           <t>Timeliness &amp; Wait Times</t>
         </is>
       </c>
-      <c r="I294" t="inlineStr"/>
       <c r="J294" t="inlineStr">
         <is>
           <t>Positive</t>
@@ -35301,7 +32862,6 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="L294" t="inlineStr"/>
       <c r="M294" t="inlineStr">
         <is>
           <t>Service</t>
@@ -35310,7 +32870,6 @@
       <c r="N294" t="b">
         <v>0</v>
       </c>
-      <c r="O294" t="inlineStr"/>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -35353,7 +32912,6 @@
           <t>Staff Attitude &amp; Behaviour</t>
         </is>
       </c>
-      <c r="I295" t="inlineStr"/>
       <c r="J295" t="inlineStr">
         <is>
           <t>Positive</t>
@@ -35364,7 +32922,6 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="L295" t="inlineStr"/>
       <c r="M295" t="inlineStr">
         <is>
           <t>Service</t>
@@ -35373,7 +32930,6 @@
       <c r="N295" t="b">
         <v>0</v>
       </c>
-      <c r="O295" t="inlineStr"/>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -35416,7 +32972,6 @@
           <t>Timeliness &amp; Wait Times</t>
         </is>
       </c>
-      <c r="I296" t="inlineStr"/>
       <c r="J296" t="inlineStr">
         <is>
           <t>Positive</t>
@@ -35427,7 +32982,6 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="L296" t="inlineStr"/>
       <c r="M296" t="inlineStr">
         <is>
           <t>Service</t>
@@ -35436,7 +32990,6 @@
       <c r="N296" t="b">
         <v>0</v>
       </c>
-      <c r="O296" t="inlineStr"/>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -35479,7 +33032,6 @@
           <t>Vehicle Knowledge &amp; Explanation</t>
         </is>
       </c>
-      <c r="I297" t="inlineStr"/>
       <c r="J297" t="inlineStr">
         <is>
           <t>Positive</t>
@@ -35490,7 +33042,6 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="L297" t="inlineStr"/>
       <c r="M297" t="inlineStr">
         <is>
           <t>Service</t>
@@ -35499,7 +33050,6 @@
       <c r="N297" t="b">
         <v>0</v>
       </c>
-      <c r="O297" t="inlineStr"/>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -35542,7 +33092,6 @@
           <t>Pricing &amp; Charges</t>
         </is>
       </c>
-      <c r="I298" t="inlineStr"/>
       <c r="J298" t="inlineStr">
         <is>
           <t>Positive</t>
@@ -35553,7 +33102,6 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="L298" t="inlineStr"/>
       <c r="M298" t="inlineStr">
         <is>
           <t>Parts</t>
@@ -35562,7 +33110,6 @@
       <c r="N298" t="b">
         <v>0</v>
       </c>
-      <c r="O298" t="inlineStr"/>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -35605,7 +33152,6 @@
           <t>Communication &amp; Updates</t>
         </is>
       </c>
-      <c r="I299" t="inlineStr"/>
       <c r="J299" t="inlineStr">
         <is>
           <t>Positive</t>
@@ -35616,7 +33162,6 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="L299" t="inlineStr"/>
       <c r="M299" t="inlineStr">
         <is>
           <t>Service</t>
@@ -35625,7 +33170,6 @@
       <c r="N299" t="b">
         <v>0</v>
       </c>
-      <c r="O299" t="inlineStr"/>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -35668,7 +33212,6 @@
           <t>Staff Attitude &amp; Behaviour</t>
         </is>
       </c>
-      <c r="I300" t="inlineStr"/>
       <c r="J300" t="inlineStr">
         <is>
           <t>Positive</t>
@@ -35679,7 +33222,6 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="L300" t="inlineStr"/>
       <c r="M300" t="inlineStr">
         <is>
           <t>Sales</t>
@@ -35688,7 +33230,6 @@
       <c r="N300" t="b">
         <v>0</v>
       </c>
-      <c r="O300" t="inlineStr"/>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -35731,7 +33272,6 @@
           <t>Staff Attitude &amp; Behaviour</t>
         </is>
       </c>
-      <c r="I301" t="inlineStr"/>
       <c r="J301" t="inlineStr">
         <is>
           <t>Positive</t>
@@ -35742,7 +33282,6 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="L301" t="inlineStr"/>
       <c r="M301" t="inlineStr">
         <is>
           <t>Sales</t>
@@ -35751,7 +33290,6 @@
       <c r="N301" t="b">
         <v>0</v>
       </c>
-      <c r="O301" t="inlineStr"/>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -35794,7 +33332,6 @@
           <t>Staff Attitude &amp; Behaviour</t>
         </is>
       </c>
-      <c r="I302" t="inlineStr"/>
       <c r="J302" t="inlineStr">
         <is>
           <t>Positive</t>
@@ -35805,7 +33342,6 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="L302" t="inlineStr"/>
       <c r="M302" t="inlineStr">
         <is>
           <t>Service</t>
@@ -35814,7 +33350,6 @@
       <c r="N302" t="b">
         <v>0</v>
       </c>
-      <c r="O302" t="inlineStr"/>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -35857,7 +33392,6 @@
           <t>Positive Experience (General)</t>
         </is>
       </c>
-      <c r="I303" t="inlineStr"/>
       <c r="J303" t="inlineStr">
         <is>
           <t>Positive</t>
@@ -35868,7 +33402,6 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="L303" t="inlineStr"/>
       <c r="M303" t="inlineStr">
         <is>
           <t>Service</t>
@@ -35877,7 +33410,6 @@
       <c r="N303" t="b">
         <v>0</v>
       </c>
-      <c r="O303" t="inlineStr"/>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -35920,7 +33452,6 @@
           <t>Communication &amp; Updates</t>
         </is>
       </c>
-      <c r="I304" t="inlineStr"/>
       <c r="J304" t="inlineStr">
         <is>
           <t>Positive</t>
@@ -35931,7 +33462,6 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="L304" t="inlineStr"/>
       <c r="M304" t="inlineStr">
         <is>
           <t>Sales</t>
@@ -35940,7 +33470,6 @@
       <c r="N304" t="b">
         <v>0</v>
       </c>
-      <c r="O304" t="inlineStr"/>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -35983,7 +33512,6 @@
           <t>Staff Attitude &amp; Behaviour</t>
         </is>
       </c>
-      <c r="I305" t="inlineStr"/>
       <c r="J305" t="inlineStr">
         <is>
           <t>Positive</t>
@@ -35994,7 +33522,6 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="L305" t="inlineStr"/>
       <c r="M305" t="inlineStr">
         <is>
           <t>Sales</t>
@@ -36003,7 +33530,6 @@
       <c r="N305" t="b">
         <v>0</v>
       </c>
-      <c r="O305" t="inlineStr"/>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -36046,7 +33572,6 @@
           <t>Positive Experience (General)</t>
         </is>
       </c>
-      <c r="I306" t="inlineStr"/>
       <c r="J306" t="inlineStr">
         <is>
           <t>Positive</t>
@@ -36057,7 +33582,6 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="L306" t="inlineStr"/>
       <c r="M306" t="inlineStr">
         <is>
           <t>Service</t>
@@ -36066,7 +33590,6 @@
       <c r="N306" t="b">
         <v>0</v>
       </c>
-      <c r="O306" t="inlineStr"/>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -36109,7 +33632,6 @@
           <t>Communication &amp; Updates</t>
         </is>
       </c>
-      <c r="I307" t="inlineStr"/>
       <c r="J307" t="inlineStr">
         <is>
           <t>Positive</t>
@@ -36120,7 +33642,6 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="L307" t="inlineStr"/>
       <c r="M307" t="inlineStr">
         <is>
           <t>Service</t>
@@ -36129,7 +33650,6 @@
       <c r="N307" t="b">
         <v>0</v>
       </c>
-      <c r="O307" t="inlineStr"/>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
@@ -36172,7 +33692,6 @@
           <t>Staff Attitude &amp; Behaviour</t>
         </is>
       </c>
-      <c r="I308" t="inlineStr"/>
       <c r="J308" t="inlineStr">
         <is>
           <t>Positive</t>
@@ -36183,7 +33702,6 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="L308" t="inlineStr"/>
       <c r="M308" t="inlineStr">
         <is>
           <t>Service</t>
@@ -36192,7 +33710,6 @@
       <c r="N308" t="b">
         <v>0</v>
       </c>
-      <c r="O308" t="inlineStr"/>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
@@ -36235,7 +33752,6 @@
           <t>Booking &amp; Scheduling</t>
         </is>
       </c>
-      <c r="I309" t="inlineStr"/>
       <c r="J309" t="inlineStr">
         <is>
           <t>Positive</t>
@@ -36246,7 +33762,6 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="L309" t="inlineStr"/>
       <c r="M309" t="inlineStr">
         <is>
           <t>Service</t>
@@ -36255,7 +33770,6 @@
       <c r="N309" t="b">
         <v>0</v>
       </c>
-      <c r="O309" t="inlineStr"/>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -36298,7 +33812,6 @@
           <t>Staff Attitude &amp; Behaviour</t>
         </is>
       </c>
-      <c r="I310" t="inlineStr"/>
       <c r="J310" t="inlineStr">
         <is>
           <t>Positive</t>
@@ -36309,7 +33822,6 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="L310" t="inlineStr"/>
       <c r="M310" t="inlineStr">
         <is>
           <t>Service</t>
@@ -36318,7 +33830,6 @@
       <c r="N310" t="b">
         <v>0</v>
       </c>
-      <c r="O310" t="inlineStr"/>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -36361,7 +33872,6 @@
           <t>Staff Attitude &amp; Behaviour</t>
         </is>
       </c>
-      <c r="I311" t="inlineStr"/>
       <c r="J311" t="inlineStr">
         <is>
           <t>Positive</t>
@@ -36372,7 +33882,6 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="L311" t="inlineStr"/>
       <c r="M311" t="inlineStr">
         <is>
           <t>Sales</t>
@@ -36381,7 +33890,6 @@
       <c r="N311" t="b">
         <v>0</v>
       </c>
-      <c r="O311" t="inlineStr"/>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -36424,7 +33932,6 @@
           <t>Staff Attitude &amp; Behaviour</t>
         </is>
       </c>
-      <c r="I312" t="inlineStr"/>
       <c r="J312" t="inlineStr">
         <is>
           <t>Positive</t>
@@ -36435,7 +33942,6 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="L312" t="inlineStr"/>
       <c r="M312" t="inlineStr">
         <is>
           <t>Service</t>
@@ -36444,7 +33950,6 @@
       <c r="N312" t="b">
         <v>0</v>
       </c>
-      <c r="O312" t="inlineStr"/>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -36487,7 +33992,6 @@
           <t>Staff Attitude &amp; Behaviour</t>
         </is>
       </c>
-      <c r="I313" t="inlineStr"/>
       <c r="J313" t="inlineStr">
         <is>
           <t>Positive</t>
@@ -36498,7 +34002,6 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="L313" t="inlineStr"/>
       <c r="M313" t="inlineStr">
         <is>
           <t>Service</t>
@@ -36507,7 +34010,6 @@
       <c r="N313" t="b">
         <v>0</v>
       </c>
-      <c r="O313" t="inlineStr"/>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
@@ -36550,7 +34052,6 @@
           <t>Staff Attitude &amp; Behaviour</t>
         </is>
       </c>
-      <c r="I314" t="inlineStr"/>
       <c r="J314" t="inlineStr">
         <is>
           <t>Positive</t>
@@ -36561,7 +34062,6 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="L314" t="inlineStr"/>
       <c r="M314" t="inlineStr">
         <is>
           <t>Parts</t>
@@ -36570,7 +34070,6 @@
       <c r="N314" t="b">
         <v>0</v>
       </c>
-      <c r="O314" t="inlineStr"/>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -36613,7 +34112,6 @@
           <t>Vehicle Knowledge &amp; Explanation</t>
         </is>
       </c>
-      <c r="I315" t="inlineStr"/>
       <c r="J315" t="inlineStr">
         <is>
           <t>Positive</t>
@@ -36624,7 +34122,6 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="L315" t="inlineStr"/>
       <c r="M315" t="inlineStr">
         <is>
           <t>Sales</t>
@@ -36633,7 +34130,6 @@
       <c r="N315" t="b">
         <v>0</v>
       </c>
-      <c r="O315" t="inlineStr"/>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -36676,7 +34172,6 @@
           <t>Vehicle Knowledge &amp; Explanation</t>
         </is>
       </c>
-      <c r="I316" t="inlineStr"/>
       <c r="J316" t="inlineStr">
         <is>
           <t>Positive</t>
@@ -36687,7 +34182,6 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="L316" t="inlineStr"/>
       <c r="M316" t="inlineStr">
         <is>
           <t>Sales</t>
@@ -36696,7 +34190,6 @@
       <c r="N316" t="b">
         <v>0</v>
       </c>
-      <c r="O316" t="inlineStr"/>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -36739,7 +34232,6 @@
           <t>Timeliness &amp; Wait Times</t>
         </is>
       </c>
-      <c r="I317" t="inlineStr"/>
       <c r="J317" t="inlineStr">
         <is>
           <t>Positive</t>
@@ -36750,7 +34242,6 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="L317" t="inlineStr"/>
       <c r="M317" t="inlineStr">
         <is>
           <t>Service</t>
@@ -36759,7 +34250,6 @@
       <c r="N317" t="b">
         <v>0</v>
       </c>
-      <c r="O317" t="inlineStr"/>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
@@ -36802,7 +34292,6 @@
           <t>Vehicle Knowledge &amp; Explanation</t>
         </is>
       </c>
-      <c r="I318" t="inlineStr"/>
       <c r="J318" t="inlineStr">
         <is>
           <t>Positive</t>
@@ -36813,7 +34302,6 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="L318" t="inlineStr"/>
       <c r="M318" t="inlineStr">
         <is>
           <t>Parts</t>
@@ -36822,7 +34310,6 @@
       <c r="N318" t="b">
         <v>0</v>
       </c>
-      <c r="O318" t="inlineStr"/>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
@@ -36865,7 +34352,6 @@
           <t>Communication &amp; Updates</t>
         </is>
       </c>
-      <c r="I319" t="inlineStr"/>
       <c r="J319" t="inlineStr">
         <is>
           <t>Positive</t>
@@ -36876,7 +34362,6 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="L319" t="inlineStr"/>
       <c r="M319" t="inlineStr">
         <is>
           <t>Sales</t>
@@ -36885,7 +34370,6 @@
       <c r="N319" t="b">
         <v>0</v>
       </c>
-      <c r="O319" t="inlineStr"/>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
@@ -36928,7 +34412,6 @@
           <t>Pricing &amp; Charges</t>
         </is>
       </c>
-      <c r="I320" t="inlineStr"/>
       <c r="J320" t="inlineStr">
         <is>
           <t>Positive</t>
@@ -36939,7 +34422,6 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="L320" t="inlineStr"/>
       <c r="M320" t="inlineStr">
         <is>
           <t>Sales</t>
@@ -36948,7 +34430,6 @@
       <c r="N320" t="b">
         <v>0</v>
       </c>
-      <c r="O320" t="inlineStr"/>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -36991,7 +34472,6 @@
           <t>Vehicle Knowledge &amp; Explanation</t>
         </is>
       </c>
-      <c r="I321" t="inlineStr"/>
       <c r="J321" t="inlineStr">
         <is>
           <t>Positive</t>
@@ -37002,7 +34482,6 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="L321" t="inlineStr"/>
       <c r="M321" t="inlineStr">
         <is>
           <t>Sales</t>
@@ -37011,7 +34490,6 @@
       <c r="N321" t="b">
         <v>0</v>
       </c>
-      <c r="O321" t="inlineStr"/>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
@@ -37054,7 +34532,6 @@
           <t>Staff Attitude &amp; Behaviour</t>
         </is>
       </c>
-      <c r="I322" t="inlineStr"/>
       <c r="J322" t="inlineStr">
         <is>
           <t>Positive</t>
@@ -37065,7 +34542,6 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="L322" t="inlineStr"/>
       <c r="M322" t="inlineStr">
         <is>
           <t>Sales</t>
@@ -37074,7 +34550,6 @@
       <c r="N322" t="b">
         <v>0</v>
       </c>
-      <c r="O322" t="inlineStr"/>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
@@ -37117,7 +34592,6 @@
           <t>Staff Attitude &amp; Behaviour</t>
         </is>
       </c>
-      <c r="I323" t="inlineStr"/>
       <c r="J323" t="inlineStr">
         <is>
           <t>Positive</t>
@@ -37128,7 +34602,6 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="L323" t="inlineStr"/>
       <c r="M323" t="inlineStr">
         <is>
           <t>Parts</t>
@@ -37137,7 +34610,6 @@
       <c r="N323" t="b">
         <v>0</v>
       </c>
-      <c r="O323" t="inlineStr"/>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
@@ -37180,7 +34652,6 @@
           <t>Staff Attitude &amp; Behaviour</t>
         </is>
       </c>
-      <c r="I324" t="inlineStr"/>
       <c r="J324" t="inlineStr">
         <is>
           <t>Positive</t>
@@ -37191,7 +34662,6 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="L324" t="inlineStr"/>
       <c r="M324" t="inlineStr">
         <is>
           <t>Parts</t>
@@ -37200,7 +34670,6 @@
       <c r="N324" t="b">
         <v>0</v>
       </c>
-      <c r="O324" t="inlineStr"/>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
@@ -37243,7 +34712,6 @@
           <t>Parts Availability &amp; Delays</t>
         </is>
       </c>
-      <c r="I325" t="inlineStr"/>
       <c r="J325" t="inlineStr">
         <is>
           <t>Positive</t>
@@ -37254,7 +34722,6 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="L325" t="inlineStr"/>
       <c r="M325" t="inlineStr">
         <is>
           <t>Parts</t>
@@ -37263,7 +34730,6 @@
       <c r="N325" t="b">
         <v>0</v>
       </c>
-      <c r="O325" t="inlineStr"/>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
@@ -37306,7 +34772,6 @@
           <t>Timeliness &amp; Wait Times</t>
         </is>
       </c>
-      <c r="I326" t="inlineStr"/>
       <c r="J326" t="inlineStr">
         <is>
           <t>Positive</t>
@@ -37317,7 +34782,6 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="L326" t="inlineStr"/>
       <c r="M326" t="inlineStr">
         <is>
           <t>Parts</t>
@@ -37326,7 +34790,6 @@
       <c r="N326" t="b">
         <v>0</v>
       </c>
-      <c r="O326" t="inlineStr"/>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -37369,7 +34832,6 @@
           <t>Staff Attitude &amp; Behaviour</t>
         </is>
       </c>
-      <c r="I327" t="inlineStr"/>
       <c r="J327" t="inlineStr">
         <is>
           <t>Positive</t>
@@ -37380,7 +34842,6 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="L327" t="inlineStr"/>
       <c r="M327" t="inlineStr">
         <is>
           <t>Service</t>
@@ -37389,7 +34850,6 @@
       <c r="N327" t="b">
         <v>0</v>
       </c>
-      <c r="O327" t="inlineStr"/>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
@@ -37432,7 +34892,6 @@
           <t>Staff Attitude &amp; Behaviour</t>
         </is>
       </c>
-      <c r="I328" t="inlineStr"/>
       <c r="J328" t="inlineStr">
         <is>
           <t>Positive</t>
@@ -37443,7 +34902,6 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="L328" t="inlineStr"/>
       <c r="M328" t="inlineStr">
         <is>
           <t>Service</t>
@@ -37452,7 +34910,6 @@
       <c r="N328" t="b">
         <v>0</v>
       </c>
-      <c r="O328" t="inlineStr"/>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -37495,7 +34952,6 @@
           <t>Staff Attitude &amp; Behaviour</t>
         </is>
       </c>
-      <c r="I329" t="inlineStr"/>
       <c r="J329" t="inlineStr">
         <is>
           <t>Positive</t>
@@ -37506,7 +34962,6 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="L329" t="inlineStr"/>
       <c r="M329" t="inlineStr">
         <is>
           <t>Service</t>
@@ -37515,7 +34970,6 @@
       <c r="N329" t="b">
         <v>0</v>
       </c>
-      <c r="O329" t="inlineStr"/>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
@@ -37558,7 +35012,6 @@
           <t>Staff Attitude &amp; Behaviour</t>
         </is>
       </c>
-      <c r="I330" t="inlineStr"/>
       <c r="J330" t="inlineStr">
         <is>
           <t>Positive</t>
@@ -37569,7 +35022,6 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="L330" t="inlineStr"/>
       <c r="M330" t="inlineStr">
         <is>
           <t>Service</t>
@@ -37578,7 +35030,6 @@
       <c r="N330" t="b">
         <v>0</v>
       </c>
-      <c r="O330" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -37657,9 +35108,7 @@
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr"/>
-    </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>

--- a/code_and_data/ai_output/validation_sample.xlsx
+++ b/code_and_data/ai_output/validation_sample.xlsx
@@ -536,10 +536,8 @@
           <t>Really friendly mob at service, made a first-timer like me feel at ease. Wish someone had shown me how the app connects to the car though, spent my first weekend guessing.</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
+      <c r="F2" t="n">
+        <v>3</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -586,10 +584,8 @@
           <t>Service was done in under two hours like they promised, but nobody showed me how to use the charging cable that came with the EV.</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
+      <c r="F3" t="n">
+        <v>3</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -636,10 +632,8 @@
           <t>Ordering five vehicles for the fleet went through without a hitch and the handover was organised. I did find the repeated attempts to upsell protection packages and finance tiresome.</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
+      <c r="F4" t="n">
+        <v>4</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -686,10 +680,8 @@
           <t>easy process, no hassle. car came back dirty with grease on the seat though.</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
+      <c r="F5" t="n">
+        <v>4</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -736,10 +728,8 @@
           <t>understood every part of the paperwork, which is rare for me. being stuck in the queue at the service desk for 50 minutes before anyone looked up was a bit rich though.</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
+      <c r="F6" t="n">
+        <v>3</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -786,10 +776,8 @@
           <t>Warm welcome every time. Stood at the counter for about 35 minutes before anyone got to me, and there were only two people ahead.</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
+      <c r="F7" t="n">
+        <v>2</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -836,10 +824,8 @@
           <t>Text updates spot on, never had to ring and chase. Stood at the service counter for ages though while one person served everyone.</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
+      <c r="F8" t="n">
+        <v>2</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -886,10 +872,8 @@
           <t>Process: no complaints. Spec sheet, build date, compliance, drive-away price all sorted first go with no runaround. Attitude of the salesman: arrogant, brushed off my questions about the torque figures like I should just trust him.</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
+      <c r="F9" t="n">
+        <v>3</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -936,10 +920,8 @@
           <t>Good on ya for the text updates. Pity about the wait, mate, it was ridiculous.</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
+      <c r="F10" t="n">
+        <v>3</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -986,10 +968,8 @@
           <t>I was very happy with how fast my car was finished, they respected my time. The waiting lounge was untidy and there was nowhere to put my bag or get a cup of water.</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
+      <c r="F11" t="n">
+        <v>4</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -1036,10 +1016,8 @@
           <t>Lovely welcoming staff, made my morning easy. But I only found out the car was ready because I rang them. Never a text.</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
+      <c r="F12" t="n">
+        <v>2</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -1086,10 +1064,8 @@
           <t>Said Raj was kind and made her feel at home, bless him. After that she heard nothing at all about the Ridge and had to ring the dealership herself to find out if it was done.</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
+      <c r="F13" t="n">
+        <v>4</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1141,10 +1117,8 @@
           <t>Everybody I met was courteous and obliging I was promised a call on Thursday I am still to receive it and have since had to chase it myself</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
+      <c r="F14" t="n">
+        <v>3</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1191,10 +1165,8 @@
           <t>everyone i met was polite, friendly and eager to help. i do wish, however, that someone had phoned to tell me the work was running behind rather than leaving me to find out by calling in myself.</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
+      <c r="F15" t="n">
+        <v>4</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1241,10 +1213,8 @@
           <t>the explanation of what was done was clear and honest. i just think waiting three hours is a bit much for a minor service.</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
+      <c r="F16" t="n">
+        <v>3</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1291,10 +1261,8 @@
           <t>Good people, bad invoice.</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
+      <c r="F17" t="n">
+        <v>3</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1341,10 +1309,8 @@
           <t>Lovely, kind people. Do not like the sales talk for the insurance, very much.</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
+      <c r="F18" t="n">
+        <v>4</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1391,10 +1357,8 @@
           <t>Good communication throughout Car not raedy on pickup</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
+      <c r="F19" t="n">
+        <v>3</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1441,10 +1405,8 @@
           <t>Good people, very nice to deal with. Slow, slow, slow.</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
+      <c r="F20" t="n">
+        <v>3</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1491,10 +1453,8 @@
           <t>Great speed on the timing belt job, they got it done in the one day like they said. Getting that day was the problem, because the first two dates I asked for were both full. Call me on [REDACTED_PHONE].</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
+      <c r="F21" t="n">
+        <v>3</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1541,10 +1501,8 @@
           <t>Lovely welcome from Mel, honestly. Part's still not here though. Brilliant.</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
+      <c r="F22" t="n">
+        <v>4</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1591,10 +1549,8 @@
           <t>Paperwork explained properly, no pressure. Handover was a shambles though, car wasn't ready and they had to go find the second key.</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
+      <c r="F23" t="n">
+        <v>2</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1641,10 +1597,8 @@
           <t>Bec was a sweetheart, got me a tea and chatted about the grandkids while I waited. Booking was another story, they rang to say they'd have to push me back a fortnight.</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
+      <c r="F24" t="n">
+        <v>3</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1691,10 +1645,8 @@
           <t>Really efficient, had us out the door quick smart. Though the price ended up being a lot more than what I was told upfront.</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
+      <c r="F25" t="n">
+        <v>3</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1741,10 +1693,8 @@
           <t>Big thanks for ringing me back with updates, very kind. I stand in the line long time at the desk, one hour almost. Too long for me.</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
+      <c r="F26" t="n">
+        <v>3</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1791,10 +1741,8 @@
           <t>Booked in three cars for the business and every one was back in the yard before the end of the day, which keeps my drivers on the road. Shame I had to ring four times just to find out which one was ready, nobody ever phoned me.</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
+      <c r="F27" t="n">
+        <v>3</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1841,10 +1789,8 @@
           <t>Lovely team, communication needs work.</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
+      <c r="F28" t="n">
+        <v>4</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1891,10 +1837,8 @@
           <t>Good communication. Long wait.</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
+      <c r="F29" t="n">
+        <v>3</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1941,10 +1885,8 @@
           <t>With two kids climbing over the seats I expected to switch off, but Fatima kept it short and clear. I knew exactly what was done to the Altura Corsa and why. (rego 909MZB)</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
+      <c r="F30" t="n">
+        <v>4</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1991,10 +1933,8 @@
           <t>Nice and easy. Did what it said on the tin.</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="F31" t="n">
+        <v>5</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -2041,10 +1981,8 @@
           <t>quick note, staff were great, friendly and helpful. thanks Josh</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
+      <c r="F32" t="n">
+        <v>5</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -2091,10 +2029,8 @@
           <t>Priya called me twice to let me know how the Arc was going. Very good.</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="F33" t="n">
+        <v>5</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -2141,10 +2077,8 @@
           <t>Staff were cheerful and nothing was too much trouble. I got a text when the car came in and another when it was ready to collect.</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
+      <c r="F34" t="n">
+        <v>5</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -2191,10 +2125,8 @@
           <t>Timing was spot on, just as quoted. (rego [REDACTED_REGO])</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
+      <c r="F35" t="n">
+        <v>4</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -2241,10 +2173,8 @@
           <t>Very good timing, mate. Ready when I rocked up.</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="F36" t="n">
+        <v>5</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -2291,10 +2221,8 @@
           <t>Understood everything the first time. Doesn’t happen often.</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="F37" t="n">
+        <v>5</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -2341,10 +2269,8 @@
           <t>Not a single sour face in there. Refreshing, to be honest.</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="F38" t="n">
+        <v>5</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -2391,10 +2317,8 @@
           <t>Excellent value. Our trade business keeps costs tight and this was right in line, if not better.</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="F39" t="n">
+        <v>5</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -2441,10 +2365,8 @@
           <t>The explanation was really great. I did not know about the fuel economy dipslay and now I do.</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="F40" t="n">
+        <v>5</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -2491,10 +2413,8 @@
           <t>gr8 staff, super friendly (rego [REDACTED_REGO])</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="F41" t="n">
+        <v>5</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -2541,10 +2461,8 @@
           <t>Great speed, kept to the schedule. Nothing else to add.</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="F42" t="n">
+        <v>5</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -2591,10 +2509,8 @@
           <t>satff were lovely. thx</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="F43" t="n">
+        <v>5</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -2641,10 +2557,8 @@
           <t>quick as. thanks</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="F44" t="n">
+        <v>5</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -2691,10 +2605,8 @@
           <t>Polite and welcoming staff. I felt respected. (rego 367UFV)</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="F45" t="n">
+        <v>5</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -2741,10 +2653,8 @@
           <t>Gave me a buzz as soon as the diagnosis was done, and again when the work finished. Lovely. (rego [REDACTED_REGO])</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
+      <c r="F46" t="n">
+        <v>4</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -2791,10 +2701,8 @@
           <t>Gold star for Mick, super friendly.</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="F47" t="n">
+        <v>5</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -2841,10 +2749,8 @@
           <t>I walked in knowing nothing and walked out with keys. That's about all there is to say, it was that straightforward.</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="F48" t="n">
+        <v>5</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -2891,10 +2797,8 @@
           <t>Staff very helpful and kind to me. Price is not expensive, I think is good value for money. Thank you very much.</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
+      <c r="F49" t="n">
+        <v>4</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -2941,10 +2845,8 @@
           <t>Not usually one to write these but Raj was just really nice to deal with. That's it.</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
+      <c r="F50" t="n">
+        <v>4</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -2991,10 +2893,8 @@
           <t>Good staff. Friendly and helpful.</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="F51" t="n">
+        <v>5</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -3041,10 +2941,8 @@
           <t>Lovely lady on the front counter offered to help me with the paperwork when I was fumbling around. Very kind.</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
+      <c r="F52" t="n">
+        <v>4</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -3091,10 +2989,8 @@
           <t>Yep, good staff. Friendly. Done. (rego [REDACTED_REGO])</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="F53" t="n">
+        <v>5</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -3141,10 +3037,8 @@
           <t>The reception girls are a delight. Always a smile and a hello, even on a Monday morning when I'd be grumpy myself.</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="F54" t="n">
+        <v>5</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -3191,10 +3085,8 @@
           <t>Quick job, no dramas, back to work.</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="F55" t="n">
+        <v>5</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -3241,10 +3133,8 @@
           <t>right to the point and easy to follow. that’s all i want.</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="F56" t="n">
+        <v>5</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -3291,10 +3181,8 @@
           <t>Pirce was right Genuine part for less than the quote I got elsewhere</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="F57" t="n">
+        <v>5</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -3341,10 +3229,8 @@
           <t>Very good explaining about the air filter. The man tell me which side is up, how to see when it is dirty, and he show me the arrow on the frame. I understand all now, no problem.</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
+      <c r="F58" t="n">
+        <v>5</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -3391,10 +3277,8 @@
           <t>Lovely welcome from the whole team. Josh even held the door for me when my hands were full.</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="F59" t="n">
+        <v>5</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -3441,10 +3325,8 @@
           <t>Staff were lovely to my mum and me both. Geniunely caring bunch.</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="F60" t="n">
+        <v>5</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -3491,10 +3373,8 @@
           <t>Rocked up, handed over the keys, and it was done before I knew it. Top effort.</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="F61" t="n">
+        <v>5</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -3541,10 +3421,8 @@
           <t>Everyone smiled and said hello. Simple, but it counts.</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="F62" t="n">
+        <v>5</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -3591,10 +3469,8 @@
           <t>Very fair pricing. I compared with two other places and this was the cheapest by a decent margin for the same service.</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="F63" t="n">
+        <v>5</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -3641,10 +3517,8 @@
           <t>having only just moved to town, i was after a place that felt welcoming. this is it, the people are great.</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
+      <c r="F64" t="n">
+        <v>4</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -3691,10 +3565,8 @@
           <t>My husband and I are on a fixed income and the price of the mirror cover was lower than I thought it would be. Very grateful.</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="F65" t="n">
+        <v>5</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -3741,10 +3613,8 @@
           <t>[REDACTED_NAME] - Customer stated the pricing was very reasonable and good value for what was done.</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
+      <c r="F66" t="n">
+        <v>4</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -3791,10 +3661,8 @@
           <t>Easy peasy</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="F67" t="n">
+        <v>5</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -3841,10 +3709,8 @@
           <t>Lovely, helpful staff. Even with a queue they stayed smiling.</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
+      <c r="F68" t="n">
+        <v>4</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -3891,10 +3757,8 @@
           <t>Staff cheerful from the second the door opened. That's all she wanted to say.</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="F69" t="n">
+        <v>5</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -3941,10 +3805,8 @@
           <t>Got a ring when they were halfway through, which let me sort a lift home without panicking.</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="F70" t="n">
+        <v>5</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
@@ -3991,10 +3853,8 @@
           <t>[REDACTED_NAME] - Sarcastic but positive - said he almost fell off his chair when the service desk actually called him first.</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="F71" t="n">
+        <v>5</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
@@ -4041,10 +3901,8 @@
           <t>Gee, took no time at all Done quicker than I can normally get a haircut</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="F72" t="n">
+        <v>5</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
@@ -4091,10 +3949,8 @@
           <t>Told me exactly what the brake job meant. No waffle. (rego 449ZAL)</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="F73" t="n">
+        <v>5</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
@@ -4141,10 +3997,8 @@
           <t>Didn't glaze over once. That says a lot.</t>
         </is>
       </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="F74" t="n">
+        <v>5</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
@@ -4191,10 +4045,8 @@
           <t>Quick texts through the day kept me in the picture while I was out on jobs. Top effort.</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="F75" t="n">
+        <v>5</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
@@ -4241,10 +4093,8 @@
           <t>Great deal for the money, would pay it again.</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
+      <c r="F76" t="n">
+        <v>4</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
@@ -4291,10 +4141,8 @@
           <t>Honestly expected a cold shoulder, so I'm eating my words Staff were warm and chatty from the second I walked in, even with me covered in sawdust</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="F77" t="n">
+        <v>5</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
@@ -4341,10 +4189,8 @@
           <t>Friendly bunch. That is all.</t>
         </is>
       </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="F78" t="n">
+        <v>5</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
@@ -4391,10 +4237,8 @@
           <t>Ordered the ute for the business, signed once, collected it. Nothing chased up, nothing redone.</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
+      <c r="F79" t="n">
+        <v>4</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
@@ -4441,10 +4285,8 @@
           <t>My tradie mates reckon dealerships are cold. Told them this one's different, the staff are bloody friendly.</t>
         </is>
       </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="F80" t="n">
+        <v>5</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
@@ -4491,10 +4333,8 @@
           <t>Honestly, I came in braced for a lecture full of jargon and got a proper conversation instead. Raj described the work in everyday language and even drew on the invoice to show me which bit was which.</t>
         </is>
       </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="F81" t="n">
+        <v>5</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
@@ -4541,10 +4381,8 @@
           <t>Being new around here I had no clue about toll tags. Josh explained how they link to the car and what I needed to set up.</t>
         </is>
       </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
+      <c r="F82" t="n">
+        <v>4</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
@@ -4591,10 +4429,8 @@
           <t>Walked in expecting the usual runaround. Instead Dave was genuinely helpful, took the time to explain the finance contract line by line, and kept the chat easy. Rare these days.</t>
         </is>
       </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
+      <c r="F83" t="n">
+        <v>4</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
@@ -4641,10 +4477,8 @@
           <t>Kind staff, kind smiles. Good.</t>
         </is>
       </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
+      <c r="F84" t="n">
+        <v>4</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
@@ -4691,10 +4525,8 @@
           <t>Super friendly bloke, explained all the features on the Altura Terra without making him feel dumb.</t>
         </is>
       </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="F85" t="n">
+        <v>5</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
@@ -4741,10 +4573,8 @@
           <t>super welcoming. felt like walking into a mate's place. (rego 173GWU)</t>
         </is>
       </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="F86" t="n">
+        <v>5</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
@@ -4791,10 +4621,8 @@
           <t>Sarah was lovely. Chatty without being pushy.</t>
         </is>
       </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="F87" t="n">
+        <v>5</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
@@ -4841,10 +4669,8 @@
           <t>for a first-time owner the amount of detail i got was fantastic. why the oil gets changed, what the filter does, what the logbook is for. all explained without any fuss.</t>
         </is>
       </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="F88" t="n">
+        <v>5</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
@@ -4891,10 +4717,8 @@
           <t>Said they were prompt. Part was ready on the day it was told to them.</t>
         </is>
       </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="F89" t="n">
+        <v>5</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
@@ -4941,10 +4765,8 @@
           <t>Kind people Very welcome feeling</t>
         </is>
       </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="F90" t="n">
+        <v>5</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
@@ -4991,10 +4813,8 @@
           <t>being a bit of a car nut, i expected to be talked down to. instead kylie got into the specifics of the dpf regen cycle and why short trips were causing my issue, and it all made sense. nice to deal with someone who actually knows the detail and can say it straight. (rego [REDACTED_REGO])</t>
         </is>
       </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="F91" t="n">
+        <v>5</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
@@ -5041,10 +4861,8 @@
           <t>Moved here a few weeks back and wasn't sure what to expect, but the brake pads were across the counter in about five minutes.</t>
         </is>
       </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="F92" t="n">
+        <v>5</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
@@ -5091,10 +4909,8 @@
           <t>under budget, which never happens with cars.</t>
         </is>
       </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="F93" t="n">
+        <v>5</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
@@ -5141,10 +4957,8 @@
           <t>sarcastic by nature so i'll say it plain: the staff were bloody friendly and i've got nothing clever to add.</t>
         </is>
       </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="F94" t="n">
+        <v>5</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
@@ -5191,10 +5005,8 @@
           <t>Said the explanation was so clear she didn't need to ask a single question. That's a first for her.</t>
         </is>
       </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="F95" t="n">
+        <v>5</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
@@ -5241,10 +5053,8 @@
           <t>Reckon I got about five messages in one day. Not one was wasted, each told me something new.</t>
         </is>
       </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="F96" t="n">
+        <v>5</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
@@ -5291,10 +5101,8 @@
           <t>i walked in not knowing what to expect and walked out with the altura terra done and dusted. dead simple.</t>
         </is>
       </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
+      <c r="F97" t="n">
+        <v>4</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
@@ -5341,10 +5149,8 @@
           <t>Honestly thought I'd be stuck there till arvo. Nope, back on the road by morning smoke.</t>
         </is>
       </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
+      <c r="F98" t="n">
+        <v>4</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
@@ -5391,10 +5197,8 @@
           <t>Didn't have to wait around at all, they had my Vista sorted and ready to go in no time.</t>
         </is>
       </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="F99" t="n">
+        <v>5</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
@@ -5441,10 +5245,8 @@
           <t>Pleasantly surprised by the final cost. It was well under what I'd mentally prepared for.</t>
         </is>
       </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
+      <c r="F100" t="n">
+        <v>4</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
@@ -5491,10 +5293,8 @@
           <t>Staff kind, price good.</t>
         </is>
       </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
+      <c r="F101" t="n">
+        <v>4</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
@@ -5541,10 +5341,8 @@
           <t>Sorted in record time, Tuan had me back on the road before the kettle would've boiled.</t>
         </is>
       </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="F102" t="n">
+        <v>5</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
@@ -5591,10 +5389,8 @@
           <t>Brilliant explanation of how the tow bar wiring and the brake controller work. We have a trailer to haul every week so that matters. (rego [REDACTED_REGO])</t>
         </is>
       </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="F103" t="n">
+        <v>5</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
@@ -5641,10 +5437,8 @@
           <t>Knew the whole time where the ute was up to. Great.</t>
         </is>
       </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="F104" t="n">
+        <v>5</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
@@ -5691,10 +5485,8 @@
           <t>In and out in under an hour. Brilliant.</t>
         </is>
       </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="F105" t="n">
+        <v>5</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
@@ -5741,10 +5533,8 @@
           <t>Being new to the area I didn't know who to trust on price. Found the parts here cheaper than the quote I'd been given by a workshop, so I bought it myself and saved a fair bit.</t>
         </is>
       </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="F106" t="n">
+        <v>5</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
@@ -5791,10 +5581,8 @@
           <t>Cheerful lot down there. Mel in particular was a ripper.</t>
         </is>
       </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="F107" t="n">
+        <v>5</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
@@ -5841,10 +5629,8 @@
           <t>Very quick service, part is ready when you say. Thank you.</t>
         </is>
       </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="F108" t="n">
+        <v>5</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
@@ -5891,10 +5677,8 @@
           <t>Dropped it in on a tight budget and tighter schedule, and they nailed the schedule part. Staff were kind and helpful, too.</t>
         </is>
       </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
+      <c r="F109" t="n">
+        <v>4</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
@@ -5941,10 +5725,8 @@
           <t>Told me straight how the tyre pressure monitoring works and what the warning means. Handy. (rego [REDACTED_REGO])</t>
         </is>
       </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="F110" t="n">
+        <v>5</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
@@ -5991,10 +5773,8 @@
           <t>As someone who does most of his own spannerwork, I braced for the usual dumbed-down spiel. Gaz instead gave me the actual torque spec issue and why the part was replaced rather than reconditioned. Respect.</t>
         </is>
       </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
+      <c r="F111" t="n">
+        <v>4</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
@@ -6041,10 +5821,8 @@
           <t>Good explanation. I understand what they fix on my car and why. Thank you very much.</t>
         </is>
       </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="F112" t="n">
+        <v>5</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
@@ -6091,10 +5869,8 @@
           <t>[REDACTED_NAME] - Cust said Gaz was patient and cheerful even with a toddler screaming in the background. Appreciated the kindness.</t>
         </is>
       </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
+      <c r="F113" t="n">
+        <v>4</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
@@ -6141,10 +5917,8 @@
           <t>Dead simple from the first enquiry to handover, and I never had to ring to ask what was going on because Nat was already onto it with a text or call. (rego [REDACTED_REGO])</t>
         </is>
       </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="F114" t="n">
+        <v>5</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
@@ -6191,10 +5965,8 @@
           <t>I appreciated how often they updated me about my Altura Vista. Every time I wondered what was happening, my phone buzzed with an answer.</t>
         </is>
       </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="F115" t="n">
+        <v>5</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
@@ -6241,10 +6013,8 @@
           <t>Nicest reception I've had anywhere in years.</t>
         </is>
       </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
+      <c r="F116" t="n">
+        <v>4</v>
       </c>
       <c r="G116" t="inlineStr">
         <is>
@@ -6291,10 +6061,8 @@
           <t>[REDACTED_NAME] - Said not a long wait at all, which with three kids in the waiting room was a blessing.</t>
         </is>
       </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="F117" t="n">
+        <v>5</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
@@ -6341,10 +6109,8 @@
           <t>I have lived in this town only a short while, and I was worried about finding a place I could trust. The people in the service area were kind, patient and chatty without being pushy. I came away feeling like I had found a home base for the Ridge, and that is down to how warmly I was treated.</t>
         </is>
       </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
+      <c r="F118" t="n">
+        <v>4</v>
       </c>
       <c r="G118" t="inlineStr">
         <is>
@@ -6391,10 +6157,8 @@
           <t>I've been wrenching on my own cars for thirty years and I'm usually wary of service desks, but Mel spoke to me like an equal and was genuinely pleasant about it. Good people. (rego [REDACTED_REGO])</t>
         </is>
       </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="F119" t="n">
+        <v>5</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
@@ -6441,10 +6205,8 @@
           <t>Thank you to all in the sales team for the warm hello and the helpful hands. My husband and I felt respected.</t>
         </is>
       </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
+      <c r="F120" t="n">
+        <v>4</v>
       </c>
       <c r="G120" t="inlineStr">
         <is>
@@ -6491,10 +6253,8 @@
           <t>Very fair pricing. My husband and I kept waiting for the catch and there wasn't one, just a lower price than we expected.</t>
         </is>
       </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
+      <c r="F121" t="n">
+        <v>4</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
@@ -6541,10 +6301,8 @@
           <t>Great service from the Southport team, highly recommend</t>
         </is>
       </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="F122" t="n">
+        <v>5</v>
       </c>
       <c r="G122" t="inlineStr">
         <is>
@@ -6591,10 +6349,8 @@
           <t>Impressive how quickly the team got through the service on my Terra. Didn't feel like I was waiting around at all.</t>
         </is>
       </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="F123" t="n">
+        <v>5</v>
       </c>
       <c r="G123" t="inlineStr">
         <is>
@@ -6641,10 +6397,8 @@
           <t>Staff explain car very clear for me, I understand all the paper. Process is very easy and smooth, thank you.</t>
         </is>
       </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="F124" t="n">
+        <v>5</v>
       </c>
       <c r="G124" t="inlineStr">
         <is>
@@ -6691,10 +6445,8 @@
           <t>In and out. Quick as.</t>
         </is>
       </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="F125" t="n">
+        <v>5</v>
       </c>
       <c r="G125" t="inlineStr">
         <is>
@@ -6741,10 +6493,8 @@
           <t>They fiished the work on schedule and took the time to explain the bits I didn't understand. Thank you kindly.</t>
         </is>
       </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
+      <c r="F126" t="n">
+        <v>4</v>
       </c>
       <c r="G126" t="inlineStr">
         <is>
@@ -6791,10 +6541,8 @@
           <t>Said, after years of coming here, the explanations are always clear and today was no different. (rego [REDACTED_REGO])</t>
         </is>
       </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="F127" t="n">
+        <v>5</v>
       </c>
       <c r="G127" t="inlineStr">
         <is>
@@ -6841,10 +6589,8 @@
           <t>Friendly crew. Will be back. (rego 420GFW)</t>
         </is>
       </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="F128" t="n">
+        <v>5</v>
       </c>
       <c r="G128" t="inlineStr">
         <is>
@@ -6891,10 +6637,8 @@
           <t>Honestly the updates were the best bit. I'm skint and stressing about when I'd have wheels, and Sarah told me each time without me having to ask.</t>
         </is>
       </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
+      <c r="F129" t="n">
+        <v>4</v>
       </c>
       <c r="G129" t="inlineStr">
         <is>
@@ -6941,10 +6685,8 @@
           <t>Didn't think they'd get my battery in same day but they did. Cheers.</t>
         </is>
       </c>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
+      <c r="F130" t="n">
+        <v>4</v>
       </c>
       <c r="G130" t="inlineStr">
         <is>
@@ -6991,10 +6733,8 @@
           <t>Never had a salesperson be so nice to me before. Tuan treated me like I mattered.</t>
         </is>
       </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="F131" t="n">
+        <v>5</v>
       </c>
       <c r="G131" t="inlineStr">
         <is>
@@ -7041,10 +6781,8 @@
           <t>Very fair cost. My wife and I are on a fixed income and we appreciated it.</t>
         </is>
       </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="F132" t="n">
+        <v>5</v>
       </c>
       <c r="G132" t="inlineStr">
         <is>
@@ -7091,10 +6829,8 @@
           <t>Honestly the best bang for buck I've found anywhere on the Gold Coast.</t>
         </is>
       </c>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
+      <c r="F133" t="n">
+        <v>4</v>
       </c>
       <c r="G133" t="inlineStr">
         <is>
@@ -7141,10 +6877,8 @@
           <t>Fast. Kept me posted. Done. (rego 506VAW)</t>
         </is>
       </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="F134" t="n">
+        <v>5</v>
       </c>
       <c r="G134" t="inlineStr">
         <is>
@@ -7191,10 +6925,8 @@
           <t>They actually told me what was happening without me having to hunt them down. Updates came through when they said they would.</t>
         </is>
       </c>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="F135" t="n">
+        <v>5</v>
       </c>
       <c r="G135" t="inlineStr">
         <is>
@@ -7241,10 +6973,8 @@
           <t>After all these years with this dealership I'm still imprsesed by how they explain things. Never feel in the dark.</t>
         </is>
       </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="F136" t="n">
+        <v>5</v>
       </c>
       <c r="G136" t="inlineStr">
         <is>
@@ -7291,10 +7021,8 @@
           <t>i wish to commend the pricing of my recent service. the amount charged was notably below what i had anticipated, and i consider it to be very good value. (rego 601BJG)</t>
         </is>
       </c>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="F137" t="n">
+        <v>5</v>
       </c>
       <c r="G137" t="inlineStr">
         <is>
@@ -7341,10 +7069,8 @@
           <t>Welcoming staff, constant updates.</t>
         </is>
       </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="F138" t="n">
+        <v>5</v>
       </c>
       <c r="G138" t="inlineStr">
         <is>
@@ -7391,10 +7117,8 @@
           <t>Mick took us through the cabin and boot setup on the EV and explained how the seats fold for the gear we carry. Practical stuff that I'd have missed.</t>
         </is>
       </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
+      <c r="F139" t="n">
+        <v>4</v>
       </c>
       <c r="G139" t="inlineStr">
         <is>
@@ -7441,10 +7165,8 @@
           <t>rang up, got a time that suited, car was done and ready before i'd finished my cuppa and a read of the paper. couldn't ask for a smoother morning.</t>
         </is>
       </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
+      <c r="F140" t="n">
+        <v>4</v>
       </c>
       <c r="G140" t="inlineStr">
         <is>
@@ -7491,10 +7213,8 @@
           <t>Helpful and welcoming staff, every time.</t>
         </is>
       </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="F141" t="n">
+        <v>5</v>
       </c>
       <c r="G141" t="inlineStr">
         <is>
@@ -7541,10 +7261,8 @@
           <t>Staff were bloody lovely. Can't say it any plainer.</t>
         </is>
       </c>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
+      <c r="F142" t="n">
+        <v>4</v>
       </c>
       <c r="G142" t="inlineStr">
         <is>
@@ -7591,10 +7309,8 @@
           <t>good communication all round and the guys were easy to deal with. aroha even gave me a ring when the job took a bit longer than expected.</t>
         </is>
       </c>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="F143" t="n">
+        <v>5</v>
       </c>
       <c r="G143" t="inlineStr">
         <is>
@@ -7641,10 +7357,8 @@
           <t>The explanation of the work was bang on. Nothing left unclear.</t>
         </is>
       </c>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
+      <c r="F144" t="n">
+        <v>4</v>
       </c>
       <c r="G144" t="inlineStr">
         <is>
@@ -7691,10 +7405,8 @@
           <t>Thorough, patient explanation of every item. I felt I understood the whole serice before I picked up the keys.</t>
         </is>
       </c>
-      <c r="F145" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="F145" t="n">
+        <v>5</v>
       </c>
       <c r="G145" t="inlineStr">
         <is>
@@ -7741,10 +7453,8 @@
           <t>Smiles all round, carcked a few jokes with Aroha while waiting. Easy as.</t>
         </is>
       </c>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
+      <c r="F146" t="n">
+        <v>5</v>
       </c>
       <c r="G146" t="inlineStr">
         <is>
@@ -7791,10 +7501,8 @@
           <t>After forty years of dealing with service departments I can honestly say these are some of the friendliest staff I've met. Well done to every one of them.</t>
         </is>
       </c>
-      <c r="F147" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="F147" t="n">
+        <v>5</v>
       </c>
       <c r="G147" t="inlineStr">
         <is>
@@ -7841,10 +7549,8 @@
           <t>Pleasantly surprised at how well it was all explained.</t>
         </is>
       </c>
-      <c r="F148" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
+      <c r="F148" t="n">
+        <v>5</v>
       </c>
       <c r="G148" t="inlineStr">
         <is>
@@ -7891,10 +7597,8 @@
           <t>My husband and I both said on the way out how nice everyone was. Pleasant and warm from start to finish.</t>
         </is>
       </c>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="F149" t="n">
+        <v>5</v>
       </c>
       <c r="G149" t="inlineStr">
         <is>
@@ -7941,10 +7645,8 @@
           <t>Fair prices and no funny business with the total. I was expecting to pay more. (rego 001YLL)</t>
         </is>
       </c>
-      <c r="F150" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="F150" t="n">
+        <v>5</v>
       </c>
       <c r="G150" t="inlineStr">
         <is>
@@ -7991,10 +7693,8 @@
           <t>For our three-van order, Gaz explained how the fleet discount is applied and exactly what's on each invoice Easy to pass on to our bookkeeper</t>
         </is>
       </c>
-      <c r="F151" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="F151" t="n">
+        <v>5</v>
       </c>
       <c r="G151" t="inlineStr">
         <is>
@@ -8041,10 +7741,8 @@
           <t>Friendly as. Even the bloke on the front lot waved and said g'day. (rego [REDACTED_REGO])</t>
         </is>
       </c>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="F152" t="n">
+        <v>5</v>
       </c>
       <c r="G152" t="inlineStr">
         <is>
@@ -8091,10 +7789,8 @@
           <t>[REDACTED_NAME] - Rang twice with updates, no need to call in himself. Said that's how it should be.</t>
         </is>
       </c>
-      <c r="F153" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="F153" t="n">
+        <v>5</v>
       </c>
       <c r="G153" t="inlineStr">
         <is>
@@ -8141,10 +7837,8 @@
           <t>Well isn't this a nuisance, everything running perfectly. How am I supposed to have a good whinge now?</t>
         </is>
       </c>
-      <c r="F154" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="F154" t="n">
+        <v>5</v>
       </c>
       <c r="G154" t="inlineStr">
         <is>
@@ -8191,10 +7885,8 @@
           <t>yeah nah, i usually switch off when mechanics talk, but this time i actually followed it all. (rego [REDACTED_REGO])</t>
         </is>
       </c>
-      <c r="F155" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="F155" t="n">
+        <v>5</v>
       </c>
       <c r="G155" t="inlineStr">
         <is>
@@ -8241,10 +7933,8 @@
           <t>Not once did I feel like a bother. Lovely people.</t>
         </is>
       </c>
-      <c r="F156" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="F156" t="n">
+        <v>5</v>
       </c>
       <c r="G156" t="inlineStr">
         <is>
@@ -8291,10 +7981,8 @@
           <t>Bit of a shock, honestly. Usually you hear nothing till you front up at the counter. This time the texts rolled in all day long.</t>
         </is>
       </c>
-      <c r="F157" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="F157" t="n">
+        <v>5</v>
       </c>
       <c r="G157" t="inlineStr">
         <is>
@@ -8341,10 +8029,8 @@
           <t>Everyone at the parts counter said g'day and genuinely wanted to help Part was ready when they said it'd be, which is more than I can say for other places I've tried</t>
         </is>
       </c>
-      <c r="F158" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="F158" t="n">
+        <v>5</v>
       </c>
       <c r="G158" t="inlineStr">
         <is>
@@ -8391,10 +8077,8 @@
           <t>Showed me where the spare tyre release is and how the jack works on the Voltra Arc, which I'd never bothered to learn. Handy to know.</t>
         </is>
       </c>
-      <c r="F159" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
+      <c r="F159" t="n">
+        <v>4</v>
       </c>
       <c r="G159" t="inlineStr">
         <is>
@@ -8441,10 +8125,8 @@
           <t>Was kept in the loop the whole time. Text when it was booked in, call when they found the extra work, text when done. That's all I ask.</t>
         </is>
       </c>
-      <c r="F160" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="F160" t="n">
+        <v>5</v>
       </c>
       <c r="G160" t="inlineStr">
         <is>
@@ -8491,10 +8173,8 @@
           <t>I appreciate the kind and respectful manner in which I was received The staff were most helpful</t>
         </is>
       </c>
-      <c r="F161" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
+      <c r="F161" t="n">
+        <v>4</v>
       </c>
       <c r="G161" t="inlineStr">
         <is>
@@ -8541,10 +8221,8 @@
           <t>Booked in Tuesday, collected Tuesday. That's the way it should be.</t>
         </is>
       </c>
-      <c r="F162" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
+      <c r="F162" t="n">
+        <v>4</v>
       </c>
       <c r="G162" t="inlineStr">
         <is>
@@ -8591,10 +8269,8 @@
           <t>Prices are very good, I am happy with how much I pay.</t>
         </is>
       </c>
-      <c r="F163" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="F163" t="n">
+        <v>5</v>
       </c>
       <c r="G163" t="inlineStr">
         <is>
@@ -8641,10 +8317,8 @@
           <t>Honestly the least stressful big purchase I've made. Felt like it organised itself.</t>
         </is>
       </c>
-      <c r="F164" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="F164" t="n">
+        <v>5</v>
       </c>
       <c r="G164" t="inlineStr">
         <is>
@@ -8691,10 +8365,8 @@
           <t>Faster than the other mob I used to go to, by a long way.</t>
         </is>
       </c>
-      <c r="F165" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="F165" t="n">
+        <v>5</v>
       </c>
       <c r="G165" t="inlineStr">
         <is>
@@ -8741,10 +8413,8 @@
           <t>RETIRED NOW SO I'M NOT IN A RUSH, BUT IT WAS NICE TO BE HANDED THE KEYS BACK WELL BEFORE LUNCH.</t>
         </is>
       </c>
-      <c r="F166" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
+      <c r="F166" t="n">
+        <v>4</v>
       </c>
       <c r="G166" t="inlineStr">
         <is>
@@ -8791,10 +8461,8 @@
           <t>Back-ordered part, so we were stuck with a loan car and car seats to shuffle for ages. Then the invoice showed a cleaning fee and a higher parts price than quoted. Bit rich.</t>
         </is>
       </c>
-      <c r="F167" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
+      <c r="F167" t="n">
+        <v>1</v>
       </c>
       <c r="G167" t="inlineStr">
         <is>
@@ -8846,10 +8514,8 @@
           <t>Pretty sure I was kept waiting 90 minutes. Yes, thanks to Kylie I now understand the paperwork. Fantastic use of my Saturday.</t>
         </is>
       </c>
-      <c r="F168" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
+      <c r="F168" t="n">
+        <v>3</v>
       </c>
       <c r="G168" t="inlineStr">
         <is>
@@ -8896,10 +8562,8 @@
           <t>Passed on a message through the front desk about a quote and it vanished into thin air.</t>
         </is>
       </c>
-      <c r="F169" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
+      <c r="F169" t="n">
+        <v>3</v>
       </c>
       <c r="G169" t="inlineStr">
         <is>
@@ -8946,10 +8610,8 @@
           <t>Nappy change table in the toilets was broken and the floor was wet. Said she ended up changing the baby on her lap in the car.</t>
         </is>
       </c>
-      <c r="F170" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
+      <c r="F170" t="n">
+        <v>1</v>
       </c>
       <c r="G170" t="inlineStr">
         <is>
@@ -8996,10 +8658,8 @@
           <t>Brake light still flickering. Honestly.</t>
         </is>
       </c>
-      <c r="F171" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
+      <c r="F171" t="n">
+        <v>1</v>
       </c>
       <c r="G171" t="inlineStr">
         <is>
@@ -9051,10 +8711,8 @@
           <t>Quick one: nobody called me back about my part. Twice. Sort it out.</t>
         </is>
       </c>
-      <c r="F172" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
+      <c r="F172" t="n">
+        <v>1</v>
       </c>
       <c r="G172" t="inlineStr">
         <is>
@@ -9101,10 +8759,8 @@
           <t>Been chasing the service desk for a week for an update on my Veyra S4. Emails ignored, clls go to voicemail. Pretty ordinary effort. (rego [REDACTED_REGO])</t>
         </is>
       </c>
-      <c r="F173" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
+      <c r="F173" t="n">
+        <v>1</v>
       </c>
       <c r="G173" t="inlineStr">
         <is>
@@ -9156,10 +8812,8 @@
           <t>Cust says first service on Corsa cost nearly double what the website said, and the check engine light is back on already. Not happy, felt a bit dudded as a first-timer.</t>
         </is>
       </c>
-      <c r="F174" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
+      <c r="F174" t="n">
+        <v>2</v>
       </c>
       <c r="G174" t="inlineStr">
         <is>
@@ -9211,10 +8865,8 @@
           <t>[REDACTED_NAME] - Sent a text from the car park asking if it was ready. No reply. Went in and they didn't know either.</t>
         </is>
       </c>
-      <c r="F175" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
+      <c r="F175" t="n">
+        <v>1</v>
       </c>
       <c r="G175" t="inlineStr">
         <is>
@@ -9261,10 +8913,8 @@
           <t>two kids under five, one meltdown, and a 70 minute wait just to get to the front of the queue. please add another person to the desk.</t>
         </is>
       </c>
-      <c r="F176" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
+      <c r="F176" t="n">
+        <v>2</v>
       </c>
       <c r="G176" t="inlineStr">
         <is>
@@ -9311,10 +8961,8 @@
           <t>Yeah nah. Nice blokes, but the job's rubbish.</t>
         </is>
       </c>
-      <c r="F177" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
+      <c r="F177" t="n">
+        <v>3</v>
       </c>
       <c r="G177" t="inlineStr">
         <is>
@@ -9361,10 +9009,8 @@
           <t>As a first car owner I was glad it was ready so fast, but the extras added to my bill gave me a shock. Email me [REDACTED_EMAIL]</t>
         </is>
       </c>
-      <c r="F178" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
+      <c r="F178" t="n">
+        <v>3</v>
       </c>
       <c r="G178" t="inlineStr">
         <is>
@@ -9416,10 +9062,8 @@
           <t>Overcharged. Rude about it too.</t>
         </is>
       </c>
-      <c r="F179" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
+      <c r="F179" t="n">
+        <v>1</v>
       </c>
       <c r="G179" t="inlineStr">
         <is>
@@ -9466,10 +9110,8 @@
           <t>BIT ANNOYED, MATE. QUOTED ONE PRICE, PAID ANOTHER, AND THE PART THEY NEEDED WASN'T EVEN HERE SO THE JOB DRAGGED ON FOR AGES.</t>
         </is>
       </c>
-      <c r="F180" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
+      <c r="F180" t="n">
+        <v>1</v>
       </c>
       <c r="G180" t="inlineStr">
         <is>
@@ -9516,10 +9158,8 @@
           <t>Ten days now for a headlight globe and I'm driving at night with one eye, basically. Call me on [REDACTED_PHONE].</t>
         </is>
       </c>
-      <c r="F181" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
+      <c r="F181" t="n">
+        <v>2</v>
       </c>
       <c r="G181" t="inlineStr">
         <is>
@@ -9571,10 +9211,8 @@
           <t>Really appreciated Mel calling to let me know how it was going. The car still has the problem though, so it felt like a bit of a waste.</t>
         </is>
       </c>
-      <c r="F182" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
+      <c r="F182" t="n">
+        <v>4</v>
       </c>
       <c r="G182" t="inlineStr">
         <is>
@@ -9621,10 +9259,8 @@
           <t>Honestly I expected better The window regulator was replaced and the glass now sits crooked and whistles at speed</t>
         </is>
       </c>
-      <c r="F183" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
+      <c r="F183" t="n">
+        <v>1</v>
       </c>
       <c r="G183" t="inlineStr">
         <is>
@@ -9671,10 +9307,8 @@
           <t>I do not know much about cars and I told Fatima this. He spoke to me like I was stupid and used lots of jargon on purpose, I think. I left feeling small.</t>
         </is>
       </c>
-      <c r="F184" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
+      <c r="F184" t="n">
+        <v>1</v>
       </c>
       <c r="G184" t="inlineStr">
         <is>
@@ -9726,10 +9360,8 @@
           <t>Oh brilliant, a hassle-free purchase, right up until the finance office tried to sell me every add-on under the sun. Five minutes of 'no' wasn't enough apparently.</t>
         </is>
       </c>
-      <c r="F185" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
+      <c r="F185" t="n">
+        <v>2</v>
       </c>
       <c r="G185" t="inlineStr">
         <is>
@@ -9776,10 +9408,8 @@
           <t>I asked for an update twice and both times was told it would be sent through. Neither ever arrived.</t>
         </is>
       </c>
-      <c r="F186" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
+      <c r="F186" t="n">
+        <v>1</v>
       </c>
       <c r="G186" t="inlineStr">
         <is>
@@ -9826,10 +9456,8 @@
           <t>Phones just rang and rang. Took forever for anyone to pick up.</t>
         </is>
       </c>
-      <c r="F187" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
+      <c r="F187" t="n">
+        <v>1</v>
       </c>
       <c r="G187" t="inlineStr">
         <is>
@@ -9876,10 +9504,8 @@
           <t>Emailed the service manager directly with a list of concerns about a clunk over speed humps. No reply, not even an acknowledgement. Had to phone, and then it was news to them. Email me [REDACTED_EMAIL]</t>
         </is>
       </c>
-      <c r="F188" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
+      <c r="F188" t="n">
+        <v>1</v>
       </c>
       <c r="G188" t="inlineStr">
         <is>
@@ -9931,10 +9557,8 @@
           <t>Booked a courtesy car and then waited ages for that too, nearly an hour at the counter before I got the keys.</t>
         </is>
       </c>
-      <c r="F189" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
+      <c r="F189" t="n">
+        <v>3</v>
       </c>
       <c r="G189" t="inlineStr">
         <is>
@@ -9981,10 +9605,8 @@
           <t>Said she doesn't understand the technical stuff but just wanted someone to tell her in plain words what was going on. Nobody got back to her.</t>
         </is>
       </c>
-      <c r="F190" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
+      <c r="F190" t="n">
+        <v>2</v>
       </c>
       <c r="G190" t="inlineStr">
         <is>
@@ -10031,10 +9653,8 @@
           <t>WAS THERE FROM 8AM AND THE BINS HADN'T BEEN EMPTIED SINCE THE DAY BEFORE BY THE LOOK OF IT. SMELT LIKE OLD TAKEAWAY.</t>
         </is>
       </c>
-      <c r="F191" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
+      <c r="F191" t="n">
+        <v>3</v>
       </c>
       <c r="G191" t="inlineStr">
         <is>
@@ -10081,10 +9701,8 @@
           <t>Turnaround was impressive, no waiting around. Shame they left a wheel nut loose, I noticed a wobble on the drive home and had to pull over and check.</t>
         </is>
       </c>
-      <c r="F192" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
+      <c r="F192" t="n">
+        <v>3</v>
       </c>
       <c r="G192" t="inlineStr">
         <is>
@@ -10136,10 +9754,8 @@
           <t>I dont know much about cars so I just nodded when Josh was talking real fast. Next minute I was in the carpark holding the key and I couldnt even find how to open the petrol cap. Wish someone had slowed down and shown me.</t>
         </is>
       </c>
-      <c r="F193" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
+      <c r="F193" t="n">
+        <v>2</v>
       </c>
       <c r="G193" t="inlineStr">
         <is>
@@ -10186,10 +9802,8 @@
           <t>Two hours of finance pressure and I still drove off not knowing if the range figure on the dash is real when towing. Nobody showed me the charge port settings either.</t>
         </is>
       </c>
-      <c r="F194" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
+      <c r="F194" t="n">
+        <v>3</v>
       </c>
       <c r="G194" t="inlineStr">
         <is>
@@ -10236,10 +9850,8 @@
           <t>Why does it take so long to be served at the service desk? Waited twenty-five minutes with nobody in sight.</t>
         </is>
       </c>
-      <c r="F195" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
+      <c r="F195" t="n">
+        <v>2</v>
       </c>
       <c r="G195" t="inlineStr">
         <is>
@@ -10286,10 +9898,8 @@
           <t>Look, I'm retired, I've got the time, and I still can't get a slot that suits. They keep offering days when the bus doesn't run near the place and I don't drive in the dark.</t>
         </is>
       </c>
-      <c r="F196" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
+      <c r="F196" t="n">
+        <v>1</v>
       </c>
       <c r="G196" t="inlineStr">
         <is>
@@ -10336,10 +9946,8 @@
           <t>Oh brilliant, another 'while we were in there' item added to the bill. Gee, thanks for looking out for my wallet.</t>
         </is>
       </c>
-      <c r="F197" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
+      <c r="F197" t="n">
+        <v>1</v>
       </c>
       <c r="G197" t="inlineStr">
         <is>
@@ -10391,10 +9999,8 @@
           <t>Two reschedules and the noise is still there. Useless.</t>
         </is>
       </c>
-      <c r="F198" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
+      <c r="F198" t="n">
+        <v>1</v>
       </c>
       <c r="G198" t="inlineStr">
         <is>
@@ -10441,10 +10047,8 @@
           <t>Quick and painless to book in. Not fixed.</t>
         </is>
       </c>
-      <c r="F199" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
+      <c r="F199" t="n">
+        <v>4</v>
       </c>
       <c r="G199" t="inlineStr">
         <is>
@@ -10491,10 +10095,8 @@
           <t>Oh brilliant, the paperwork was explained beautifully and I knew exactly what I was signing. Shame the same person couldn't be bothered to look up from his screen when I asked a simple question about the keys. Top service, truly.</t>
         </is>
       </c>
-      <c r="F200" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
+      <c r="F200" t="n">
+        <v>3</v>
       </c>
       <c r="G200" t="inlineStr">
         <is>
@@ -10546,10 +10148,8 @@
           <t>After years of loyalty I expected better The car sat there all day, and I had to chase for every scrap of information</t>
         </is>
       </c>
-      <c r="F201" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
+      <c r="F201" t="n">
+        <v>1</v>
       </c>
       <c r="G201" t="inlineStr">
         <is>
@@ -10596,10 +10196,8 @@
           <t>Pricing is all over the shop. Same service on my last Kodiak Trek was $100 cheaper and this time they've added bits I didn't ask for. Call me on [REDACTED_PHONE].</t>
         </is>
       </c>
-      <c r="F202" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
+      <c r="F202" t="n">
+        <v>2</v>
       </c>
       <c r="G202" t="inlineStr">
         <is>
@@ -10651,10 +10249,8 @@
           <t>terrible attitude from the girl on the phone, hung up before i'd finished.</t>
         </is>
       </c>
-      <c r="F203" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
+      <c r="F203" t="n">
+        <v>2</v>
       </c>
       <c r="G203" t="inlineStr">
         <is>
@@ -10701,10 +10297,8 @@
           <t>Do you people even check your voicemail? Asking because I've left five.</t>
         </is>
       </c>
-      <c r="F204" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
+      <c r="F204" t="n">
+        <v>3</v>
       </c>
       <c r="G204" t="inlineStr">
         <is>
@@ -10751,10 +10345,8 @@
           <t>Two-hour wait just to be told they didn't have the part. Cheers for that.</t>
         </is>
       </c>
-      <c r="F205" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
+      <c r="F205" t="n">
+        <v>2</v>
       </c>
       <c r="G205" t="inlineStr">
         <is>
@@ -10801,10 +10393,8 @@
           <t>i've bought four cars through this group over twenty-odd years and always had my servicing done here, so it pains me to write this. when i came in for the corsa's service, jess barely looked up from the screen, answered me in single words and made me feel i was holding up his day. i'd have thought loyalty counted for something. a little courtesy would have gone a long way. Email me [REDACTED_EMAIL]</t>
         </is>
       </c>
-      <c r="F206" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
+      <c r="F206" t="n">
+        <v>1</v>
       </c>
       <c r="G206" t="inlineStr">
         <is>
@@ -10856,10 +10446,8 @@
           <t>Just moved up from Melbourne and thought I'd give you a go. Calling and calling to find out about my car is not how I wanted to start.</t>
         </is>
       </c>
-      <c r="F207" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
+      <c r="F207" t="n">
+        <v>2</v>
       </c>
       <c r="G207" t="inlineStr">
         <is>
@@ -10906,10 +10494,8 @@
           <t>Bloody hopeless attitude. Nobody cared.</t>
         </is>
       </c>
-      <c r="F208" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
+      <c r="F208" t="n">
+        <v>1</v>
       </c>
       <c r="G208" t="inlineStr">
         <is>
@@ -10956,10 +10542,8 @@
           <t>My invoice says I paid for cabin filter and air filter. I only approved the air filter. Refund the cabin one please.</t>
         </is>
       </c>
-      <c r="F209" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
+      <c r="F209" t="n">
+        <v>2</v>
       </c>
       <c r="G209" t="inlineStr">
         <is>
@@ -11011,10 +10595,8 @@
           <t>Rang to book a service for my Vista and was told nothing available for five weeks Asked to be put on a cancellation list and was promised a call Still waiting, obviously</t>
         </is>
       </c>
-      <c r="F210" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
+      <c r="F210" t="n">
+        <v>1</v>
       </c>
       <c r="G210" t="inlineStr">
         <is>
@@ -11061,10 +10643,8 @@
           <t>Eight company cars to collect and every one had something wrong. Missing floor mats, no fuel, and two without keys for the lockbox. Took the whole day.</t>
         </is>
       </c>
-      <c r="F211" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
+      <c r="F211" t="n">
+        <v>1</v>
       </c>
       <c r="G211" t="inlineStr">
         <is>
@@ -11116,10 +10696,8 @@
           <t>Dear Parts Team, I wish to register my concern regarding the extended delay on a water pump for my Vista. I was advised ten business days and it has now exceeded five weeks.</t>
         </is>
       </c>
-      <c r="F212" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
+      <c r="F212" t="n">
+        <v>2</v>
       </c>
       <c r="G212" t="inlineStr">
         <is>
@@ -11171,10 +10749,8 @@
           <t>Two little ones in the back and no heater demister because the blower motor isn't available. Winter mornings are miserable. Weeks now.</t>
         </is>
       </c>
-      <c r="F213" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
+      <c r="F213" t="n">
+        <v>1</v>
       </c>
       <c r="G213" t="inlineStr">
         <is>
@@ -11226,10 +10802,8 @@
           <t>No signage to find the service reception, no covered walkway, and no seating outside. Got drenched finding my way in as a first-timer. Call me on [REDACTED_PHONE].</t>
         </is>
       </c>
-      <c r="F214" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
+      <c r="F214" t="n">
+        <v>2</v>
       </c>
       <c r="G214" t="inlineStr">
         <is>
@@ -11281,10 +10855,8 @@
           <t>Pickup time came and went, then the car sat in the carpark another 40 minutes while the counter sorted paperwork. School pickup was at 3:15 and I made it with about two minutes to spare, sweating the whole way.</t>
         </is>
       </c>
-      <c r="F215" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
+      <c r="F215" t="n">
+        <v>1</v>
       </c>
       <c r="G215" t="inlineStr">
         <is>
@@ -11331,10 +10903,8 @@
           <t>Can't believe you had no brake pads for my Terra. Brake pads!</t>
         </is>
       </c>
-      <c r="F216" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
+      <c r="F216" t="n">
+        <v>1</v>
       </c>
       <c r="G216" t="inlineStr">
         <is>
@@ -11386,10 +10956,8 @@
           <t>Told me everything in simple terms, no pressure. Then the car came back with the same noise. Back again next week I guess.</t>
         </is>
       </c>
-      <c r="F217" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
+      <c r="F217" t="n">
+        <v>3</v>
       </c>
       <c r="G217" t="inlineStr">
         <is>
@@ -11436,10 +11004,8 @@
           <t>left a greasy handprint on the headliner and one on the steering wheel. i notice these things.</t>
         </is>
       </c>
-      <c r="F218" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
+      <c r="F218" t="n">
+        <v>2</v>
       </c>
       <c r="G218" t="inlineStr">
         <is>
@@ -11486,10 +11052,8 @@
           <t>Honestly, how hard is it to send a text? One text. 'Your car is ready.' That's all I wanted.</t>
         </is>
       </c>
-      <c r="F219" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
+      <c r="F219" t="n">
+        <v>1</v>
       </c>
       <c r="G219" t="inlineStr">
         <is>
@@ -11536,10 +11100,8 @@
           <t>[REDACTED_NAME] - Moved here a month ago and has no idea who to ask for. Said she rang the number on the booking sheet and it just rolled to a generic message, so she's not sure anyone knows her car is there.</t>
         </is>
       </c>
-      <c r="F220" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
+      <c r="F220" t="n">
+        <v>1</v>
       </c>
       <c r="G220" t="inlineStr">
         <is>
@@ -11591,10 +11153,8 @@
           <t>They put the wrong hubcap on, one scratched and cracked, and kept the original. Not good enough.</t>
         </is>
       </c>
-      <c r="F221" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
+      <c r="F221" t="n">
+        <v>2</v>
       </c>
       <c r="G221" t="inlineStr">
         <is>
@@ -11641,10 +11201,8 @@
           <t>i understand that workshops get busy, but a two minute phone call to let me know what's happening is not too much to ask. i didn't get one.</t>
         </is>
       </c>
-      <c r="F222" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
+      <c r="F222" t="n">
+        <v>2</v>
       </c>
       <c r="G222" t="inlineStr">
         <is>
@@ -11691,10 +11249,8 @@
           <t>Uni student, tight budget, told them my limit twice. Still got the loan-and-insurance spiel every visit. Emailed for a quote, crickets.</t>
         </is>
       </c>
-      <c r="F223" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
+      <c r="F223" t="n">
+        <v>1</v>
       </c>
       <c r="G223" t="inlineStr">
         <is>
@@ -11741,10 +11297,8 @@
           <t>Waiting on a window regulator. Almost a month. Mate said his local mechanic got one in two days.</t>
         </is>
       </c>
-      <c r="F224" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
+      <c r="F224" t="n">
+        <v>1</v>
       </c>
       <c r="G224" t="inlineStr">
         <is>
@@ -11791,10 +11345,8 @@
           <t>Cheap service, rude staff.</t>
         </is>
       </c>
-      <c r="F225" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
+      <c r="F225" t="n">
+        <v>3</v>
       </c>
       <c r="G225" t="inlineStr">
         <is>
@@ -11841,10 +11393,8 @@
           <t>Noody tells you anything unless you ring, and then nobody knows anything either.</t>
         </is>
       </c>
-      <c r="F226" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
+      <c r="F226" t="n">
+        <v>1</v>
       </c>
       <c r="G226" t="inlineStr">
         <is>
@@ -11891,10 +11441,8 @@
           <t>I'm a bit shy about asking questions at the counter, so I just paid. Got home, looked at the receipt properly and there's $130 for a 'diagnostic scan' when the light was already explained to me as a loose gas cap. Feel pretty silly.</t>
         </is>
       </c>
-      <c r="F227" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="F227" t="n">
+        <v>1</v>
       </c>
       <c r="G227" t="inlineStr">
         <is>
@@ -11946,10 +11494,8 @@
           <t>Dash is covered in dust and there's a sticky patch on the gear stick. Did they even wipe it down?</t>
         </is>
       </c>
-      <c r="F228" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
+      <c r="F228" t="n">
+        <v>1</v>
       </c>
       <c r="G228" t="inlineStr">
         <is>
@@ -11996,10 +11542,8 @@
           <t>Parts. Again. (rego [REDACTED_REGO])</t>
         </is>
       </c>
-      <c r="F229" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
+      <c r="F229" t="n">
+        <v>1</v>
       </c>
       <c r="G229" t="inlineStr">
         <is>
@@ -12046,10 +11590,8 @@
           <t>Not sure if this is normal but the waiting area smelt strongly of something chemical and the windows were all fogged up. I don't know anything about cars so I wasn't sure if I should be worried, but I just wanted fresh air.</t>
         </is>
       </c>
-      <c r="F230" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
+      <c r="F230" t="n">
+        <v>1</v>
       </c>
       <c r="G230" t="inlineStr">
         <is>
@@ -12101,10 +11643,8 @@
           <t>Sorry for typos on my phone, in a hurry. Part wasn't there AGAIN. Third trip now.</t>
         </is>
       </c>
-      <c r="F231" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
+      <c r="F231" t="n">
+        <v>1</v>
       </c>
       <c r="G231" t="inlineStr">
         <is>
@@ -12151,10 +11691,8 @@
           <t>Been loyal to this place since my first car, and lately it's gone downhill. Can't get a booking when I need one, and last visit I waited nearly two hours past the pickup time they gave me.</t>
         </is>
       </c>
-      <c r="F232" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="F232" t="n">
+        <v>1</v>
       </c>
       <c r="G232" t="inlineStr">
         <is>
@@ -12201,10 +11739,8 @@
           <t>Great, another fantastic experience. Took 3 weeks to get a booking, and the car came back with the same rattle plus a lovely new scratch on the door.</t>
         </is>
       </c>
-      <c r="F233" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
+      <c r="F233" t="n">
+        <v>3</v>
       </c>
       <c r="G233" t="inlineStr">
         <is>
@@ -12251,10 +11787,8 @@
           <t>Rescheduled again.</t>
         </is>
       </c>
-      <c r="F234" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
+      <c r="F234" t="n">
+        <v>1</v>
       </c>
       <c r="G234" t="inlineStr">
         <is>
@@ -12301,10 +11835,8 @@
           <t>I DO NOT USE COMPUTER MUCH, MY DAUGHTER HELPED ME WITH THE NEW BOOKING WEBSITE. IT WOULD NOT LET US CHOOSE THE DAY WE WANTED AND THEN THE BOOKING DISAPPEARED. VERY FRUSTRATING FOR AN OLD MAN.</t>
         </is>
       </c>
-      <c r="F235" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
+      <c r="F235" t="n">
+        <v>1</v>
       </c>
       <c r="G235" t="inlineStr">
         <is>
@@ -12351,10 +11883,8 @@
           <t>i gave my mobile number and asked for a text once the part arrived. i'm still waiting for that text. i eventually rang, and it turned out the part had been there for nearly a week.</t>
         </is>
       </c>
-      <c r="F236" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
+      <c r="F236" t="n">
+        <v>3</v>
       </c>
       <c r="G236" t="inlineStr">
         <is>
@@ -12401,10 +11931,8 @@
           <t>The tradie in me knows when a job's been half done. Whoever did the brakes didn't bed them in or check them, and there's still a pulsing through the pedal.</t>
         </is>
       </c>
-      <c r="F237" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
+      <c r="F237" t="n">
+        <v>3</v>
       </c>
       <c r="G237" t="inlineStr">
         <is>
@@ -12456,10 +11984,8 @@
           <t>Ugh, five hours for what the booking said was a 'quick service'. Never again at this rate.</t>
         </is>
       </c>
-      <c r="F238" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
+      <c r="F238" t="n">
+        <v>2</v>
       </c>
       <c r="G238" t="inlineStr">
         <is>
@@ -12506,10 +12032,8 @@
           <t>SO THE PART IS 'ON ITS WAY FROM OVERSEAS'. OF COURSE IT IS. MEANWHILE I'M CATCHING THE BUS TO THE BOWLS CLUB WITH MY SHOPPING. Call me on [REDACTED_PHONE].</t>
         </is>
       </c>
-      <c r="F239" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
+      <c r="F239" t="n">
+        <v>1</v>
       </c>
       <c r="G239" t="inlineStr">
         <is>
@@ -12561,10 +12085,8 @@
           <t>Parts markup on my filters was ridiculous. Same filter is $19 at the auto shop and you charged $58.</t>
         </is>
       </c>
-      <c r="F240" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
+      <c r="F240" t="n">
+        <v>1</v>
       </c>
       <c r="G240" t="inlineStr">
         <is>
@@ -12611,10 +12133,8 @@
           <t>No idea what's happening with my car. Nobody tells me anything. I ask and they say wait. I wait.</t>
         </is>
       </c>
-      <c r="F241" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
+      <c r="F241" t="n">
+        <v>2</v>
       </c>
       <c r="G241" t="inlineStr">
         <is>
@@ -12661,10 +12181,8 @@
           <t>Quick job. No updates though, had to chase.</t>
         </is>
       </c>
-      <c r="F242" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
+      <c r="F242" t="n">
+        <v>2</v>
       </c>
       <c r="G242" t="inlineStr">
         <is>
@@ -12711,10 +12229,8 @@
           <t>I was told the service advisor would phone me with a quote before any work was done. That call never came, so I spent the day wondering what was happening with my car.</t>
         </is>
       </c>
-      <c r="F243" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
+      <c r="F243" t="n">
+        <v>1</v>
       </c>
       <c r="G243" t="inlineStr">
         <is>
@@ -12761,10 +12277,8 @@
           <t>They said it'd be done by lunch, so I walked to the shops and back. Twice. Ended up doing a third lap.</t>
         </is>
       </c>
-      <c r="F244" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
+      <c r="F244" t="n">
+        <v>2</v>
       </c>
       <c r="G244" t="inlineStr">
         <is>
@@ -12811,10 +12325,8 @@
           <t>Nice people, fault not fixed.</t>
         </is>
       </c>
-      <c r="F245" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
+      <c r="F245" t="n">
+        <v>2</v>
       </c>
       <c r="G245" t="inlineStr">
         <is>
@@ -12861,10 +12373,8 @@
           <t>Oh brilliant, I finally understand what a cambelt does. Shame the dealership doesn't seem to understand what 'having the part in stock' means. Fortnight and counting. Email me [REDACTED_EMAIL]</t>
         </is>
       </c>
-      <c r="F246" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
+      <c r="F246" t="n">
+        <v>4</v>
       </c>
       <c r="G246" t="inlineStr">
         <is>
@@ -12911,10 +12421,8 @@
           <t>honestly, the ’express service’ was a bit of a laugh. forty-five minutes was meant to be the go, and i was there for almost three hours. reckon i could’ve done it myself in the driveway.</t>
         </is>
       </c>
-      <c r="F247" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
+      <c r="F247" t="n">
+        <v>1</v>
       </c>
       <c r="G247" t="inlineStr">
         <is>
@@ -12961,10 +12469,8 @@
           <t>car returned with a dent in the rear bumper. asked raj about it and was told someone would call me back. still waiting.</t>
         </is>
       </c>
-      <c r="F248" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
+      <c r="F248" t="n">
+        <v>1</v>
       </c>
       <c r="G248" t="inlineStr">
         <is>
@@ -13016,10 +12522,8 @@
           <t>Reasonable price, fine. Part wasn't in stock, no ETA.</t>
         </is>
       </c>
-      <c r="F249" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
+      <c r="F249" t="n">
+        <v>3</v>
       </c>
       <c r="G249" t="inlineStr">
         <is>
@@ -13066,10 +12570,8 @@
           <t>Still waiting</t>
         </is>
       </c>
-      <c r="F250" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
+      <c r="F250" t="n">
+        <v>3</v>
       </c>
       <c r="G250" t="inlineStr">
         <is>
@@ -13116,10 +12618,8 @@
           <t>They phoned me as soon as they knew the part was delayed and kept updating me after that. Still, a week and a half for a part is a long time to be without wheels.</t>
         </is>
       </c>
-      <c r="F251" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
+      <c r="F251" t="n">
+        <v>3</v>
       </c>
       <c r="G251" t="inlineStr">
         <is>
@@ -13262,10 +12762,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
+      <c r="G2" t="n">
+        <v>3</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -13332,10 +12830,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
+      <c r="G3" t="n">
+        <v>3</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -13402,10 +12898,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
+      <c r="G4" t="n">
+        <v>3</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -13472,10 +12966,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
+      <c r="G5" t="n">
+        <v>3</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -13542,10 +13034,8 @@
           <t>Parts</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
+      <c r="G6" t="n">
+        <v>3</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -13612,10 +13102,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
+      <c r="G7" t="n">
+        <v>2</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -13687,10 +13175,8 @@
           <t>Sales</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
+      <c r="G8" t="n">
+        <v>1</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -13757,10 +13243,8 @@
           <t>Sales</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
+      <c r="G9" t="n">
+        <v>1</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -13827,10 +13311,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
+      <c r="G10" t="n">
+        <v>1</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -13897,10 +13379,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
+      <c r="G11" t="n">
+        <v>1</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -13972,10 +13452,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
+      <c r="G12" t="n">
+        <v>2</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -14042,10 +13520,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
+      <c r="G13" t="n">
+        <v>1</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -14112,10 +13588,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
+      <c r="G14" t="n">
+        <v>3</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -14182,10 +13656,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
+      <c r="G15" t="n">
+        <v>3</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -14252,10 +13724,8 @@
           <t>Sales</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
+      <c r="G16" t="n">
+        <v>4</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -14322,10 +13792,8 @@
           <t>Sales</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
+      <c r="G17" t="n">
+        <v>4</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -14392,10 +13860,8 @@
           <t>Parts</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
+      <c r="G18" t="n">
+        <v>1</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -14462,10 +13928,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
+      <c r="G19" t="n">
+        <v>2</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -14532,10 +13996,8 @@
           <t>Sales</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
+      <c r="G20" t="n">
+        <v>3</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -14602,10 +14064,8 @@
           <t>Sales</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
+      <c r="G21" t="n">
+        <v>3</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -14672,10 +14132,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
+      <c r="G22" t="n">
+        <v>3</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -14742,10 +14200,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
+      <c r="G23" t="n">
+        <v>3</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -14812,10 +14268,8 @@
           <t>Sales</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
+      <c r="G24" t="n">
+        <v>1</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -14887,10 +14341,8 @@
           <t>Sales</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
+      <c r="G25" t="n">
+        <v>1</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -14957,10 +14409,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
+      <c r="G26" t="n">
+        <v>1</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -15027,10 +14477,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
+      <c r="G27" t="n">
+        <v>1</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
@@ -15097,10 +14545,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
+      <c r="G28" t="n">
+        <v>1</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
@@ -15172,10 +14618,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
+      <c r="G29" t="n">
+        <v>1</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
@@ -15242,10 +14686,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
+      <c r="G30" t="n">
+        <v>2</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
@@ -15312,10 +14754,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
+      <c r="G31" t="n">
+        <v>1</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
@@ -15382,10 +14822,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
+      <c r="G32" t="n">
+        <v>1</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
@@ -15452,10 +14890,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
+      <c r="G33" t="n">
+        <v>1</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
@@ -15522,10 +14958,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
+      <c r="G34" t="n">
+        <v>2</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
@@ -15592,10 +15026,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
+      <c r="G35" t="n">
+        <v>2</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
@@ -15662,10 +15094,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
+      <c r="G36" t="n">
+        <v>1</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
@@ -15737,10 +15167,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
+      <c r="G37" t="n">
+        <v>1</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
@@ -15812,10 +15240,8 @@
           <t>Sales</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
+      <c r="G38" t="n">
+        <v>3</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
@@ -15882,10 +15308,8 @@
           <t>Sales</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
+      <c r="G39" t="n">
+        <v>3</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
@@ -15952,10 +15376,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
+      <c r="G40" t="n">
+        <v>3</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
@@ -16022,10 +15444,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
+      <c r="G41" t="n">
+        <v>3</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
@@ -16092,10 +15512,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
+      <c r="G42" t="n">
+        <v>1</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
@@ -16162,10 +15580,8 @@
           <t>Parts</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
+      <c r="G43" t="n">
+        <v>1</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
@@ -16232,10 +15648,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
+      <c r="G44" t="n">
+        <v>3</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
@@ -16302,10 +15716,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
+      <c r="G45" t="n">
+        <v>3</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
@@ -16372,10 +15784,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
+      <c r="G46" t="n">
+        <v>3</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
@@ -16447,10 +15857,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
+      <c r="G47" t="n">
+        <v>1</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
@@ -16522,10 +15930,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
+      <c r="G48" t="n">
+        <v>1</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
@@ -16597,10 +16003,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
+      <c r="G49" t="n">
+        <v>2</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
@@ -16667,10 +16071,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
+      <c r="G50" t="n">
+        <v>2</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
@@ -16737,10 +16139,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
+      <c r="G51" t="n">
+        <v>3</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
@@ -16807,10 +16207,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
+      <c r="G52" t="n">
+        <v>3</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
@@ -16877,10 +16275,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
+      <c r="G53" t="n">
+        <v>3</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
@@ -16947,10 +16343,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
+      <c r="G54" t="n">
+        <v>3</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
@@ -17022,10 +16416,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
+      <c r="G55" t="n">
+        <v>1</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
@@ -17092,10 +16484,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
+      <c r="G56" t="n">
+        <v>1</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
@@ -17162,10 +16552,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
+      <c r="G57" t="n">
+        <v>1</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
@@ -17232,10 +16620,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
+      <c r="G58" t="n">
+        <v>3</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
@@ -17302,10 +16688,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
+      <c r="G59" t="n">
+        <v>3</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
@@ -17372,10 +16756,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
+      <c r="G60" t="n">
+        <v>3</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
@@ -17442,10 +16824,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
+      <c r="G61" t="n">
+        <v>3</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
@@ -17512,10 +16892,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
+      <c r="G62" t="n">
+        <v>3</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
@@ -17587,10 +16965,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
+      <c r="G63" t="n">
+        <v>1</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
@@ -17657,10 +17033,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
+      <c r="G64" t="n">
+        <v>3</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
@@ -17727,10 +17101,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
+      <c r="G65" t="n">
+        <v>3</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
@@ -17797,10 +17169,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
+      <c r="G66" t="n">
+        <v>1</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
@@ -17872,10 +17242,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
+      <c r="G67" t="n">
+        <v>1</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
@@ -17947,10 +17315,8 @@
           <t>Sales</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
+      <c r="G68" t="n">
+        <v>3</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
@@ -18017,10 +17383,8 @@
           <t>Sales</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
+      <c r="G69" t="n">
+        <v>3</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
@@ -18092,10 +17456,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
+      <c r="G70" t="n">
+        <v>4</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
@@ -18162,10 +17524,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
+      <c r="G71" t="n">
+        <v>4</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
@@ -18232,10 +17592,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
+      <c r="G72" t="n">
+        <v>3</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
@@ -18307,10 +17665,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
+      <c r="G73" t="n">
+        <v>3</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
@@ -18382,10 +17738,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
+      <c r="G74" t="n">
+        <v>2</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
@@ -18452,10 +17806,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
+      <c r="G75" t="n">
+        <v>2</v>
       </c>
       <c r="H75" t="inlineStr">
         <is>
@@ -18522,10 +17874,8 @@
           <t>Sales</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
+      <c r="G76" t="n">
+        <v>3</v>
       </c>
       <c r="H76" t="inlineStr">
         <is>
@@ -18592,10 +17942,8 @@
           <t>Sales</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
+      <c r="G77" t="n">
+        <v>3</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
@@ -18662,10 +18010,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
+      <c r="G78" t="n">
+        <v>3</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
@@ -18732,10 +18078,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
+      <c r="G79" t="n">
+        <v>3</v>
       </c>
       <c r="H79" t="inlineStr">
         <is>
@@ -18802,10 +18146,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
+      <c r="G80" t="n">
+        <v>4</v>
       </c>
       <c r="H80" t="inlineStr">
         <is>
@@ -18872,10 +18214,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
+      <c r="G81" t="n">
+        <v>4</v>
       </c>
       <c r="H81" t="inlineStr">
         <is>
@@ -18942,10 +18282,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
+      <c r="G82" t="n">
+        <v>1</v>
       </c>
       <c r="H82" t="inlineStr">
         <is>
@@ -19012,10 +18350,8 @@
           <t>Sales</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
+      <c r="G83" t="n">
+        <v>2</v>
       </c>
       <c r="H83" t="inlineStr">
         <is>
@@ -19082,10 +18418,8 @@
           <t>Sales</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
+      <c r="G84" t="n">
+        <v>2</v>
       </c>
       <c r="H84" t="inlineStr">
         <is>
@@ -19152,10 +18486,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
+      <c r="G85" t="n">
+        <v>2</v>
       </c>
       <c r="H85" t="inlineStr">
         <is>
@@ -19222,10 +18554,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
+      <c r="G86" t="n">
+        <v>2</v>
       </c>
       <c r="H86" t="inlineStr">
         <is>
@@ -19292,10 +18622,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
+      <c r="G87" t="n">
+        <v>1</v>
       </c>
       <c r="H87" t="inlineStr">
         <is>
@@ -19362,10 +18690,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
+      <c r="G88" t="n">
+        <v>1</v>
       </c>
       <c r="H88" t="inlineStr">
         <is>
@@ -19432,10 +18758,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
+      <c r="G89" t="n">
+        <v>4</v>
       </c>
       <c r="H89" t="inlineStr">
         <is>
@@ -19502,10 +18826,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
+      <c r="G90" t="n">
+        <v>4</v>
       </c>
       <c r="H90" t="inlineStr">
         <is>
@@ -19572,10 +18894,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
+      <c r="G91" t="n">
+        <v>1</v>
       </c>
       <c r="H91" t="inlineStr">
         <is>
@@ -19642,10 +18962,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
+      <c r="G92" t="n">
+        <v>1</v>
       </c>
       <c r="H92" t="inlineStr">
         <is>
@@ -19712,10 +19030,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
+      <c r="G93" t="n">
+        <v>2</v>
       </c>
       <c r="H93" t="inlineStr">
         <is>
@@ -19787,10 +19103,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
+      <c r="G94" t="n">
+        <v>2</v>
       </c>
       <c r="H94" t="inlineStr">
         <is>
@@ -19857,10 +19171,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
+      <c r="G95" t="n">
+        <v>2</v>
       </c>
       <c r="H95" t="inlineStr">
         <is>
@@ -19927,10 +19239,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
+      <c r="G96" t="n">
+        <v>2</v>
       </c>
       <c r="H96" t="inlineStr">
         <is>
@@ -19997,10 +19307,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
+      <c r="G97" t="n">
+        <v>3</v>
       </c>
       <c r="H97" t="inlineStr">
         <is>
@@ -20067,10 +19375,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
+      <c r="G98" t="n">
+        <v>3</v>
       </c>
       <c r="H98" t="inlineStr">
         <is>
@@ -20137,10 +19443,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
+      <c r="G99" t="n">
+        <v>2</v>
       </c>
       <c r="H99" t="inlineStr">
         <is>
@@ -20207,10 +19511,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
+      <c r="G100" t="n">
+        <v>2</v>
       </c>
       <c r="H100" t="inlineStr">
         <is>
@@ -20277,10 +19579,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
+      <c r="G101" t="n">
+        <v>1</v>
       </c>
       <c r="H101" t="inlineStr">
         <is>
@@ -20347,10 +19647,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
+      <c r="G102" t="n">
+        <v>1</v>
       </c>
       <c r="H102" t="inlineStr">
         <is>
@@ -20417,10 +19715,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
+      <c r="G103" t="n">
+        <v>3</v>
       </c>
       <c r="H103" t="inlineStr">
         <is>
@@ -20487,10 +19783,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
+      <c r="G104" t="n">
+        <v>3</v>
       </c>
       <c r="H104" t="inlineStr">
         <is>
@@ -20557,10 +19851,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
+      <c r="G105" t="n">
+        <v>4</v>
       </c>
       <c r="H105" t="inlineStr">
         <is>
@@ -20627,10 +19919,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
+      <c r="G106" t="n">
+        <v>4</v>
       </c>
       <c r="H106" t="inlineStr">
         <is>
@@ -20697,10 +19987,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
+      <c r="G107" t="n">
+        <v>4</v>
       </c>
       <c r="H107" t="inlineStr">
         <is>
@@ -20767,10 +20055,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
+      <c r="G108" t="n">
+        <v>3</v>
       </c>
       <c r="H108" t="inlineStr">
         <is>
@@ -20837,10 +20123,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
+      <c r="G109" t="n">
+        <v>2</v>
       </c>
       <c r="H109" t="inlineStr">
         <is>
@@ -20907,10 +20191,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
+      <c r="G110" t="n">
+        <v>1</v>
       </c>
       <c r="H110" t="inlineStr">
         <is>
@@ -20977,10 +20259,8 @@
           <t>Parts</t>
         </is>
       </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
+      <c r="G111" t="n">
+        <v>3</v>
       </c>
       <c r="H111" t="inlineStr">
         <is>
@@ -21047,10 +20327,8 @@
           <t>Parts</t>
         </is>
       </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
+      <c r="G112" t="n">
+        <v>3</v>
       </c>
       <c r="H112" t="inlineStr">
         <is>
@@ -21117,10 +20395,8 @@
           <t>Sales</t>
         </is>
       </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
+      <c r="G113" t="n">
+        <v>3</v>
       </c>
       <c r="H113" t="inlineStr">
         <is>
@@ -21187,10 +20463,8 @@
           <t>Sales</t>
         </is>
       </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
+      <c r="G114" t="n">
+        <v>3</v>
       </c>
       <c r="H114" t="inlineStr">
         <is>
@@ -21257,10 +20531,8 @@
           <t>Sales</t>
         </is>
       </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
+      <c r="G115" t="n">
+        <v>3</v>
       </c>
       <c r="H115" t="inlineStr">
         <is>
@@ -21327,10 +20599,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
+      <c r="G116" t="n">
+        <v>2</v>
       </c>
       <c r="H116" t="inlineStr">
         <is>
@@ -21397,10 +20667,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
+      <c r="G117" t="n">
+        <v>3</v>
       </c>
       <c r="H117" t="inlineStr">
         <is>
@@ -21467,10 +20735,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
+      <c r="G118" t="n">
+        <v>3</v>
       </c>
       <c r="H118" t="inlineStr">
         <is>
@@ -21537,10 +20803,8 @@
           <t>Parts</t>
         </is>
       </c>
-      <c r="G119" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
+      <c r="G119" t="n">
+        <v>1</v>
       </c>
       <c r="H119" t="inlineStr">
         <is>
@@ -21607,10 +20871,8 @@
           <t>Parts</t>
         </is>
       </c>
-      <c r="G120" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
+      <c r="G120" t="n">
+        <v>1</v>
       </c>
       <c r="H120" t="inlineStr">
         <is>
@@ -21677,10 +20939,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
+      <c r="G121" t="n">
+        <v>2</v>
       </c>
       <c r="H121" t="inlineStr">
         <is>
@@ -21747,10 +21007,8 @@
           <t>Parts</t>
         </is>
       </c>
-      <c r="G122" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
+      <c r="G122" t="n">
+        <v>2</v>
       </c>
       <c r="H122" t="inlineStr">
         <is>
@@ -21822,10 +21080,8 @@
           <t>Parts</t>
         </is>
       </c>
-      <c r="G123" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
+      <c r="G123" t="n">
+        <v>2</v>
       </c>
       <c r="H123" t="inlineStr">
         <is>
@@ -21892,10 +21148,8 @@
           <t>Parts</t>
         </is>
       </c>
-      <c r="G124" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
+      <c r="G124" t="n">
+        <v>2</v>
       </c>
       <c r="H124" t="inlineStr">
         <is>
@@ -21962,10 +21216,8 @@
           <t>Parts</t>
         </is>
       </c>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
+      <c r="G125" t="n">
+        <v>2</v>
       </c>
       <c r="H125" t="inlineStr">
         <is>
@@ -22037,10 +21289,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
+      <c r="G126" t="n">
+        <v>1</v>
       </c>
       <c r="H126" t="inlineStr">
         <is>
@@ -22112,10 +21362,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
+      <c r="G127" t="n">
+        <v>2</v>
       </c>
       <c r="H127" t="inlineStr">
         <is>
@@ -22182,10 +21430,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G128" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
+      <c r="G128" t="n">
+        <v>1</v>
       </c>
       <c r="H128" t="inlineStr">
         <is>
@@ -22252,10 +21498,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G129" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
+      <c r="G129" t="n">
+        <v>1</v>
       </c>
       <c r="H129" t="inlineStr">
         <is>
@@ -22322,10 +21566,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
+      <c r="G130" t="n">
+        <v>3</v>
       </c>
       <c r="H130" t="inlineStr">
         <is>
@@ -22392,10 +21634,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G131" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
+      <c r="G131" t="n">
+        <v>3</v>
       </c>
       <c r="H131" t="inlineStr">
         <is>
@@ -22462,10 +21702,8 @@
           <t>Sales</t>
         </is>
       </c>
-      <c r="G132" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
+      <c r="G132" t="n">
+        <v>2</v>
       </c>
       <c r="H132" t="inlineStr">
         <is>
@@ -22532,10 +21770,8 @@
           <t>Sales</t>
         </is>
       </c>
-      <c r="G133" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
+      <c r="G133" t="n">
+        <v>2</v>
       </c>
       <c r="H133" t="inlineStr">
         <is>
@@ -22602,10 +21838,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G134" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
+      <c r="G134" t="n">
+        <v>4</v>
       </c>
       <c r="H134" t="inlineStr">
         <is>
@@ -22672,10 +21906,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G135" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
+      <c r="G135" t="n">
+        <v>4</v>
       </c>
       <c r="H135" t="inlineStr">
         <is>
@@ -22742,10 +21974,8 @@
           <t>Sales</t>
         </is>
       </c>
-      <c r="G136" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
+      <c r="G136" t="n">
+        <v>2</v>
       </c>
       <c r="H136" t="inlineStr">
         <is>
@@ -22812,10 +22042,8 @@
           <t>Sales</t>
         </is>
       </c>
-      <c r="G137" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
+      <c r="G137" t="n">
+        <v>2</v>
       </c>
       <c r="H137" t="inlineStr">
         <is>
@@ -22882,10 +22110,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G138" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
+      <c r="G138" t="n">
+        <v>2</v>
       </c>
       <c r="H138" t="inlineStr">
         <is>
@@ -22952,10 +22178,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G139" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
+      <c r="G139" t="n">
+        <v>1</v>
       </c>
       <c r="H139" t="inlineStr">
         <is>
@@ -23022,10 +22246,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G140" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
+      <c r="G140" t="n">
+        <v>1</v>
       </c>
       <c r="H140" t="inlineStr">
         <is>
@@ -23097,10 +22319,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G141" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
+      <c r="G141" t="n">
+        <v>1</v>
       </c>
       <c r="H141" t="inlineStr">
         <is>
@@ -23172,10 +22392,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G142" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
+      <c r="G142" t="n">
+        <v>1</v>
       </c>
       <c r="H142" t="inlineStr">
         <is>
@@ -23242,10 +22460,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G143" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
+      <c r="G143" t="n">
+        <v>2</v>
       </c>
       <c r="H143" t="inlineStr">
         <is>
@@ -23312,10 +22528,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G144" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
+      <c r="G144" t="n">
+        <v>2</v>
       </c>
       <c r="H144" t="inlineStr">
         <is>
@@ -23382,10 +22596,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G145" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
+      <c r="G145" t="n">
+        <v>1</v>
       </c>
       <c r="H145" t="inlineStr">
         <is>
@@ -23452,10 +22664,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G146" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
+      <c r="G146" t="n">
+        <v>3</v>
       </c>
       <c r="H146" t="inlineStr">
         <is>
@@ -23522,10 +22732,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G147" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
+      <c r="G147" t="n">
+        <v>3</v>
       </c>
       <c r="H147" t="inlineStr">
         <is>
@@ -23592,10 +22800,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G148" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
+      <c r="G148" t="n">
+        <v>3</v>
       </c>
       <c r="H148" t="inlineStr">
         <is>
@@ -23662,10 +22868,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G149" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
+      <c r="G149" t="n">
+        <v>3</v>
       </c>
       <c r="H149" t="inlineStr">
         <is>
@@ -23732,10 +22936,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G150" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
+      <c r="G150" t="n">
+        <v>4</v>
       </c>
       <c r="H150" t="inlineStr">
         <is>
@@ -23802,10 +23004,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G151" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
+      <c r="G151" t="n">
+        <v>4</v>
       </c>
       <c r="H151" t="inlineStr">
         <is>
@@ -23872,10 +23072,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G152" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
+      <c r="G152" t="n">
+        <v>1</v>
       </c>
       <c r="H152" t="inlineStr">
         <is>
@@ -23942,10 +23140,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G153" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
+      <c r="G153" t="n">
+        <v>2</v>
       </c>
       <c r="H153" t="inlineStr">
         <is>
@@ -24012,10 +23208,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G154" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
+      <c r="G154" t="n">
+        <v>2</v>
       </c>
       <c r="H154" t="inlineStr">
         <is>
@@ -24082,10 +23276,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G155" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
+      <c r="G155" t="n">
+        <v>1</v>
       </c>
       <c r="H155" t="inlineStr">
         <is>
@@ -24157,10 +23349,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G156" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
+      <c r="G156" t="n">
+        <v>4</v>
       </c>
       <c r="H156" t="inlineStr">
         <is>
@@ -24227,10 +23417,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G157" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
+      <c r="G157" t="n">
+        <v>4</v>
       </c>
       <c r="H157" t="inlineStr">
         <is>
@@ -24297,10 +23485,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G158" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
+      <c r="G158" t="n">
+        <v>1</v>
       </c>
       <c r="H158" t="inlineStr">
         <is>
@@ -24372,10 +23558,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G159" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
+      <c r="G159" t="n">
+        <v>1</v>
       </c>
       <c r="H159" t="inlineStr">
         <is>
@@ -24442,10 +23626,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G160" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
+      <c r="G160" t="n">
+        <v>2</v>
       </c>
       <c r="H160" t="inlineStr">
         <is>
@@ -24512,10 +23694,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G161" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
+      <c r="G161" t="n">
+        <v>2</v>
       </c>
       <c r="H161" t="inlineStr">
         <is>
@@ -24582,10 +23762,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G162" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
+      <c r="G162" t="n">
+        <v>1</v>
       </c>
       <c r="H162" t="inlineStr">
         <is>
@@ -24652,10 +23830,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G163" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
+      <c r="G163" t="n">
+        <v>3</v>
       </c>
       <c r="H163" t="inlineStr">
         <is>
@@ -24722,10 +23898,8 @@
           <t>Parts</t>
         </is>
       </c>
-      <c r="G164" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
+      <c r="G164" t="n">
+        <v>1</v>
       </c>
       <c r="H164" t="inlineStr">
         <is>
@@ -24792,10 +23966,8 @@
           <t>Parts</t>
         </is>
       </c>
-      <c r="G165" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
+      <c r="G165" t="n">
+        <v>1</v>
       </c>
       <c r="H165" t="inlineStr">
         <is>
@@ -24867,10 +24039,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G166" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
+      <c r="G166" t="n">
+        <v>1</v>
       </c>
       <c r="H166" t="inlineStr">
         <is>
@@ -24937,10 +24107,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G167" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
+      <c r="G167" t="n">
+        <v>1</v>
       </c>
       <c r="H167" t="inlineStr">
         <is>
@@ -25007,10 +24175,8 @@
           <t>Sales</t>
         </is>
       </c>
-      <c r="G168" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
+      <c r="G168" t="n">
+        <v>3</v>
       </c>
       <c r="H168" t="inlineStr">
         <is>
@@ -25077,10 +24243,8 @@
           <t>Sales</t>
         </is>
       </c>
-      <c r="G169" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
+      <c r="G169" t="n">
+        <v>3</v>
       </c>
       <c r="H169" t="inlineStr">
         <is>
@@ -25147,10 +24311,8 @@
           <t>Sales</t>
         </is>
       </c>
-      <c r="G170" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
+      <c r="G170" t="n">
+        <v>1</v>
       </c>
       <c r="H170" t="inlineStr">
         <is>
@@ -25222,10 +24384,8 @@
           <t>Sales</t>
         </is>
       </c>
-      <c r="G171" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
+      <c r="G171" t="n">
+        <v>1</v>
       </c>
       <c r="H171" t="inlineStr">
         <is>
@@ -25292,10 +24452,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G172" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="G172" t="n">
+        <v>1</v>
       </c>
       <c r="H172" t="inlineStr">
         <is>
@@ -25367,10 +24525,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G173" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="G173" t="n">
+        <v>1</v>
       </c>
       <c r="H173" t="inlineStr">
         <is>
@@ -25437,10 +24593,8 @@
           <t>Sales</t>
         </is>
       </c>
-      <c r="G174" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
+      <c r="G174" t="n">
+        <v>4</v>
       </c>
       <c r="H174" t="inlineStr">
         <is>
@@ -25507,10 +24661,8 @@
           <t>Sales</t>
         </is>
       </c>
-      <c r="G175" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
+      <c r="G175" t="n">
+        <v>4</v>
       </c>
       <c r="H175" t="inlineStr">
         <is>
@@ -25577,10 +24729,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G176" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
+      <c r="G176" t="n">
+        <v>4</v>
       </c>
       <c r="H176" t="inlineStr">
         <is>
@@ -25647,10 +24797,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G177" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
+      <c r="G177" t="n">
+        <v>4</v>
       </c>
       <c r="H177" t="inlineStr">
         <is>
@@ -25717,10 +24865,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G178" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="G178" t="n">
+        <v>1</v>
       </c>
       <c r="H178" t="inlineStr">
         <is>
@@ -25787,10 +24933,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G179" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="G179" t="n">
+        <v>1</v>
       </c>
       <c r="H179" t="inlineStr">
         <is>
@@ -25857,10 +25001,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G180" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
+      <c r="G180" t="n">
+        <v>3</v>
       </c>
       <c r="H180" t="inlineStr">
         <is>
@@ -25927,10 +25069,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G181" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
+      <c r="G181" t="n">
+        <v>3</v>
       </c>
       <c r="H181" t="inlineStr">
         <is>
@@ -25997,10 +25137,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G182" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
+      <c r="G182" t="n">
+        <v>2</v>
       </c>
       <c r="H182" t="inlineStr">
         <is>
@@ -26072,10 +25210,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G183" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
+      <c r="G183" t="n">
+        <v>2</v>
       </c>
       <c r="H183" t="inlineStr">
         <is>
@@ -26142,10 +25278,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G184" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
+      <c r="G184" t="n">
+        <v>2</v>
       </c>
       <c r="H184" t="inlineStr">
         <is>
@@ -26217,10 +25351,8 @@
           <t>Parts</t>
         </is>
       </c>
-      <c r="G185" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
+      <c r="G185" t="n">
+        <v>1</v>
       </c>
       <c r="H185" t="inlineStr">
         <is>
@@ -26287,10 +25419,8 @@
           <t>Parts</t>
         </is>
       </c>
-      <c r="G186" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
+      <c r="G186" t="n">
+        <v>1</v>
       </c>
       <c r="H186" t="inlineStr">
         <is>
@@ -26362,10 +25492,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G187" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
+      <c r="G187" t="n">
+        <v>3</v>
       </c>
       <c r="H187" t="inlineStr">
         <is>
@@ -26432,10 +25560,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G188" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
+      <c r="G188" t="n">
+        <v>3</v>
       </c>
       <c r="H188" t="inlineStr">
         <is>
@@ -26502,10 +25628,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G189" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
+      <c r="G189" t="n">
+        <v>4</v>
       </c>
       <c r="H189" t="inlineStr">
         <is>
@@ -26572,10 +25696,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G190" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
+      <c r="G190" t="n">
+        <v>4</v>
       </c>
       <c r="H190" t="inlineStr">
         <is>
@@ -26642,10 +25764,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G191" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
+      <c r="G191" t="n">
+        <v>1</v>
       </c>
       <c r="H191" t="inlineStr">
         <is>
@@ -26712,10 +25832,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G192" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
+      <c r="G192" t="n">
+        <v>1</v>
       </c>
       <c r="H192" t="inlineStr">
         <is>
@@ -26782,10 +25900,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G193" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="G193" t="n">
+        <v>5</v>
       </c>
       <c r="H193" t="inlineStr">
         <is>
@@ -26842,10 +25958,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G194" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="G194" t="n">
+        <v>5</v>
       </c>
       <c r="H194" t="inlineStr">
         <is>
@@ -26902,10 +26016,8 @@
           <t>Sales</t>
         </is>
       </c>
-      <c r="G195" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="G195" t="n">
+        <v>5</v>
       </c>
       <c r="H195" t="inlineStr">
         <is>
@@ -26962,10 +26074,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G196" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="G196" t="n">
+        <v>5</v>
       </c>
       <c r="H196" t="inlineStr">
         <is>
@@ -27022,10 +26132,8 @@
           <t>Sales</t>
         </is>
       </c>
-      <c r="G197" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="G197" t="n">
+        <v>5</v>
       </c>
       <c r="H197" t="inlineStr">
         <is>
@@ -27082,10 +26190,8 @@
           <t>Sales</t>
         </is>
       </c>
-      <c r="G198" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="G198" t="n">
+        <v>5</v>
       </c>
       <c r="H198" t="inlineStr">
         <is>
@@ -27142,10 +26248,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G199" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
+      <c r="G199" t="n">
+        <v>4</v>
       </c>
       <c r="H199" t="inlineStr">
         <is>
@@ -27202,10 +26306,8 @@
           <t>Parts</t>
         </is>
       </c>
-      <c r="G200" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="G200" t="n">
+        <v>5</v>
       </c>
       <c r="H200" t="inlineStr">
         <is>
@@ -27262,10 +26364,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G201" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="G201" t="n">
+        <v>5</v>
       </c>
       <c r="H201" t="inlineStr">
         <is>
@@ -27322,10 +26422,8 @@
           <t>Sales</t>
         </is>
       </c>
-      <c r="G202" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="G202" t="n">
+        <v>5</v>
       </c>
       <c r="H202" t="inlineStr">
         <is>
@@ -27382,10 +26480,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G203" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="G203" t="n">
+        <v>5</v>
       </c>
       <c r="H203" t="inlineStr">
         <is>
@@ -27442,10 +26538,8 @@
           <t>Sales</t>
         </is>
       </c>
-      <c r="G204" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="G204" t="n">
+        <v>5</v>
       </c>
       <c r="H204" t="inlineStr">
         <is>
@@ -27502,10 +26596,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G205" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
+      <c r="G205" t="n">
+        <v>4</v>
       </c>
       <c r="H205" t="inlineStr">
         <is>
@@ -27562,10 +26654,8 @@
           <t>Sales</t>
         </is>
       </c>
-      <c r="G206" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
+      <c r="G206" t="n">
+        <v>4</v>
       </c>
       <c r="H206" t="inlineStr">
         <is>
@@ -27622,10 +26712,8 @@
           <t>Parts</t>
         </is>
       </c>
-      <c r="G207" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="G207" t="n">
+        <v>5</v>
       </c>
       <c r="H207" t="inlineStr">
         <is>
@@ -27682,10 +26770,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G208" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="G208" t="n">
+        <v>5</v>
       </c>
       <c r="H208" t="inlineStr">
         <is>
@@ -27742,10 +26828,8 @@
           <t>Sales</t>
         </is>
       </c>
-      <c r="G209" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="G209" t="n">
+        <v>5</v>
       </c>
       <c r="H209" t="inlineStr">
         <is>
@@ -27802,10 +26886,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G210" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="G210" t="n">
+        <v>5</v>
       </c>
       <c r="H210" t="inlineStr">
         <is>
@@ -27862,10 +26944,8 @@
           <t>Sales</t>
         </is>
       </c>
-      <c r="G211" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
+      <c r="G211" t="n">
+        <v>4</v>
       </c>
       <c r="H211" t="inlineStr">
         <is>
@@ -27922,10 +27002,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G212" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
+      <c r="G212" t="n">
+        <v>4</v>
       </c>
       <c r="H212" t="inlineStr">
         <is>
@@ -27982,10 +27060,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G213" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="G213" t="n">
+        <v>5</v>
       </c>
       <c r="H213" t="inlineStr">
         <is>
@@ -28042,10 +27118,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G214" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="G214" t="n">
+        <v>5</v>
       </c>
       <c r="H214" t="inlineStr">
         <is>
@@ -28102,10 +27176,8 @@
           <t>Sales</t>
         </is>
       </c>
-      <c r="G215" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="G215" t="n">
+        <v>5</v>
       </c>
       <c r="H215" t="inlineStr">
         <is>
@@ -28162,10 +27234,8 @@
           <t>Sales</t>
         </is>
       </c>
-      <c r="G216" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
+      <c r="G216" t="n">
+        <v>4</v>
       </c>
       <c r="H216" t="inlineStr">
         <is>
@@ -28222,10 +27292,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G217" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="G217" t="n">
+        <v>5</v>
       </c>
       <c r="H217" t="inlineStr">
         <is>
@@ -28282,10 +27350,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G218" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="G218" t="n">
+        <v>5</v>
       </c>
       <c r="H218" t="inlineStr">
         <is>
@@ -28342,10 +27408,8 @@
           <t>Sales</t>
         </is>
       </c>
-      <c r="G219" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
+      <c r="G219" t="n">
+        <v>4</v>
       </c>
       <c r="H219" t="inlineStr">
         <is>
@@ -28402,10 +27466,8 @@
           <t>Sales</t>
         </is>
       </c>
-      <c r="G220" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
+      <c r="G220" t="n">
+        <v>4</v>
       </c>
       <c r="H220" t="inlineStr">
         <is>
@@ -28462,10 +27524,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G221" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="G221" t="n">
+        <v>5</v>
       </c>
       <c r="H221" t="inlineStr">
         <is>
@@ -28522,10 +27582,8 @@
           <t>Sales</t>
         </is>
       </c>
-      <c r="G222" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
+      <c r="G222" t="n">
+        <v>4</v>
       </c>
       <c r="H222" t="inlineStr">
         <is>
@@ -28582,10 +27640,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G223" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="G223" t="n">
+        <v>5</v>
       </c>
       <c r="H223" t="inlineStr">
         <is>
@@ -28642,10 +27698,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G224" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="G224" t="n">
+        <v>5</v>
       </c>
       <c r="H224" t="inlineStr">
         <is>
@@ -28702,10 +27756,8 @@
           <t>Sales</t>
         </is>
       </c>
-      <c r="G225" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
+      <c r="G225" t="n">
+        <v>4</v>
       </c>
       <c r="H225" t="inlineStr">
         <is>
@@ -28762,10 +27814,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G226" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="G226" t="n">
+        <v>5</v>
       </c>
       <c r="H226" t="inlineStr">
         <is>
@@ -28822,10 +27872,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G227" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
+      <c r="G227" t="n">
+        <v>4</v>
       </c>
       <c r="H227" t="inlineStr">
         <is>
@@ -28882,10 +27930,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G228" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
+      <c r="G228" t="n">
+        <v>4</v>
       </c>
       <c r="H228" t="inlineStr">
         <is>
@@ -28942,10 +27988,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G229" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="G229" t="n">
+        <v>5</v>
       </c>
       <c r="H229" t="inlineStr">
         <is>
@@ -29002,10 +28046,8 @@
           <t>Sales</t>
         </is>
       </c>
-      <c r="G230" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="G230" t="n">
+        <v>5</v>
       </c>
       <c r="H230" t="inlineStr">
         <is>
@@ -29062,10 +28104,8 @@
           <t>Parts</t>
         </is>
       </c>
-      <c r="G231" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="G231" t="n">
+        <v>5</v>
       </c>
       <c r="H231" t="inlineStr">
         <is>
@@ -29122,10 +28162,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G232" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="G232" t="n">
+        <v>5</v>
       </c>
       <c r="H232" t="inlineStr">
         <is>
@@ -29182,10 +28220,8 @@
           <t>Sales</t>
         </is>
       </c>
-      <c r="G233" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
+      <c r="G233" t="n">
+        <v>4</v>
       </c>
       <c r="H233" t="inlineStr">
         <is>
@@ -29242,10 +28278,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G234" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
+      <c r="G234" t="n">
+        <v>4</v>
       </c>
       <c r="H234" t="inlineStr">
         <is>
@@ -29302,10 +28336,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G235" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="G235" t="n">
+        <v>5</v>
       </c>
       <c r="H235" t="inlineStr">
         <is>
@@ -29362,10 +28394,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G236" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
+      <c r="G236" t="n">
+        <v>4</v>
       </c>
       <c r="H236" t="inlineStr">
         <is>
@@ -29422,10 +28452,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G237" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
+      <c r="G237" t="n">
+        <v>4</v>
       </c>
       <c r="H237" t="inlineStr">
         <is>
@@ -29482,10 +28510,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G238" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
+      <c r="G238" t="n">
+        <v>4</v>
       </c>
       <c r="H238" t="inlineStr">
         <is>
@@ -29542,10 +28568,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G239" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="G239" t="n">
+        <v>5</v>
       </c>
       <c r="H239" t="inlineStr">
         <is>
@@ -29602,10 +28626,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G240" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="G240" t="n">
+        <v>5</v>
       </c>
       <c r="H240" t="inlineStr">
         <is>
@@ -29662,10 +28684,8 @@
           <t>Sales</t>
         </is>
       </c>
-      <c r="G241" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="G241" t="n">
+        <v>5</v>
       </c>
       <c r="H241" t="inlineStr">
         <is>
@@ -29722,10 +28742,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G242" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
+      <c r="G242" t="n">
+        <v>4</v>
       </c>
       <c r="H242" t="inlineStr">
         <is>
@@ -29782,10 +28800,8 @@
           <t>Parts</t>
         </is>
       </c>
-      <c r="G243" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="G243" t="n">
+        <v>5</v>
       </c>
       <c r="H243" t="inlineStr">
         <is>
@@ -29842,10 +28858,8 @@
           <t>Parts</t>
         </is>
       </c>
-      <c r="G244" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="G244" t="n">
+        <v>5</v>
       </c>
       <c r="H244" t="inlineStr">
         <is>
@@ -29902,10 +28916,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G245" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="G245" t="n">
+        <v>5</v>
       </c>
       <c r="H245" t="inlineStr">
         <is>
@@ -29962,10 +28974,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G246" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
+      <c r="G246" t="n">
+        <v>4</v>
       </c>
       <c r="H246" t="inlineStr">
         <is>
@@ -30022,10 +29032,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G247" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="G247" t="n">
+        <v>5</v>
       </c>
       <c r="H247" t="inlineStr">
         <is>
@@ -30082,10 +29090,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G248" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="G248" t="n">
+        <v>5</v>
       </c>
       <c r="H248" t="inlineStr">
         <is>
@@ -30142,10 +29148,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G249" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="G249" t="n">
+        <v>5</v>
       </c>
       <c r="H249" t="inlineStr">
         <is>
@@ -30202,10 +29206,8 @@
           <t>Sales</t>
         </is>
       </c>
-      <c r="G250" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="G250" t="n">
+        <v>5</v>
       </c>
       <c r="H250" t="inlineStr">
         <is>
@@ -30262,10 +29264,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G251" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="G251" t="n">
+        <v>5</v>
       </c>
       <c r="H251" t="inlineStr">
         <is>
@@ -30322,10 +29322,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G252" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
+      <c r="G252" t="n">
+        <v>4</v>
       </c>
       <c r="H252" t="inlineStr">
         <is>
@@ -30382,10 +29380,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G253" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="G253" t="n">
+        <v>5</v>
       </c>
       <c r="H253" t="inlineStr">
         <is>
@@ -30442,10 +29438,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G254" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="G254" t="n">
+        <v>5</v>
       </c>
       <c r="H254" t="inlineStr">
         <is>
@@ -30502,10 +29496,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G255" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="G255" t="n">
+        <v>5</v>
       </c>
       <c r="H255" t="inlineStr">
         <is>
@@ -30562,10 +29554,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G256" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
+      <c r="G256" t="n">
+        <v>4</v>
       </c>
       <c r="H256" t="inlineStr">
         <is>
@@ -30622,10 +29612,8 @@
           <t>Parts</t>
         </is>
       </c>
-      <c r="G257" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="G257" t="n">
+        <v>5</v>
       </c>
       <c r="H257" t="inlineStr">
         <is>
@@ -30682,10 +29670,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G258" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="G258" t="n">
+        <v>5</v>
       </c>
       <c r="H258" t="inlineStr">
         <is>
@@ -30742,10 +29728,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G259" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="G259" t="n">
+        <v>5</v>
       </c>
       <c r="H259" t="inlineStr">
         <is>
@@ -30802,10 +29786,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G260" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
+      <c r="G260" t="n">
+        <v>4</v>
       </c>
       <c r="H260" t="inlineStr">
         <is>
@@ -30862,10 +29844,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G261" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="G261" t="n">
+        <v>5</v>
       </c>
       <c r="H261" t="inlineStr">
         <is>
@@ -30922,10 +29902,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G262" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
+      <c r="G262" t="n">
+        <v>4</v>
       </c>
       <c r="H262" t="inlineStr">
         <is>
@@ -30982,10 +29960,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G263" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="G263" t="n">
+        <v>5</v>
       </c>
       <c r="H263" t="inlineStr">
         <is>
@@ -31042,10 +30018,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G264" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
+      <c r="G264" t="n">
+        <v>4</v>
       </c>
       <c r="H264" t="inlineStr">
         <is>
@@ -31102,10 +30076,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G265" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
+      <c r="G265" t="n">
+        <v>3</v>
       </c>
       <c r="H265" t="inlineStr">
         <is>
@@ -31162,10 +30134,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G266" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="G266" t="n">
+        <v>5</v>
       </c>
       <c r="H266" t="inlineStr">
         <is>
@@ -31222,10 +30192,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G267" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="G267" t="n">
+        <v>5</v>
       </c>
       <c r="H267" t="inlineStr">
         <is>
@@ -31282,10 +30250,8 @@
           <t>Unknown</t>
         </is>
       </c>
-      <c r="G268" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="G268" t="n">
+        <v>5</v>
       </c>
       <c r="H268" t="inlineStr">
         <is>
@@ -31342,10 +30308,8 @@
           <t>Sales</t>
         </is>
       </c>
-      <c r="G269" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="G269" t="n">
+        <v>5</v>
       </c>
       <c r="H269" t="inlineStr">
         <is>
@@ -31402,10 +30366,8 @@
           <t>Parts</t>
         </is>
       </c>
-      <c r="G270" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="G270" t="n">
+        <v>5</v>
       </c>
       <c r="H270" t="inlineStr">
         <is>
@@ -31462,10 +30424,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G271" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="G271" t="n">
+        <v>5</v>
       </c>
       <c r="H271" t="inlineStr">
         <is>
@@ -31522,10 +30482,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G272" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="G272" t="n">
+        <v>5</v>
       </c>
       <c r="H272" t="inlineStr">
         <is>
@@ -31582,10 +30540,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G273" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="G273" t="n">
+        <v>5</v>
       </c>
       <c r="H273" t="inlineStr">
         <is>
@@ -31642,10 +30598,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G274" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
+      <c r="G274" t="n">
+        <v>4</v>
       </c>
       <c r="H274" t="inlineStr">
         <is>
@@ -31702,10 +30656,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G275" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="G275" t="n">
+        <v>5</v>
       </c>
       <c r="H275" t="inlineStr">
         <is>
@@ -31762,10 +30714,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G276" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="G276" t="n">
+        <v>5</v>
       </c>
       <c r="H276" t="inlineStr">
         <is>
@@ -31822,10 +30772,8 @@
           <t>Parts</t>
         </is>
       </c>
-      <c r="G277" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="G277" t="n">
+        <v>5</v>
       </c>
       <c r="H277" t="inlineStr">
         <is>
@@ -31882,10 +30830,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G278" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="G278" t="n">
+        <v>5</v>
       </c>
       <c r="H278" t="inlineStr">
         <is>
@@ -31942,10 +30888,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G279" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="G279" t="n">
+        <v>5</v>
       </c>
       <c r="H279" t="inlineStr">
         <is>
@@ -32002,10 +30946,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G280" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
+      <c r="G280" t="n">
+        <v>4</v>
       </c>
       <c r="H280" t="inlineStr">
         <is>
@@ -32062,10 +31004,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G281" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="G281" t="n">
+        <v>5</v>
       </c>
       <c r="H281" t="inlineStr">
         <is>
@@ -32122,10 +31062,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G282" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="G282" t="n">
+        <v>5</v>
       </c>
       <c r="H282" t="inlineStr">
         <is>
@@ -32182,10 +31120,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G283" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="G283" t="n">
+        <v>5</v>
       </c>
       <c r="H283" t="inlineStr">
         <is>
@@ -32242,10 +31178,8 @@
           <t>Parts</t>
         </is>
       </c>
-      <c r="G284" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="G284" t="n">
+        <v>5</v>
       </c>
       <c r="H284" t="inlineStr">
         <is>
@@ -32302,10 +31236,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G285" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="G285" t="n">
+        <v>5</v>
       </c>
       <c r="H285" t="inlineStr">
         <is>
@@ -32362,10 +31294,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G286" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="G286" t="n">
+        <v>5</v>
       </c>
       <c r="H286" t="inlineStr">
         <is>
@@ -32422,10 +31352,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G287" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="G287" t="n">
+        <v>5</v>
       </c>
       <c r="H287" t="inlineStr">
         <is>
@@ -32482,10 +31410,8 @@
           <t>Sales</t>
         </is>
       </c>
-      <c r="G288" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="G288" t="n">
+        <v>5</v>
       </c>
       <c r="H288" t="inlineStr">
         <is>
@@ -32542,10 +31468,8 @@
           <t>Sales</t>
         </is>
       </c>
-      <c r="G289" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
+      <c r="G289" t="n">
+        <v>4</v>
       </c>
       <c r="H289" t="inlineStr">
         <is>
@@ -32602,10 +31526,8 @@
           <t>Sales</t>
         </is>
       </c>
-      <c r="G290" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="G290" t="n">
+        <v>5</v>
       </c>
       <c r="H290" t="inlineStr">
         <is>
@@ -32662,10 +31584,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G291" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="G291" t="n">
+        <v>5</v>
       </c>
       <c r="H291" t="inlineStr">
         <is>
@@ -32722,10 +31642,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G292" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
+      <c r="G292" t="n">
+        <v>4</v>
       </c>
       <c r="H292" t="inlineStr">
         <is>
@@ -32782,10 +31700,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G293" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="G293" t="n">
+        <v>5</v>
       </c>
       <c r="H293" t="inlineStr">
         <is>
@@ -32842,10 +31758,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G294" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="G294" t="n">
+        <v>5</v>
       </c>
       <c r="H294" t="inlineStr">
         <is>
@@ -32902,10 +31816,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G295" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
+      <c r="G295" t="n">
+        <v>4</v>
       </c>
       <c r="H295" t="inlineStr">
         <is>
@@ -32962,10 +31874,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G296" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="G296" t="n">
+        <v>5</v>
       </c>
       <c r="H296" t="inlineStr">
         <is>
@@ -33022,10 +31932,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G297" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="G297" t="n">
+        <v>5</v>
       </c>
       <c r="H297" t="inlineStr">
         <is>
@@ -33082,10 +31990,8 @@
           <t>Parts</t>
         </is>
       </c>
-      <c r="G298" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="G298" t="n">
+        <v>5</v>
       </c>
       <c r="H298" t="inlineStr">
         <is>
@@ -33142,10 +32048,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G299" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="G299" t="n">
+        <v>5</v>
       </c>
       <c r="H299" t="inlineStr">
         <is>
@@ -33202,10 +32106,8 @@
           <t>Sales</t>
         </is>
       </c>
-      <c r="G300" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
+      <c r="G300" t="n">
+        <v>4</v>
       </c>
       <c r="H300" t="inlineStr">
         <is>
@@ -33262,10 +32164,8 @@
           <t>Sales</t>
         </is>
       </c>
-      <c r="G301" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="G301" t="n">
+        <v>5</v>
       </c>
       <c r="H301" t="inlineStr">
         <is>
@@ -33322,10 +32222,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G302" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="G302" t="n">
+        <v>5</v>
       </c>
       <c r="H302" t="inlineStr">
         <is>
@@ -33382,10 +32280,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G303" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
+      <c r="G303" t="n">
+        <v>4</v>
       </c>
       <c r="H303" t="inlineStr">
         <is>
@@ -33442,10 +32338,8 @@
           <t>Sales</t>
         </is>
       </c>
-      <c r="G304" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="G304" t="n">
+        <v>5</v>
       </c>
       <c r="H304" t="inlineStr">
         <is>
@@ -33502,10 +32396,8 @@
           <t>Sales</t>
         </is>
       </c>
-      <c r="G305" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="G305" t="n">
+        <v>5</v>
       </c>
       <c r="H305" t="inlineStr">
         <is>
@@ -33562,10 +32454,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G306" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
+      <c r="G306" t="n">
+        <v>4</v>
       </c>
       <c r="H306" t="inlineStr">
         <is>
@@ -33622,10 +32512,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G307" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="G307" t="n">
+        <v>5</v>
       </c>
       <c r="H307" t="inlineStr">
         <is>
@@ -33682,10 +32570,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G308" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="G308" t="n">
+        <v>5</v>
       </c>
       <c r="H308" t="inlineStr">
         <is>
@@ -33742,10 +32628,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G309" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
+      <c r="G309" t="n">
+        <v>4</v>
       </c>
       <c r="H309" t="inlineStr">
         <is>
@@ -33802,10 +32686,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G310" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
+      <c r="G310" t="n">
+        <v>4</v>
       </c>
       <c r="H310" t="inlineStr">
         <is>
@@ -33862,10 +32744,8 @@
           <t>Sales</t>
         </is>
       </c>
-      <c r="G311" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="G311" t="n">
+        <v>5</v>
       </c>
       <c r="H311" t="inlineStr">
         <is>
@@ -33922,10 +32802,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G312" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="G312" t="n">
+        <v>5</v>
       </c>
       <c r="H312" t="inlineStr">
         <is>
@@ -33982,10 +32860,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G313" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="G313" t="n">
+        <v>5</v>
       </c>
       <c r="H313" t="inlineStr">
         <is>
@@ -34042,10 +32918,8 @@
           <t>Parts</t>
         </is>
       </c>
-      <c r="G314" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="G314" t="n">
+        <v>5</v>
       </c>
       <c r="H314" t="inlineStr">
         <is>
@@ -34102,10 +32976,8 @@
           <t>Sales</t>
         </is>
       </c>
-      <c r="G315" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
+      <c r="G315" t="n">
+        <v>4</v>
       </c>
       <c r="H315" t="inlineStr">
         <is>
@@ -34162,10 +33034,8 @@
           <t>Sales</t>
         </is>
       </c>
-      <c r="G316" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="G316" t="n">
+        <v>5</v>
       </c>
       <c r="H316" t="inlineStr">
         <is>
@@ -34222,10 +33092,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G317" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="G317" t="n">
+        <v>5</v>
       </c>
       <c r="H317" t="inlineStr">
         <is>
@@ -34282,10 +33150,8 @@
           <t>Parts</t>
         </is>
       </c>
-      <c r="G318" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
+      <c r="G318" t="n">
+        <v>5</v>
       </c>
       <c r="H318" t="inlineStr">
         <is>
@@ -34342,10 +33208,8 @@
           <t>Sales</t>
         </is>
       </c>
-      <c r="G319" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
+      <c r="G319" t="n">
+        <v>5</v>
       </c>
       <c r="H319" t="inlineStr">
         <is>
@@ -34402,10 +33266,8 @@
           <t>Sales</t>
         </is>
       </c>
-      <c r="G320" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
+      <c r="G320" t="n">
+        <v>4</v>
       </c>
       <c r="H320" t="inlineStr">
         <is>
@@ -34462,10 +33324,8 @@
           <t>Sales</t>
         </is>
       </c>
-      <c r="G321" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
+      <c r="G321" t="n">
+        <v>5</v>
       </c>
       <c r="H321" t="inlineStr">
         <is>
@@ -34522,10 +33382,8 @@
           <t>Sales</t>
         </is>
       </c>
-      <c r="G322" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
+      <c r="G322" t="n">
+        <v>5</v>
       </c>
       <c r="H322" t="inlineStr">
         <is>
@@ -34582,10 +33440,8 @@
           <t>Parts</t>
         </is>
       </c>
-      <c r="G323" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
+      <c r="G323" t="n">
+        <v>5</v>
       </c>
       <c r="H323" t="inlineStr">
         <is>
@@ -34642,10 +33498,8 @@
           <t>Parts</t>
         </is>
       </c>
-      <c r="G324" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="G324" t="n">
+        <v>5</v>
       </c>
       <c r="H324" t="inlineStr">
         <is>
@@ -34702,10 +33556,8 @@
           <t>Parts</t>
         </is>
       </c>
-      <c r="G325" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
+      <c r="G325" t="n">
+        <v>4</v>
       </c>
       <c r="H325" t="inlineStr">
         <is>
@@ -34762,10 +33614,8 @@
           <t>Parts</t>
         </is>
       </c>
-      <c r="G326" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="G326" t="n">
+        <v>5</v>
       </c>
       <c r="H326" t="inlineStr">
         <is>
@@ -34822,10 +33672,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G327" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="G327" t="n">
+        <v>5</v>
       </c>
       <c r="H327" t="inlineStr">
         <is>
@@ -34882,10 +33730,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G328" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="G328" t="n">
+        <v>5</v>
       </c>
       <c r="H328" t="inlineStr">
         <is>
@@ -34942,10 +33788,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G329" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="G329" t="n">
+        <v>5</v>
       </c>
       <c r="H329" t="inlineStr">
         <is>
@@ -35002,10 +33846,8 @@
           <t>Service</t>
         </is>
       </c>
-      <c r="G330" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
+      <c r="G330" t="n">
+        <v>5</v>
       </c>
       <c r="H330" t="inlineStr">
         <is>
@@ -35108,7 +33950,6 @@
         </is>
       </c>
     </row>
-    <row r="10"/>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
